--- a/rejected_guests.xlsx
+++ b/rejected_guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA120"/>
+  <dimension ref="A1:AA88"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -516,28 +516,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>80590616-1876-4bcc-aa17-e9a92b2be8c6</v>
+        <v>35ab59d2-67e0-45ea-9954-fc2bddbfa672</v>
       </c>
       <c r="C2" t="str">
-        <v>Lucky Ali</v>
+        <v>AASIF</v>
       </c>
       <c r="D2" t="str">
-        <v>aasukhark@gmail.com</v>
+        <v>darkhorriblestories@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>7082671024</v>
+        <v>9050056941</v>
       </c>
       <c r="F2" t="str">
-        <v>7082671024</v>
+        <v>9050056941</v>
       </c>
       <c r="G2" t="str">
-        <v>Govt Model Sanskriti Sr Sec School Israna Panipat</v>
+        <v>Govt.Model Sanskriti Sr. Sec. School</v>
       </c>
       <c r="H2" t="str">
         <v>Yes</v>
       </c>
       <c r="I2" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J2" t="str">
         <v>Haryana</v>
@@ -567,31 +567,31 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>STUDENT_PASS_80590616</v>
+        <v>STUDENT_PASS_35AB59D2</v>
       </c>
       <c r="T2" t="str">
-        <v>Saved (51.2 KB)</v>
+        <v>Saved (100.7 KB)</v>
       </c>
       <c r="U2" t="str">
-        <v>rejected_guest_documents/80590616-1876-4bcc-aa17-e9a92b2be8c6_school_id.jpg</v>
+        <v>rejected_guest_documents/35ab59d2-67e0-45ea-9954-fc2bddbfa672_school_id.jpg</v>
       </c>
       <c r="V2" t="str">
-        <v>Saved (143.0 KB)</v>
+        <v>Saved (92.3 KB)</v>
       </c>
       <c r="W2" t="str">
-        <v>rejected_guest_documents/80590616-1876-4bcc-aa17-e9a92b2be8c6_aadhar.jpg</v>
+        <v>rejected_guest_documents/35ab59d2-67e0-45ea-9954-fc2bddbfa672_aadhar.jpg</v>
       </c>
       <c r="X2" t="str">
         <v>No</v>
       </c>
       <c r="Y2" t="str">
-        <v>2/10/2026, 10:50:13 pm</v>
+        <v>3/10/2026, 12:11:16 pm</v>
       </c>
       <c r="Z2" t="str">
-        <v>2/10/2026, 11:25:24 pm</v>
+        <v>3/10/2026, 12:15:28 pm</v>
       </c>
       <c r="AA2" t="str">
-        <v>6abfe7cd7ef9e5b5deaae462</v>
+        <v>6ac0a38c5fa47f7f445803cd</v>
       </c>
     </row>
     <row r="3">
@@ -599,28 +599,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>aa43ae38-d7ee-41ae-81c5-05794fdd1311</v>
+        <v>3a87e4da-6552-4d4d-8b7f-e0306aad9039</v>
       </c>
       <c r="C3" t="str">
-        <v>Ansh</v>
+        <v>Aasif</v>
       </c>
       <c r="D3" t="str">
-        <v>anshhuria5@gmail.com</v>
+        <v>luckykhark05@gmail.com</v>
       </c>
       <c r="E3" t="str">
-        <v>8950886149</v>
+        <v>8571895972</v>
       </c>
       <c r="F3" t="str">
-        <v>8950886149</v>
+        <v>8571895972</v>
       </c>
       <c r="G3" t="str">
-        <v>National Institute of open schooling</v>
+        <v>Govt Model Sanskriti Sr Sec School Israna Panipat</v>
       </c>
       <c r="H3" t="str">
         <v>Yes</v>
       </c>
       <c r="I3" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J3" t="str">
         <v>Haryana</v>
@@ -650,31 +650,31 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>STUDENT_PASS_AA43AE38</v>
+        <v>STUDENT_PASS_3A87E4DA</v>
       </c>
       <c r="T3" t="str">
-        <v>Saved (15.0 KB)</v>
+        <v>Saved (100.7 KB)</v>
       </c>
       <c r="U3" t="str">
-        <v>rejected_guest_documents/aa43ae38-d7ee-41ae-81c5-05794fdd1311_school_id.jpg</v>
+        <v>rejected_guest_documents/3a87e4da-6552-4d4d-8b7f-e0306aad9039_school_id.jpg</v>
       </c>
       <c r="V3" t="str">
-        <v>Saved (67.2 KB)</v>
+        <v>Saved (130.9 KB)</v>
       </c>
       <c r="W3" t="str">
-        <v>rejected_guest_documents/aa43ae38-d7ee-41ae-81c5-05794fdd1311_aadhar.jpg</v>
+        <v>rejected_guest_documents/3a87e4da-6552-4d4d-8b7f-e0306aad9039_aadhar.jpg</v>
       </c>
       <c r="X3" t="str">
         <v>No</v>
       </c>
       <c r="Y3" t="str">
-        <v>2/10/2026, 10:31:30 pm</v>
+        <v>3/10/2026, 12:11:09 pm</v>
       </c>
       <c r="Z3" t="str">
-        <v>2/10/2026, 11:30:58 pm</v>
+        <v>3/10/2026, 12:15:54 pm</v>
       </c>
       <c r="AA3" t="str">
-        <v>6abfe36ac75b2c080a827bc1</v>
+        <v>6ac0a3855fa47f7f445803c9</v>
       </c>
     </row>
     <row r="4">
@@ -682,28 +682,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>27d9d4fb-b1c8-4790-81bb-e46c741da977</v>
+        <v>56e05b7d-ed4f-4997-9e00-609a447f2aa6</v>
       </c>
       <c r="C4" t="str">
-        <v>Preeti</v>
+        <v>Aasuf</v>
       </c>
       <c r="D4" t="str">
-        <v>Preeti200811@gmail.com</v>
+        <v>luckykhark05@gmail.com</v>
       </c>
       <c r="E4" t="str">
-        <v>8571800955</v>
+        <v>8571895972</v>
       </c>
       <c r="F4" t="str">
-        <v>8571800955</v>
+        <v>8571895972</v>
       </c>
       <c r="G4" t="str">
-        <v>PM. SHRI G.G.S.S.S. MODEL TOWN PANIPAT</v>
+        <v>Govt Model Sanskriti Sr Sec School Israna Panipat</v>
       </c>
       <c r="H4" t="str">
         <v>Yes</v>
       </c>
       <c r="I4" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J4" t="str">
         <v>Haryana</v>
@@ -733,31 +733,31 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v>STUDENT_PASS_27D9D4FB</v>
+        <v>STUDENT_PASS_56E05B7D</v>
       </c>
       <c r="T4" t="str">
-        <v>Saved (86.3 KB)</v>
+        <v>Saved (100.7 KB)</v>
       </c>
       <c r="U4" t="str">
-        <v>rejected_guest_documents/27d9d4fb-b1c8-4790-81bb-e46c741da977_school_id.jpg</v>
+        <v>rejected_guest_documents/56e05b7d-ed4f-4997-9e00-609a447f2aa6_school_id.jpg</v>
       </c>
       <c r="V4" t="str">
-        <v>Saved (46.0 KB)</v>
+        <v>Saved (130.9 KB)</v>
       </c>
       <c r="W4" t="str">
-        <v>rejected_guest_documents/27d9d4fb-b1c8-4790-81bb-e46c741da977_aadhar.jpg</v>
+        <v>rejected_guest_documents/56e05b7d-ed4f-4997-9e00-609a447f2aa6_aadhar.jpg</v>
       </c>
       <c r="X4" t="str">
         <v>No</v>
       </c>
       <c r="Y4" t="str">
-        <v>2/10/2026, 5:17:08 pm</v>
+        <v>3/10/2026, 12:10:00 pm</v>
       </c>
       <c r="Z4" t="str">
-        <v>2/10/2026, 11:33:59 pm</v>
+        <v>3/10/2026, 12:17:55 pm</v>
       </c>
       <c r="AA4" t="str">
-        <v>6abf99bcd9286e3efe7ea963</v>
+        <v>6ac0a3405fa47f7f445803ad</v>
       </c>
     </row>
     <row r="5">
@@ -765,19 +765,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>4d01c983-85b2-40ea-a9c6-bacb7fdf03e4</v>
+        <v>f059ed3c-2886-4dbe-9299-796674ac4963</v>
       </c>
       <c r="C5" t="str">
-        <v>Karan</v>
+        <v>Mayank</v>
       </c>
       <c r="D5" t="str">
-        <v>Karanshankwar2008@gmail.com</v>
+        <v>ranimanju38952@gmail.com</v>
       </c>
       <c r="E5" t="str">
-        <v>8570932504</v>
+        <v>9034774449</v>
       </c>
       <c r="F5" t="str">
-        <v>8570932504</v>
+        <v>9034774449</v>
       </c>
       <c r="G5" t="str">
         <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
@@ -786,7 +786,7 @@
         <v>No</v>
       </c>
       <c r="I5" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J5" t="str">
         <v>Haryana</v>
@@ -816,31 +816,31 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>STUDENT_PASS_4D01C983</v>
+        <v>STUDENT_PASS_F059ED3C</v>
       </c>
       <c r="T5" t="str">
-        <v>Saved (11.6 KB)</v>
+        <v>Saved (71.0 KB)</v>
       </c>
       <c r="U5" t="str">
-        <v>rejected_guest_documents/4d01c983-85b2-40ea-a9c6-bacb7fdf03e4_school_id.jpg</v>
+        <v>rejected_guest_documents/f059ed3c-2886-4dbe-9299-796674ac4963_school_id.jpg</v>
       </c>
       <c r="V5" t="str">
-        <v>Saved (73.0 KB)</v>
+        <v>Saved (109.8 KB)</v>
       </c>
       <c r="W5" t="str">
-        <v>rejected_guest_documents/4d01c983-85b2-40ea-a9c6-bacb7fdf03e4_aadhar.jpg</v>
+        <v>rejected_guest_documents/f059ed3c-2886-4dbe-9299-796674ac4963_aadhar.jpg</v>
       </c>
       <c r="X5" t="str">
         <v>No</v>
       </c>
       <c r="Y5" t="str">
-        <v>2/10/2026, 5:16:24 pm</v>
+        <v>3/10/2026, 12:08:11 pm</v>
       </c>
       <c r="Z5" t="str">
-        <v>2/10/2026, 11:33:11 pm</v>
+        <v>3/10/2026, 12:18:38 pm</v>
       </c>
       <c r="AA5" t="str">
-        <v>6abf9990d9286e3efe7ea960</v>
+        <v>6ac0a2d35fa47f7f44580399</v>
       </c>
     </row>
     <row r="6">
@@ -848,25 +848,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>214120a6-f364-40ef-a547-187f5b17c476</v>
+        <v>f9a9dfa9-3ad5-4526-8d49-e3aa01debae3</v>
       </c>
       <c r="C6" t="str">
-        <v>Jatin Kumar</v>
+        <v>Nidhi</v>
       </c>
       <c r="D6" t="str">
-        <v>jk5255881@gmail.com</v>
+        <v>nidhibathla42@gmail.com</v>
       </c>
       <c r="E6" t="str">
-        <v>09053230018</v>
+        <v>+1918307970110</v>
       </c>
       <c r="F6" t="str">
-        <v>09053230018</v>
+        <v>+1918307970110</v>
       </c>
       <c r="G6" t="str">
-        <v>gyandeep senior secondary school</v>
+        <v>St marry convent school</v>
       </c>
       <c r="H6" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I6" t="str">
         <v>12th</v>
@@ -884,7 +884,7 @@
         <v>failed</v>
       </c>
       <c r="N6" t="str">
-        <v>NA</v>
+        <v>please share your proper documents.</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -899,31 +899,31 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>STUDENT_PASS_214120A6</v>
+        <v>STUDENT_PASS_F9A9DFA9</v>
       </c>
       <c r="T6" t="str">
-        <v>Saved (54.0 KB)</v>
+        <v>Saved (5.5 KB)</v>
       </c>
       <c r="U6" t="str">
-        <v>rejected_guest_documents/214120a6-f364-40ef-a547-187f5b17c476_school_id.jpg</v>
+        <v>rejected_guest_documents/f9a9dfa9-3ad5-4526-8d49-e3aa01debae3_school_id.jpg</v>
       </c>
       <c r="V6" t="str">
-        <v>Saved (75.4 KB)</v>
+        <v>Saved (43.3 KB)</v>
       </c>
       <c r="W6" t="str">
-        <v>rejected_guest_documents/214120a6-f364-40ef-a547-187f5b17c476_aadhar.jpg</v>
+        <v>rejected_guest_documents/f9a9dfa9-3ad5-4526-8d49-e3aa01debae3_aadhar.jpg</v>
       </c>
       <c r="X6" t="str">
         <v>No</v>
       </c>
       <c r="Y6" t="str">
-        <v>2/10/2026, 5:15:31 pm</v>
+        <v>3/10/2026, 12:07:54 pm</v>
       </c>
       <c r="Z6" t="str">
-        <v>2/10/2026, 11:24:44 pm</v>
+        <v>3/10/2026, 12:19:15 pm</v>
       </c>
       <c r="AA6" t="str">
-        <v>6abf995bd9286e3efe7ea95a</v>
+        <v>6ac0a2c25fa47f7f44580393</v>
       </c>
     </row>
     <row r="7">
@@ -931,25 +931,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>3abbade9-9c47-4913-b12b-5206c7e146ae</v>
+        <v>fc63adb8-e615-4449-b4ed-709c31e0742d</v>
       </c>
       <c r="C7" t="str">
-        <v>Aryan Rajput</v>
+        <v>Mohd Aasif</v>
       </c>
       <c r="D7" t="str">
-        <v>arynrjpt20@gmail.com</v>
+        <v>jattkhark@gmail.com</v>
       </c>
       <c r="E7" t="str">
-        <v>9817018353</v>
+        <v>8571895972</v>
       </c>
       <c r="F7" t="str">
-        <v>9817018353</v>
+        <v>8571895972</v>
       </c>
       <c r="G7" t="str">
-        <v>gyandeep senior secondary school</v>
+        <v>Govt.Model Sanskriti Sr. Sec. School Israna Panipat</v>
       </c>
       <c r="H7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I7" t="str">
         <v>12th</v>
@@ -982,31 +982,31 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>STUDENT_PASS_3ABBADE9</v>
+        <v>STUDENT_PASS_FC63ADB8</v>
       </c>
       <c r="T7" t="str">
-        <v>Saved (70.2 KB)</v>
+        <v>Saved (78.0 KB)</v>
       </c>
       <c r="U7" t="str">
-        <v>rejected_guest_documents/3abbade9-9c47-4913-b12b-5206c7e146ae_school_id.jpg</v>
+        <v>rejected_guest_documents/fc63adb8-e615-4449-b4ed-709c31e0742d_school_id.jpg</v>
       </c>
       <c r="V7" t="str">
-        <v>Saved (49.1 KB)</v>
+        <v>Saved (92.3 KB)</v>
       </c>
       <c r="W7" t="str">
-        <v>rejected_guest_documents/3abbade9-9c47-4913-b12b-5206c7e146ae_aadhar.jpg</v>
+        <v>rejected_guest_documents/fc63adb8-e615-4449-b4ed-709c31e0742d_aadhar.jpg</v>
       </c>
       <c r="X7" t="str">
         <v>No</v>
       </c>
       <c r="Y7" t="str">
-        <v>2/10/2026, 5:13:23 pm</v>
+        <v>3/10/2026, 12:03:29 pm</v>
       </c>
       <c r="Z7" t="str">
-        <v>2/10/2026, 11:22:33 pm</v>
+        <v>3/10/2026, 12:07:54 pm</v>
       </c>
       <c r="AA7" t="str">
-        <v>6abf98dbd9286e3efe7ea954</v>
+        <v>6ac0a1b95fa47f7f44580383</v>
       </c>
     </row>
     <row r="8">
@@ -1014,22 +1014,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>0810d170-a7a2-4d4b-8ab7-3ee5a1abfd86</v>
+        <v>0fe425ce-a32d-477a-b8d5-43500a273890</v>
       </c>
       <c r="C8" t="str">
-        <v>Aryan</v>
+        <v>Akash kumar</v>
       </c>
       <c r="D8" t="str">
-        <v>kumarvinod65012@gmail.com</v>
+        <v>aakashkumar258258@gmail.com</v>
       </c>
       <c r="E8" t="str">
-        <v>+91 7419104605</v>
+        <v>8816975214</v>
       </c>
       <c r="F8" t="str">
-        <v>+91 7419104605</v>
+        <v>8816975214</v>
       </c>
       <c r="G8" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Gsss krishnapura panipat</v>
       </c>
       <c r="H8" t="str">
         <v>Yes</v>
@@ -1065,31 +1065,31 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>STUDENT_PASS_0810D170</v>
+        <v>STUDENT_PASS_0FE425CE</v>
       </c>
       <c r="T8" t="str">
-        <v>Saved (191.9 KB)</v>
+        <v>Saved (134.6 KB)</v>
       </c>
       <c r="U8" t="str">
-        <v>rejected_guest_documents/0810d170-a7a2-4d4b-8ab7-3ee5a1abfd86_school_id.jpg</v>
+        <v>rejected_guest_documents/0fe425ce-a32d-477a-b8d5-43500a273890_school_id.jpg</v>
       </c>
       <c r="V8" t="str">
-        <v>Saved (156.2 KB)</v>
+        <v>Saved (87.8 KB)</v>
       </c>
       <c r="W8" t="str">
-        <v>rejected_guest_documents/0810d170-a7a2-4d4b-8ab7-3ee5a1abfd86_aadhar.jpg</v>
+        <v>rejected_guest_documents/0fe425ce-a32d-477a-b8d5-43500a273890_aadhar.jpg</v>
       </c>
       <c r="X8" t="str">
         <v>No</v>
       </c>
       <c r="Y8" t="str">
-        <v>2/10/2026, 4:57:51 pm</v>
+        <v>3/10/2026, 11:39:55 am</v>
       </c>
       <c r="Z8" t="str">
-        <v>2/10/2026, 11:18:31 pm</v>
+        <v>3/10/2026, 11:53:53 am</v>
       </c>
       <c r="AA8" t="str">
-        <v>6abf95375d71156a077d9e07</v>
+        <v>6ac09c335fa47f7f445802e7</v>
       </c>
     </row>
     <row r="9">
@@ -1097,28 +1097,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>19db7015-8fba-4f70-8afb-207e8f5bdc10</v>
+        <v>3c15c9f9-65be-446e-ab3c-6ce1099b6b3e</v>
       </c>
       <c r="C9" t="str">
-        <v>Nishu</v>
+        <v>Jatin Koli</v>
       </c>
       <c r="D9" t="str">
-        <v>gg1063178@gmail.com</v>
+        <v>jatinkoli1366@gmail.com</v>
       </c>
       <c r="E9" t="str">
-        <v>9996659025</v>
+        <v>+919991836995</v>
       </c>
       <c r="F9" t="str">
-        <v>9996659025</v>
+        <v>+919991836995</v>
       </c>
       <c r="G9" t="str">
-        <v>Government senior secondary School</v>
+        <v>Shree Mahabir Adarsh Sr. Sec. School</v>
       </c>
       <c r="H9" t="str">
         <v>Yes</v>
       </c>
       <c r="I9" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J9" t="str">
         <v>Haryana</v>
@@ -1148,31 +1148,31 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>STUDENT_PASS_19DB7015</v>
+        <v>STUDENT_PASS_3C15C9F9</v>
       </c>
       <c r="T9" t="str">
-        <v>Saved (164.5 KB)</v>
+        <v>Saved (223.3 KB)</v>
       </c>
       <c r="U9" t="str">
-        <v>rejected_guest_documents/19db7015-8fba-4f70-8afb-207e8f5bdc10_school_id.jpg</v>
+        <v>rejected_guest_documents/3c15c9f9-65be-446e-ab3c-6ce1099b6b3e_school_id.jpg</v>
       </c>
       <c r="V9" t="str">
-        <v>Saved (198.1 KB)</v>
+        <v>Saved (204.2 KB)</v>
       </c>
       <c r="W9" t="str">
-        <v>rejected_guest_documents/19db7015-8fba-4f70-8afb-207e8f5bdc10_aadhar.jpg</v>
+        <v>rejected_guest_documents/3c15c9f9-65be-446e-ab3c-6ce1099b6b3e_aadhar.jpg</v>
       </c>
       <c r="X9" t="str">
         <v>No</v>
       </c>
       <c r="Y9" t="str">
-        <v>2/10/2026, 4:54:00 pm</v>
+        <v>3/10/2026, 11:37:21 am</v>
       </c>
       <c r="Z9" t="str">
-        <v>2/10/2026, 11:15:54 pm</v>
+        <v>3/10/2026, 11:54:37 am</v>
       </c>
       <c r="AA9" t="str">
-        <v>6abf94505d71156a077d9e01</v>
+        <v>6ac09b995fa47f7f445802c3</v>
       </c>
     </row>
     <row r="10">
@@ -1180,22 +1180,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>1a15bf24-3192-4456-82d4-89e08d481382</v>
+        <v>b6ad6a87-5839-4e58-8ad6-34018ed27721</v>
       </c>
       <c r="C10" t="str">
-        <v>Vansh</v>
+        <v>Raushan Kumar</v>
       </c>
       <c r="D10" t="str">
-        <v>surajbrajesh0000@gmail.com</v>
+        <v>ragvenderyadav562@gmail.com</v>
       </c>
       <c r="E10" t="str">
-        <v>9812755516</v>
+        <v>8307844816</v>
       </c>
       <c r="F10" t="str">
-        <v>9812755516</v>
+        <v>8307844816</v>
       </c>
       <c r="G10" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Government Senior Secondary School Tehsil camp Panipat</v>
       </c>
       <c r="H10" t="str">
         <v>Yes</v>
@@ -1231,31 +1231,31 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>STUDENT_PASS_1A15BF24</v>
+        <v>STUDENT_PASS_B6AD6A87</v>
       </c>
       <c r="T10" t="str">
-        <v>Saved (178.4 KB)</v>
+        <v>Saved (133.3 KB)</v>
       </c>
       <c r="U10" t="str">
-        <v>rejected_guest_documents/1a15bf24-3192-4456-82d4-89e08d481382_school_id.jpg</v>
+        <v>rejected_guest_documents/b6ad6a87-5839-4e58-8ad6-34018ed27721_school_id.jpg</v>
       </c>
       <c r="V10" t="str">
-        <v>Saved (138.6 KB)</v>
+        <v>Saved (184.7 KB)</v>
       </c>
       <c r="W10" t="str">
-        <v>rejected_guest_documents/1a15bf24-3192-4456-82d4-89e08d481382_aadhar.jpg</v>
+        <v>rejected_guest_documents/b6ad6a87-5839-4e58-8ad6-34018ed27721_aadhar.jpg</v>
       </c>
       <c r="X10" t="str">
         <v>No</v>
       </c>
       <c r="Y10" t="str">
-        <v>2/10/2026, 4:50:30 pm</v>
+        <v>3/10/2026, 11:19:30 am</v>
       </c>
       <c r="Z10" t="str">
-        <v>2/10/2026, 11:15:34 pm</v>
+        <v>3/10/2026, 11:42:48 am</v>
       </c>
       <c r="AA10" t="str">
-        <v>6abf937e5d71156a077d9dfe</v>
+        <v>6ac0976ab279e4c6630e7eb6</v>
       </c>
     </row>
     <row r="11">
@@ -1263,37 +1263,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>0c28e8ce-e689-491c-83fc-d1a36721b955</v>
+        <v>ba4d89f9-0bd1-4b40-bb0a-65b0ec67646e</v>
       </c>
       <c r="C11" t="str">
-        <v>Varsha</v>
+        <v>MOHD AASIF</v>
       </c>
       <c r="D11" t="str">
-        <v>arjunchhoker2404@gmail.com</v>
+        <v>aivideosai25@gmail.com</v>
       </c>
       <c r="E11" t="str">
-        <v>8572868645</v>
+        <v>8571895972</v>
       </c>
       <c r="F11" t="str">
-        <v>8572868645</v>
+        <v>8571895972</v>
       </c>
       <c r="G11" t="str">
-        <v>CRM High School Chulkana Samalkha</v>
+        <v>Govt.Model Sanskriti Sr. Sec. School Israna Panipat</v>
       </c>
       <c r="H11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I11" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J11" t="str">
         <v>Haryana</v>
       </c>
       <c r="K11" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L11" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M11" t="str">
         <v>failed</v>
@@ -1314,31 +1314,31 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>STUDENT_PASS_0C28E8CE</v>
+        <v>STUDENT_PASS_BA4D89F9</v>
       </c>
       <c r="T11" t="str">
-        <v>Saved (131.7 KB)</v>
+        <v>Saved (94.5 KB)</v>
       </c>
       <c r="U11" t="str">
-        <v>rejected_guest_documents/0c28e8ce-e689-491c-83fc-d1a36721b955_school_id.jpg</v>
+        <v>rejected_guest_documents/ba4d89f9-0bd1-4b40-bb0a-65b0ec67646e_school_id.jpg</v>
       </c>
       <c r="V11" t="str">
-        <v>Saved (86.3 KB)</v>
+        <v>Saved (69.8 KB)</v>
       </c>
       <c r="W11" t="str">
-        <v>rejected_guest_documents/0c28e8ce-e689-491c-83fc-d1a36721b955_aadhar.jpg</v>
+        <v>rejected_guest_documents/ba4d89f9-0bd1-4b40-bb0a-65b0ec67646e_aadhar.jpg</v>
       </c>
       <c r="X11" t="str">
         <v>No</v>
       </c>
       <c r="Y11" t="str">
-        <v>2/10/2026, 4:43:43 pm</v>
+        <v>3/10/2026, 11:19:24 am</v>
       </c>
       <c r="Z11" t="str">
-        <v>2/10/2026, 11:14:17 pm</v>
+        <v>3/10/2026, 11:43:00 am</v>
       </c>
       <c r="AA11" t="str">
-        <v>6abf91e75d71156a077d9df8</v>
+        <v>6ac09764b279e4c6630e7eb3</v>
       </c>
     </row>
     <row r="12">
@@ -1346,22 +1346,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>41b04358-73c1-4077-a9da-4bf9693bc579</v>
+        <v>2041a966-f81f-4b8b-ab15-da9930120994</v>
       </c>
       <c r="C12" t="str">
-        <v>Niranjan kumar</v>
+        <v>Yuvi</v>
       </c>
       <c r="D12" t="str">
-        <v>itssurajss098@gmail.com</v>
+        <v>yuvidhingra792@gmail.com</v>
       </c>
       <c r="E12" t="str">
-        <v>+91 8930976875</v>
+        <v>7404713557</v>
       </c>
       <c r="F12" t="str">
-        <v>+91 8930976875</v>
+        <v>7404713557</v>
       </c>
       <c r="G12" t="str">
-        <v>Gsss krishanpura</v>
+        <v>DRM PUBLIC SCHOOL</v>
       </c>
       <c r="H12" t="str">
         <v>Yes</v>
@@ -1382,7 +1382,7 @@
         <v>failed</v>
       </c>
       <c r="N12" t="str">
-        <v>NA</v>
+        <v>please share your proper documents.</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1397,31 +1397,31 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>STUDENT_PASS_41B04358</v>
+        <v>STUDENT_PASS_2041A966</v>
       </c>
       <c r="T12" t="str">
-        <v>Saved (194.5 KB)</v>
+        <v>Saved (5.5 KB)</v>
       </c>
       <c r="U12" t="str">
-        <v>rejected_guest_documents/41b04358-73c1-4077-a9da-4bf9693bc579_school_id.jpg</v>
+        <v>rejected_guest_documents/2041a966-f81f-4b8b-ab15-da9930120994_school_id.jpg</v>
       </c>
       <c r="V12" t="str">
-        <v>Saved (51.5 KB)</v>
+        <v>Saved (89.9 KB)</v>
       </c>
       <c r="W12" t="str">
-        <v>rejected_guest_documents/41b04358-73c1-4077-a9da-4bf9693bc579_aadhar.jpg</v>
+        <v>rejected_guest_documents/2041a966-f81f-4b8b-ab15-da9930120994_aadhar.jpg</v>
       </c>
       <c r="X12" t="str">
         <v>No</v>
       </c>
       <c r="Y12" t="str">
-        <v>2/10/2026, 4:42:56 pm</v>
+        <v>3/10/2026, 11:17:40 am</v>
       </c>
       <c r="Z12" t="str">
-        <v>2/10/2026, 11:13:18 pm</v>
+        <v>3/10/2026, 11:44:07 am</v>
       </c>
       <c r="AA12" t="str">
-        <v>6abf91b85d71156a077d9df5</v>
+        <v>6ac096fcb279e4c6630e7ea0</v>
       </c>
     </row>
     <row r="13">
@@ -1429,22 +1429,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>e8bb8660-daec-4781-bf52-47115eca3bb5</v>
+        <v>fd731ca1-b274-44fc-9586-01d751023962</v>
       </c>
       <c r="C13" t="str">
-        <v>Aditya Sandhu</v>
+        <v>Aaditya</v>
       </c>
       <c r="D13" t="str">
-        <v>sandhuaditya141@gmail.c</v>
+        <v>kaditya27127@gmail.com</v>
       </c>
       <c r="E13" t="str">
-        <v>9996737929</v>
+        <v>9729179847</v>
       </c>
       <c r="F13" t="str">
-        <v>9996737929</v>
+        <v>9729179847</v>
       </c>
       <c r="G13" t="str">
-        <v>Dyal Singh Public School</v>
+        <v>Govt. Sr. Sec. School Tehsil Camp Panipat</v>
       </c>
       <c r="H13" t="str">
         <v>Yes</v>
@@ -1480,31 +1480,31 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>STUDENT_PASS_E8BB8660</v>
+        <v>STUDENT_PASS_FD731CA1</v>
       </c>
       <c r="T13" t="str">
-        <v>Saved (54.6 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U13" t="str">
-        <v>rejected_guest_documents/e8bb8660-daec-4781-bf52-47115eca3bb5_school_id.jpg</v>
+        <v>rejected_guest_documents/fd731ca1-b274-44fc-9586-01d751023962_school_id.jpg</v>
       </c>
       <c r="V13" t="str">
-        <v>Saved (151.3 KB)</v>
+        <v>Saved (54.8 KB)</v>
       </c>
       <c r="W13" t="str">
-        <v>rejected_guest_documents/e8bb8660-daec-4781-bf52-47115eca3bb5_aadhar.jpg</v>
+        <v>rejected_guest_documents/fd731ca1-b274-44fc-9586-01d751023962_aadhar.jpg</v>
       </c>
       <c r="X13" t="str">
         <v>No</v>
       </c>
       <c r="Y13" t="str">
-        <v>2/10/2026, 4:42:10 pm</v>
+        <v>3/10/2026, 11:17:31 am</v>
       </c>
       <c r="Z13" t="str">
-        <v>2/10/2026, 11:13:00 pm</v>
+        <v>3/10/2026, 11:43:41 am</v>
       </c>
       <c r="AA13" t="str">
-        <v>6abf918a5d71156a077d9df2</v>
+        <v>6ac096f3b279e4c6630e7e9d</v>
       </c>
     </row>
     <row r="14">
@@ -1512,43 +1512,43 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>144091db-698d-446f-b291-3893b801c389</v>
+        <v>31deac12-f27a-4f2b-9fdd-50c3a0b40294</v>
       </c>
       <c r="C14" t="str">
-        <v>Aarushi</v>
+        <v>Naitik Kumar</v>
       </c>
       <c r="D14" t="str">
-        <v>arjunchhoker2404@gmail.com</v>
+        <v>naitikkumar0910@gmail.com</v>
       </c>
       <c r="E14" t="str">
-        <v>8572868645</v>
+        <v>7015442699</v>
       </c>
       <c r="F14" t="str">
-        <v>8572868645</v>
+        <v>7015442699</v>
       </c>
       <c r="G14" t="str">
-        <v>CRM High School Chulkana Samalkha</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H14" t="str">
         <v>No</v>
       </c>
       <c r="I14" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J14" t="str">
         <v>Haryana</v>
       </c>
       <c r="K14" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L14" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M14" t="str">
         <v>failed</v>
       </c>
       <c r="N14" t="str">
-        <v>please upload your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1563,31 +1563,31 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>STUDENT_PASS_144091DB</v>
+        <v>STUDENT_PASS_31DEAC12</v>
       </c>
       <c r="T14" t="str">
-        <v>Saved (106.5 KB)</v>
+        <v>Saved (130.4 KB)</v>
       </c>
       <c r="U14" t="str">
-        <v>rejected_guest_documents/144091db-698d-446f-b291-3893b801c389_school_id.jpg</v>
+        <v>rejected_guest_documents/31deac12-f27a-4f2b-9fdd-50c3a0b40294_school_id.jpg</v>
       </c>
       <c r="V14" t="str">
-        <v>Saved (89.9 KB)</v>
+        <v>Saved (168.1 KB)</v>
       </c>
       <c r="W14" t="str">
-        <v>rejected_guest_documents/144091db-698d-446f-b291-3893b801c389_aadhar.jpg</v>
+        <v>rejected_guest_documents/31deac12-f27a-4f2b-9fdd-50c3a0b40294_aadhar.jpg</v>
       </c>
       <c r="X14" t="str">
         <v>No</v>
       </c>
       <c r="Y14" t="str">
-        <v>2/10/2026, 4:27:37 pm</v>
+        <v>3/10/2026, 11:16:01 am</v>
       </c>
       <c r="Z14" t="str">
-        <v>2/10/2026, 11:07:43 pm</v>
+        <v>3/10/2026, 11:44:39 am</v>
       </c>
       <c r="AA14" t="str">
-        <v>6abf8e215d71156a077d9de2</v>
+        <v>6ac09699b279e4c6630e7e87</v>
       </c>
     </row>
     <row r="15">
@@ -1595,25 +1595,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>dff7b7ed-13b1-4483-aead-482002a00e7e</v>
+        <v>e220d079-8af6-4256-a2f9-55a6a94e1275</v>
       </c>
       <c r="C15" t="str">
-        <v>Dev Sharma</v>
+        <v>Rahul</v>
       </c>
       <c r="D15" t="str">
-        <v>dspandit0896@gmail.com</v>
+        <v>shabsaini890@gmail.com</v>
       </c>
       <c r="E15" t="str">
-        <v>9996747322</v>
+        <v>9518123986</v>
       </c>
       <c r="F15" t="str">
-        <v>9996747322</v>
+        <v>9518123986</v>
       </c>
       <c r="G15" t="str">
-        <v>gyandeep senior secondary school</v>
+        <v>Sd Vidya Mandir</v>
       </c>
       <c r="H15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I15" t="str">
         <v>12th</v>
@@ -1631,7 +1631,7 @@
         <v>failed</v>
       </c>
       <c r="N15" t="str">
-        <v>NA</v>
+        <v>please check your name.</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1646,31 +1646,31 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>STUDENT_PASS_DFF7B7ED</v>
+        <v>STUDENT_PASS_E220D079</v>
       </c>
       <c r="T15" t="str">
-        <v>Saved (68.1 KB)</v>
+        <v>Saved (279.7 KB)</v>
       </c>
       <c r="U15" t="str">
-        <v>rejected_guest_documents/dff7b7ed-13b1-4483-aead-482002a00e7e_school_id.jpg</v>
+        <v>rejected_guest_documents/e220d079-8af6-4256-a2f9-55a6a94e1275_school_id.jpg</v>
       </c>
       <c r="V15" t="str">
-        <v>Saved (54.7 KB)</v>
+        <v>Saved (129.5 KB)</v>
       </c>
       <c r="W15" t="str">
-        <v>rejected_guest_documents/dff7b7ed-13b1-4483-aead-482002a00e7e_aadhar.jpg</v>
+        <v>rejected_guest_documents/e220d079-8af6-4256-a2f9-55a6a94e1275_aadhar.jpg</v>
       </c>
       <c r="X15" t="str">
         <v>No</v>
       </c>
       <c r="Y15" t="str">
-        <v>2/10/2026, 4:26:48 pm</v>
+        <v>3/10/2026, 11:13:00 am</v>
       </c>
       <c r="Z15" t="str">
-        <v>2/10/2026, 11:07:00 pm</v>
+        <v>3/10/2026, 11:45:01 am</v>
       </c>
       <c r="AA15" t="str">
-        <v>6abf8df05d71156a077d9ddf</v>
+        <v>6ac095e4b279e4c6630e7e66</v>
       </c>
     </row>
     <row r="16">
@@ -1678,37 +1678,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>47954e6b-1b49-4c45-b6cd-2396b9ff2c51</v>
+        <v>8ffd1531-8ca8-4747-a9a2-c03dfe696fa5</v>
       </c>
       <c r="C16" t="str">
-        <v>Aarushi</v>
+        <v>Ajay</v>
       </c>
       <c r="D16" t="str">
-        <v>chhokeraarusi@gmail.com</v>
+        <v>ajay.sh.5357@gmail.com</v>
       </c>
       <c r="E16" t="str">
-        <v>8708388011</v>
+        <v>7404365357</v>
       </c>
       <c r="F16" t="str">
-        <v>8708388011</v>
+        <v>7404365357</v>
       </c>
       <c r="G16" t="str">
-        <v>HINDU SR. SEC. SCHOOL</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I16" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J16" t="str">
         <v>Haryana</v>
       </c>
       <c r="K16" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L16" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M16" t="str">
         <v>failed</v>
@@ -1729,31 +1729,31 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>STUDENT_PASS_47954E6B</v>
+        <v>STUDENT_PASS_8FFD1531</v>
       </c>
       <c r="T16" t="str">
-        <v>Saved (125.6 KB)</v>
+        <v>Saved (102.7 KB)</v>
       </c>
       <c r="U16" t="str">
-        <v>rejected_guest_documents/47954e6b-1b49-4c45-b6cd-2396b9ff2c51_school_id.jpg</v>
+        <v>rejected_guest_documents/8ffd1531-8ca8-4747-a9a2-c03dfe696fa5_school_id.jpg</v>
       </c>
       <c r="V16" t="str">
-        <v>Saved (102.6 KB)</v>
+        <v>Saved (36.4 KB)</v>
       </c>
       <c r="W16" t="str">
-        <v>rejected_guest_documents/47954e6b-1b49-4c45-b6cd-2396b9ff2c51_aadhar.jpg</v>
+        <v>rejected_guest_documents/8ffd1531-8ca8-4747-a9a2-c03dfe696fa5_aadhar.jpg</v>
       </c>
       <c r="X16" t="str">
         <v>No</v>
       </c>
       <c r="Y16" t="str">
-        <v>2/10/2026, 4:18:52 pm</v>
+        <v>3/10/2026, 11:00:23 am</v>
       </c>
       <c r="Z16" t="str">
-        <v>2/10/2026, 11:04:17 pm</v>
+        <v>3/10/2026, 11:13:07 am</v>
       </c>
       <c r="AA16" t="str">
-        <v>6abf8c145d71156a077d9dd5</v>
+        <v>6ac092efb279e4c6630e7e21</v>
       </c>
     </row>
     <row r="17">
@@ -1761,28 +1761,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>1ac101b8-39b2-4e5f-b6e6-20347f3d7a9c</v>
+        <v>0e931e1a-2d90-41ba-945f-22129fb69461</v>
       </c>
       <c r="C17" t="str">
-        <v>Akash kumar</v>
+        <v>Anuj</v>
       </c>
       <c r="D17" t="str">
-        <v>panuj2869@gmail.com</v>
+        <v>anujsainiak2007@gmail.com</v>
       </c>
       <c r="E17" t="str">
-        <v>8816975214</v>
+        <v>7206122068</v>
       </c>
       <c r="F17" t="str">
-        <v>8816975214</v>
+        <v>7206122068</v>
       </c>
       <c r="G17" t="str">
-        <v>Gsss krishnapura panipat</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I17" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J17" t="str">
         <v>Haryana</v>
@@ -1812,31 +1812,31 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>STUDENT_PASS_1AC101B8</v>
+        <v>STUDENT_PASS_0E931E1A</v>
       </c>
       <c r="T17" t="str">
-        <v>Saved (134.6 KB)</v>
+        <v>Saved (69.6 KB)</v>
       </c>
       <c r="U17" t="str">
-        <v>rejected_guest_documents/1ac101b8-39b2-4e5f-b6e6-20347f3d7a9c_school_id.jpg</v>
+        <v>rejected_guest_documents/0e931e1a-2d90-41ba-945f-22129fb69461_school_id.jpg</v>
       </c>
       <c r="V17" t="str">
-        <v>Saved (73.4 KB)</v>
+        <v>Saved (149.2 KB)</v>
       </c>
       <c r="W17" t="str">
-        <v>rejected_guest_documents/1ac101b8-39b2-4e5f-b6e6-20347f3d7a9c_aadhar.jpg</v>
+        <v>rejected_guest_documents/0e931e1a-2d90-41ba-945f-22129fb69461_aadhar.jpg</v>
       </c>
       <c r="X17" t="str">
         <v>No</v>
       </c>
       <c r="Y17" t="str">
-        <v>2/10/2026, 4:12:43 pm</v>
+        <v>3/10/2026, 10:55:36 am</v>
       </c>
       <c r="Z17" t="str">
-        <v>2/10/2026, 11:03:04 pm</v>
+        <v>3/10/2026, 11:13:53 am</v>
       </c>
       <c r="AA17" t="str">
-        <v>6abf8aa35d71156a077d9dcf</v>
+        <v>6ac091d0b279e4c6630e7e1b</v>
       </c>
     </row>
     <row r="18">
@@ -1844,22 +1844,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>e0b8eff8-7eb9-4182-89a8-fb4aa1991a75</v>
+        <v>4beaf8b1-2627-46aa-9e41-001d18ee1802</v>
       </c>
       <c r="C18" t="str">
-        <v>Aryan</v>
+        <v>MOHD AASIF</v>
       </c>
       <c r="D18" t="str">
-        <v>kumarvinod65012@gmail.com</v>
+        <v>jattkhark@gmail.com</v>
       </c>
       <c r="E18" t="str">
-        <v>+91 7419104605</v>
+        <v>8571895972</v>
       </c>
       <c r="F18" t="str">
-        <v>+91 7419104605</v>
+        <v>8571895972</v>
       </c>
       <c r="G18" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Govt.Model Sanskriti Sr. Sec. School Israna</v>
       </c>
       <c r="H18" t="str">
         <v>Yes</v>
@@ -1895,31 +1895,31 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>STUDENT_PASS_E0B8EFF8</v>
+        <v>STUDENT_PASS_4BEAF8B1</v>
       </c>
       <c r="T18" t="str">
-        <v>Saved (193.1 KB)</v>
+        <v>Saved (76.2 KB)</v>
       </c>
       <c r="U18" t="str">
-        <v>rejected_guest_documents/e0b8eff8-7eb9-4182-89a8-fb4aa1991a75_school_id.jpg</v>
+        <v>rejected_guest_documents/4beaf8b1-2627-46aa-9e41-001d18ee1802_school_id.jpg</v>
       </c>
       <c r="V18" t="str">
-        <v>Saved (156.2 KB)</v>
+        <v>Saved (125.9 KB)</v>
       </c>
       <c r="W18" t="str">
-        <v>rejected_guest_documents/e0b8eff8-7eb9-4182-89a8-fb4aa1991a75_aadhar.jpg</v>
+        <v>rejected_guest_documents/4beaf8b1-2627-46aa-9e41-001d18ee1802_aadhar.jpg</v>
       </c>
       <c r="X18" t="str">
         <v>No</v>
       </c>
       <c r="Y18" t="str">
-        <v>2/10/2026, 3:58:10 pm</v>
+        <v>3/10/2026, 10:55:02 am</v>
       </c>
       <c r="Z18" t="str">
-        <v>2/10/2026, 11:02:25 pm</v>
+        <v>3/10/2026, 11:14:20 am</v>
       </c>
       <c r="AA18" t="str">
-        <v>6abf873a5d71156a077d9dc1</v>
+        <v>6ac091aeb279e4c6630e7e18</v>
       </c>
     </row>
     <row r="19">
@@ -1927,37 +1927,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>03eedd1a-61c8-48b1-ab6b-c7eaa17ad37e</v>
+        <v>a0183d89-8b20-466c-bc03-a05903fe361e</v>
       </c>
       <c r="C19" t="str">
-        <v>Aarushi</v>
+        <v>Nidhi</v>
       </c>
       <c r="D19" t="str">
-        <v>chhokeraarusi@gemail.com</v>
+        <v>nidhibathla42@gmail.com</v>
       </c>
       <c r="E19" t="str">
-        <v>8708388011</v>
+        <v>8307970110</v>
       </c>
       <c r="F19" t="str">
-        <v>8708388011</v>
+        <v>8307970110</v>
       </c>
       <c r="G19" t="str">
-        <v>HINDU SR. SEC. SCHOOL</v>
+        <v>St marrys convent school</v>
       </c>
       <c r="H19" t="str">
         <v>Yes</v>
       </c>
       <c r="I19" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J19" t="str">
         <v>Haryana</v>
       </c>
       <c r="K19" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L19" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M19" t="str">
         <v>failed</v>
@@ -1978,31 +1978,31 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>STUDENT_PASS_03EEDD1A</v>
+        <v>STUDENT_PASS_A0183D89</v>
       </c>
       <c r="T19" t="str">
-        <v>Saved (125.5 KB)</v>
+        <v>Saved (3.1 KB)</v>
       </c>
       <c r="U19" t="str">
-        <v>rejected_guest_documents/03eedd1a-61c8-48b1-ab6b-c7eaa17ad37e_school_id.jpg</v>
+        <v>rejected_guest_documents/a0183d89-8b20-466c-bc03-a05903fe361e_school_id.jpg</v>
       </c>
       <c r="V19" t="str">
-        <v>Saved (102.6 KB)</v>
+        <v>Saved (40.9 KB)</v>
       </c>
       <c r="W19" t="str">
-        <v>rejected_guest_documents/03eedd1a-61c8-48b1-ab6b-c7eaa17ad37e_aadhar.jpg</v>
+        <v>rejected_guest_documents/a0183d89-8b20-466c-bc03-a05903fe361e_aadhar.jpg</v>
       </c>
       <c r="X19" t="str">
         <v>No</v>
       </c>
       <c r="Y19" t="str">
-        <v>2/10/2026, 3:57:54 pm</v>
+        <v>3/10/2026, 10:50:18 am</v>
       </c>
       <c r="Z19" t="str">
-        <v>2/10/2026, 11:01:39 pm</v>
+        <v>3/10/2026, 11:45:22 am</v>
       </c>
       <c r="AA19" t="str">
-        <v>6abf872a5d71156a077d9dbb</v>
+        <v>6ac09092b279e4c6630e7e0c</v>
       </c>
     </row>
     <row r="20">
@@ -2010,37 +2010,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>1feec50c-e66b-453c-9725-08f4ce1bcf87</v>
+        <v>fabd5f64-2ec9-42cc-a2d0-b1cca21d8787</v>
       </c>
       <c r="C20" t="str">
-        <v>Aarushi</v>
+        <v>Aaditya</v>
       </c>
       <c r="D20" t="str">
-        <v>chhokeraarusi@gemail.com</v>
+        <v>factboyrk01@gmail.com</v>
       </c>
       <c r="E20" t="str">
-        <v>8708388011</v>
+        <v>9729179847</v>
       </c>
       <c r="F20" t="str">
-        <v>8708388011</v>
+        <v>9729179847</v>
       </c>
       <c r="G20" t="str">
-        <v>HINDU SR. SEC. SCHOOL</v>
+        <v>Govt. Sr. Sec. School Tehsil camp Panipat</v>
       </c>
       <c r="H20" t="str">
         <v>Yes</v>
       </c>
       <c r="I20" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J20" t="str">
         <v>Haryana</v>
       </c>
       <c r="K20" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L20" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M20" t="str">
         <v>failed</v>
@@ -2061,31 +2061,31 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>STUDENT_PASS_1FEEC50C</v>
+        <v>STUDENT_PASS_FABD5F64</v>
       </c>
       <c r="T20" t="str">
-        <v>Saved (125.6 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U20" t="str">
-        <v>rejected_guest_documents/1feec50c-e66b-453c-9725-08f4ce1bcf87_school_id.jpg</v>
+        <v>rejected_guest_documents/fabd5f64-2ec9-42cc-a2d0-b1cca21d8787_school_id.jpg</v>
       </c>
       <c r="V20" t="str">
-        <v>Saved (102.6 KB)</v>
+        <v>Saved (54.8 KB)</v>
       </c>
       <c r="W20" t="str">
-        <v>rejected_guest_documents/1feec50c-e66b-453c-9725-08f4ce1bcf87_aadhar.jpg</v>
+        <v>rejected_guest_documents/fabd5f64-2ec9-42cc-a2d0-b1cca21d8787_aadhar.jpg</v>
       </c>
       <c r="X20" t="str">
         <v>No</v>
       </c>
       <c r="Y20" t="str">
-        <v>2/10/2026, 3:54:12 pm</v>
+        <v>3/10/2026, 10:40:52 am</v>
       </c>
       <c r="Z20" t="str">
-        <v>2/10/2026, 11:01:14 pm</v>
+        <v>3/10/2026, 10:46:14 am</v>
       </c>
       <c r="AA20" t="str">
-        <v>6abf864c5d71156a077d9db8</v>
+        <v>6ac08e5cb279e4c6630e7deb</v>
       </c>
     </row>
     <row r="21">
@@ -2093,22 +2093,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>08d350cf-2de4-467b-b97e-c7d380e07110</v>
+        <v>d716bb26-7150-4209-b9ce-4d0755cc0af9</v>
       </c>
       <c r="C21" t="str">
-        <v>Akash kumar</v>
+        <v>Mohd Aasif</v>
       </c>
       <c r="D21" t="str">
-        <v>aakashkumar258258@gmail.com</v>
+        <v>jattkhark@gmail.com</v>
       </c>
       <c r="E21" t="str">
-        <v>8816975214</v>
+        <v>8571895972</v>
       </c>
       <c r="F21" t="str">
-        <v>8816975214</v>
+        <v>8571895972</v>
       </c>
       <c r="G21" t="str">
-        <v>Gsss krishnapura panipat</v>
+        <v>Govt.Model Sanskriti Sr. Sec. School Israna,Panipat</v>
       </c>
       <c r="H21" t="str">
         <v>Yes</v>
@@ -2144,31 +2144,31 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>STUDENT_PASS_08D350CF</v>
+        <v>STUDENT_PASS_D716BB26</v>
       </c>
       <c r="T21" t="str">
-        <v>Saved (117.6 KB)</v>
+        <v>Saved (76.2 KB)</v>
       </c>
       <c r="U21" t="str">
-        <v>rejected_guest_documents/08d350cf-2de4-467b-b97e-c7d380e07110_school_id.jpg</v>
+        <v>rejected_guest_documents/d716bb26-7150-4209-b9ce-4d0755cc0af9_school_id.jpg</v>
       </c>
       <c r="V21" t="str">
-        <v>Saved (73.4 KB)</v>
+        <v>Saved (142.0 KB)</v>
       </c>
       <c r="W21" t="str">
-        <v>rejected_guest_documents/08d350cf-2de4-467b-b97e-c7d380e07110_aadhar.jpg</v>
+        <v>rejected_guest_documents/d716bb26-7150-4209-b9ce-4d0755cc0af9_aadhar.jpg</v>
       </c>
       <c r="X21" t="str">
         <v>No</v>
       </c>
       <c r="Y21" t="str">
-        <v>2/10/2026, 3:52:26 pm</v>
+        <v>3/10/2026, 10:38:39 am</v>
       </c>
       <c r="Z21" t="str">
-        <v>2/10/2026, 11:00:06 pm</v>
+        <v>3/10/2026, 10:46:58 am</v>
       </c>
       <c r="AA21" t="str">
-        <v>6abf85e25d71156a077d9db5</v>
+        <v>6ac08dd7b279e4c6630e7de5</v>
       </c>
     </row>
     <row r="22">
@@ -2176,25 +2176,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>930d8d24-5b29-46fe-ad78-463a201890f3</v>
+        <v>7a36e9e0-3c49-4399-93e7-764f1e38d30b</v>
       </c>
       <c r="C22" t="str">
-        <v>Vikas</v>
+        <v>Raushan Kumar</v>
       </c>
       <c r="D22" t="str">
-        <v>vikaskumar9187310@gmail.com</v>
+        <v>rai00199777@gmail.com</v>
       </c>
       <c r="E22" t="str">
-        <v>9034413646</v>
+        <v>9817681824</v>
       </c>
       <c r="F22" t="str">
-        <v>9034413646</v>
+        <v>9817681824</v>
       </c>
       <c r="G22" t="str">
-        <v>Arya Sr Sec School Panipat</v>
+        <v>Govt. Sr.  Sec. School Tehsil Camp Panipat</v>
       </c>
       <c r="H22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I22" t="str">
         <v>12th</v>
@@ -2227,31 +2227,31 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>STUDENT_PASS_930D8D24</v>
+        <v>STUDENT_PASS_7A36E9E0</v>
       </c>
       <c r="T22" t="str">
-        <v>Saved (55.5 KB)</v>
+        <v>Saved (106.3 KB)</v>
       </c>
       <c r="U22" t="str">
-        <v>rejected_guest_documents/930d8d24-5b29-46fe-ad78-463a201890f3_school_id.jpg</v>
+        <v>rejected_guest_documents/7a36e9e0-3c49-4399-93e7-764f1e38d30b_school_id.jpg</v>
       </c>
       <c r="V22" t="str">
-        <v>Saved (163.7 KB)</v>
+        <v>Saved (100.9 KB)</v>
       </c>
       <c r="W22" t="str">
-        <v>rejected_guest_documents/930d8d24-5b29-46fe-ad78-463a201890f3_aadhar.jpg</v>
+        <v>rejected_guest_documents/7a36e9e0-3c49-4399-93e7-764f1e38d30b_aadhar.jpg</v>
       </c>
       <c r="X22" t="str">
         <v>No</v>
       </c>
       <c r="Y22" t="str">
-        <v>2/10/2026, 3:47:42 pm</v>
+        <v>3/10/2026, 10:36:12 am</v>
       </c>
       <c r="Z22" t="str">
-        <v>2/10/2026, 10:59:41 pm</v>
+        <v>3/10/2026, 11:55:37 am</v>
       </c>
       <c r="AA22" t="str">
-        <v>6abf84c65d71156a077d9dad</v>
+        <v>6ac08d44b279e4c6630e7dd9</v>
       </c>
     </row>
     <row r="23">
@@ -2259,43 +2259,43 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>e1a14039-8377-44d0-87a7-ee7c724ac4f7</v>
+        <v>653f27f0-d16a-4283-96ad-bc1c6cb780f0</v>
       </c>
       <c r="C23" t="str">
-        <v>Varsha</v>
+        <v>Rujal</v>
       </c>
       <c r="D23" t="str">
-        <v>arjunchhoker2404@gmail.com</v>
+        <v>rujalkundu007@gmail.com</v>
       </c>
       <c r="E23" t="str">
-        <v>8572868645</v>
+        <v>9671333710</v>
       </c>
       <c r="F23" t="str">
-        <v>8572868645</v>
+        <v>9671333710</v>
       </c>
       <c r="G23" t="str">
-        <v>CRM High School Chulkana Samalkha</v>
+        <v>Arya Sr Sec School Panipat</v>
       </c>
       <c r="H23" t="str">
         <v>No</v>
       </c>
       <c r="I23" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J23" t="str">
         <v>Haryana</v>
       </c>
       <c r="K23" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L23" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M23" t="str">
         <v>failed</v>
       </c>
       <c r="N23" t="str">
-        <v>please check your school name.</v>
+        <v>only passes for 11 and 12 class students.</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -2310,31 +2310,31 @@
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>STUDENT_PASS_E1A14039</v>
+        <v>STUDENT_PASS_653F27F0</v>
       </c>
       <c r="T23" t="str">
-        <v>Saved (131.7 KB)</v>
+        <v>Saved (365.8 KB)</v>
       </c>
       <c r="U23" t="str">
-        <v>rejected_guest_documents/e1a14039-8377-44d0-87a7-ee7c724ac4f7_school_id.jpg</v>
+        <v>rejected_guest_documents/653f27f0-d16a-4283-96ad-bc1c6cb780f0_school_id.jpg</v>
       </c>
       <c r="V23" t="str">
-        <v>Saved (90.5 KB)</v>
+        <v>Saved (295.2 KB)</v>
       </c>
       <c r="W23" t="str">
-        <v>rejected_guest_documents/e1a14039-8377-44d0-87a7-ee7c724ac4f7_aadhar.jpg</v>
+        <v>rejected_guest_documents/653f27f0-d16a-4283-96ad-bc1c6cb780f0_aadhar.jpg</v>
       </c>
       <c r="X23" t="str">
         <v>No</v>
       </c>
       <c r="Y23" t="str">
-        <v>2/10/2026, 3:34:45 pm</v>
+        <v>3/10/2026, 10:27:29 am</v>
       </c>
       <c r="Z23" t="str">
-        <v>2/10/2026, 3:38:12 pm</v>
+        <v>3/10/2026, 11:57:34 am</v>
       </c>
       <c r="AA23" t="str">
-        <v>6abf81bd5d71156a077d9d30</v>
+        <v>6ac08b39b279e4c6630e7db8</v>
       </c>
     </row>
     <row r="24">
@@ -2342,22 +2342,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>2e1aad8c-9175-4b0a-b092-7d49a9facd7c</v>
+        <v>c3a25e8f-93ec-40f3-9db4-d16b5b1b9b83</v>
       </c>
       <c r="C24" t="str">
-        <v>DHRUV PANWAR</v>
+        <v>Rujal</v>
       </c>
       <c r="D24" t="str">
-        <v>djpanwar90@gmail.com</v>
+        <v>rujalkundu007@gmail.com</v>
       </c>
       <c r="E24" t="str">
-        <v>8930132852</v>
+        <v>9671333710</v>
       </c>
       <c r="F24" t="str">
-        <v>8930132852</v>
+        <v>9671333710</v>
       </c>
       <c r="G24" t="str">
-        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
+        <v>Arya Sr Sec School Panipat</v>
       </c>
       <c r="H24" t="str">
         <v>No</v>
@@ -2393,31 +2393,31 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>STUDENT_PASS_2E1AAD8C</v>
+        <v>STUDENT_PASS_C3A25E8F</v>
       </c>
       <c r="T24" t="str">
-        <v>Saved (80.5 KB)</v>
+        <v>Saved (365.8 KB)</v>
       </c>
       <c r="U24" t="str">
-        <v>rejected_guest_documents/2e1aad8c-9175-4b0a-b092-7d49a9facd7c_school_id.jpg</v>
+        <v>rejected_guest_documents/c3a25e8f-93ec-40f3-9db4-d16b5b1b9b83_school_id.jpg</v>
       </c>
       <c r="V24" t="str">
-        <v>Saved (114.4 KB)</v>
+        <v>Saved (295.2 KB)</v>
       </c>
       <c r="W24" t="str">
-        <v>rejected_guest_documents/2e1aad8c-9175-4b0a-b092-7d49a9facd7c_aadhar.jpg</v>
+        <v>rejected_guest_documents/c3a25e8f-93ec-40f3-9db4-d16b5b1b9b83_aadhar.jpg</v>
       </c>
       <c r="X24" t="str">
         <v>No</v>
       </c>
       <c r="Y24" t="str">
-        <v>2/10/2026, 3:29:00 pm</v>
+        <v>3/10/2026, 10:27:10 am</v>
       </c>
       <c r="Z24" t="str">
-        <v>2/10/2026, 3:38:30 pm</v>
+        <v>3/10/2026, 11:58:15 am</v>
       </c>
       <c r="AA24" t="str">
-        <v>6abf80645d71156a077d9d1c</v>
+        <v>6ac08b26b279e4c6630e7db2</v>
       </c>
     </row>
     <row r="25">
@@ -2425,25 +2425,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>2a02f0b3-aeb8-4911-bdcb-103af650ca5c</v>
+        <v>f6347bdd-470c-4865-a448-7fa2c0c3d755</v>
       </c>
       <c r="C25" t="str">
-        <v>yashita Dua</v>
+        <v>Aaditya</v>
       </c>
       <c r="D25" t="str">
-        <v>duayashita10001@gmail.com</v>
+        <v>kaditya27127@gmail.com</v>
       </c>
       <c r="E25" t="str">
-        <v>9466565447</v>
+        <v>9729179847</v>
       </c>
       <c r="F25" t="str">
-        <v>9466565447</v>
+        <v>9729179847</v>
       </c>
       <c r="G25" t="str">
-        <v>Delhi Public School Karnal</v>
+        <v>Government Senior secondary school tehsil camp</v>
       </c>
       <c r="H25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I25" t="str">
         <v>12th</v>
@@ -2452,16 +2452,16 @@
         <v>Haryana</v>
       </c>
       <c r="K25" t="str">
-        <v>Karnal</v>
+        <v>Panipat</v>
       </c>
       <c r="L25" t="str">
-        <v>Karnal, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M25" t="str">
         <v>failed</v>
       </c>
       <c r="N25" t="str">
-        <v>please share your ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2476,31 +2476,31 @@
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>STUDENT_PASS_2A02F0B3</v>
+        <v>STUDENT_PASS_F6347BDD</v>
       </c>
       <c r="T25" t="str">
-        <v>Saved (368.8 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U25" t="str">
-        <v>rejected_guest_documents/2a02f0b3-aeb8-4911-bdcb-103af650ca5c_school_id.jpg</v>
+        <v>rejected_guest_documents/f6347bdd-470c-4865-a448-7fa2c0c3d755_school_id.jpg</v>
       </c>
       <c r="V25" t="str">
-        <v>Saved (174.9 KB)</v>
+        <v>Saved (55.4 KB)</v>
       </c>
       <c r="W25" t="str">
-        <v>rejected_guest_documents/2a02f0b3-aeb8-4911-bdcb-103af650ca5c_aadhar.jpg</v>
+        <v>rejected_guest_documents/f6347bdd-470c-4865-a448-7fa2c0c3d755_aadhar.jpg</v>
       </c>
       <c r="X25" t="str">
         <v>No</v>
       </c>
       <c r="Y25" t="str">
-        <v>2/10/2026, 3:13:44 pm</v>
+        <v>3/10/2026, 10:18:39 am</v>
       </c>
       <c r="Z25" t="str">
-        <v>2/10/2026, 3:39:35 pm</v>
+        <v>3/10/2026, 11:57:55 am</v>
       </c>
       <c r="AA25" t="str">
-        <v>6abf7cd05d71156a077d9ce5</v>
+        <v>6ac08927b279e4c6630e7d70</v>
       </c>
     </row>
     <row r="26">
@@ -2508,28 +2508,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>807587b1-e1c5-470b-82e8-52c9b0dc3f25</v>
+        <v>823122ef-020c-4479-9674-4de120027b2f</v>
       </c>
       <c r="C26" t="str">
-        <v>Sameer Ansari</v>
+        <v>Rujal</v>
       </c>
       <c r="D26" t="str">
-        <v>ng442523@gmail.com</v>
+        <v>rujalkundu007@gmail.com</v>
       </c>
       <c r="E26" t="str">
-        <v>8683928672</v>
+        <v>9671333710</v>
       </c>
       <c r="F26" t="str">
-        <v>8683928672</v>
+        <v>9671333710</v>
       </c>
       <c r="G26" t="str">
-        <v>Govt. High School</v>
+        <v>Dev huda panipat</v>
       </c>
       <c r="H26" t="str">
         <v>Yes</v>
       </c>
       <c r="I26" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J26" t="str">
         <v>Haryana</v>
@@ -2559,31 +2559,31 @@
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>STUDENT_PASS_807587B1</v>
+        <v>STUDENT_PASS_823122EF</v>
       </c>
       <c r="T26" t="str">
-        <v>Saved (89.8 KB)</v>
+        <v>Saved (365.8 KB)</v>
       </c>
       <c r="U26" t="str">
-        <v>rejected_guest_documents/807587b1-e1c5-470b-82e8-52c9b0dc3f25_school_id.jpg</v>
+        <v>rejected_guest_documents/823122ef-020c-4479-9674-4de120027b2f_school_id.jpg</v>
       </c>
       <c r="V26" t="str">
-        <v>Saved (61.9 KB)</v>
+        <v>Saved (295.2 KB)</v>
       </c>
       <c r="W26" t="str">
-        <v>rejected_guest_documents/807587b1-e1c5-470b-82e8-52c9b0dc3f25_aadhar.jpg</v>
+        <v>rejected_guest_documents/823122ef-020c-4479-9674-4de120027b2f_aadhar.jpg</v>
       </c>
       <c r="X26" t="str">
         <v>No</v>
       </c>
       <c r="Y26" t="str">
-        <v>2/10/2026, 2:47:46 pm</v>
+        <v>3/10/2026, 10:15:25 am</v>
       </c>
       <c r="Z26" t="str">
-        <v>2/10/2026, 3:40:18 pm</v>
+        <v>3/10/2026, 11:59:10 am</v>
       </c>
       <c r="AA26" t="str">
-        <v>6abf76baaa4a1b4283ae7518</v>
+        <v>6ac08865b279e4c6630e7d5d</v>
       </c>
     </row>
     <row r="27">
@@ -2591,25 +2591,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>d73d6bbc-521f-4c2f-8c3d-1f46032a5b6a</v>
+        <v>cda7f5d4-c93e-4b83-937f-319994460534</v>
       </c>
       <c r="C27" t="str">
-        <v>Rahul Sharma</v>
+        <v>RAUSHAN KUMAR</v>
       </c>
       <c r="D27" t="str">
-        <v>instagramb4n@gmail.com</v>
+        <v>rk2394533@gmail.com</v>
       </c>
       <c r="E27" t="str">
-        <v>+91 99967 11289</v>
+        <v>8307844816</v>
       </c>
       <c r="F27" t="str">
-        <v>+91 99967 11289</v>
+        <v>8307844816</v>
       </c>
       <c r="G27" t="str">
-        <v>Halwasiya Vidya Vihar Sr Sec School Bhiwani</v>
+        <v>GOVERNMENT SENIOR SECONDARY SCHOOL TEHSIL CAMP"PANIPAT"</v>
       </c>
       <c r="H27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I27" t="str">
         <v>12th</v>
@@ -2618,10 +2618,10 @@
         <v>Haryana</v>
       </c>
       <c r="K27" t="str">
-        <v>Bhiwani</v>
+        <v>Panipat</v>
       </c>
       <c r="L27" t="str">
-        <v>Bhiwani, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M27" t="str">
         <v>failed</v>
@@ -2642,31 +2642,31 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>STUDENT_PASS_D73D6BBC</v>
+        <v>STUDENT_PASS_CDA7F5D4</v>
       </c>
       <c r="T27" t="str">
-        <v>Saved (101.0 KB)</v>
+        <v>Saved (106.3 KB)</v>
       </c>
       <c r="U27" t="str">
-        <v>rejected_guest_documents/d73d6bbc-521f-4c2f-8c3d-1f46032a5b6a_school_id.jpg</v>
+        <v>rejected_guest_documents/cda7f5d4-c93e-4b83-937f-319994460534_school_id.jpg</v>
       </c>
       <c r="V27" t="str">
-        <v>Saved (32.7 KB)</v>
+        <v>Saved (100.9 KB)</v>
       </c>
       <c r="W27" t="str">
-        <v>rejected_guest_documents/d73d6bbc-521f-4c2f-8c3d-1f46032a5b6a_aadhar.jpg</v>
+        <v>rejected_guest_documents/cda7f5d4-c93e-4b83-937f-319994460534_aadhar.jpg</v>
       </c>
       <c r="X27" t="str">
         <v>No</v>
       </c>
       <c r="Y27" t="str">
-        <v>2/10/2026, 2:18:51 pm</v>
+        <v>3/10/2026, 10:13:06 am</v>
       </c>
       <c r="Z27" t="str">
-        <v>2/10/2026, 3:41:14 pm</v>
+        <v>3/10/2026, 11:59:26 am</v>
       </c>
       <c r="AA27" t="str">
-        <v>6abf6ff396ffc6b1174b86d5</v>
+        <v>6ac087dab279e4c6630e7d41</v>
       </c>
     </row>
     <row r="28">
@@ -2674,28 +2674,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>77b0ed28-574d-482f-8233-9d350438643c</v>
+        <v>cf5bb8fc-af79-4cc2-b849-0e1093ccd6a3</v>
       </c>
       <c r="C28" t="str">
-        <v>Sachin Kumar</v>
+        <v>Shubham</v>
       </c>
       <c r="D28" t="str">
-        <v>sachinchhajpur54@gmail.com</v>
+        <v>harshitsharma5820@gmail.com</v>
       </c>
       <c r="E28" t="str">
-        <v>8053266648</v>
+        <v>9350304003</v>
       </c>
       <c r="F28" t="str">
-        <v>8053266648</v>
+        <v>9350304003</v>
       </c>
       <c r="G28" t="str">
-        <v>Vijay public school panipat</v>
+        <v>govt.sr.sec.school Khalkha</v>
       </c>
       <c r="H28" t="str">
         <v>Yes</v>
       </c>
       <c r="I28" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J28" t="str">
         <v>Haryana</v>
@@ -2725,31 +2725,31 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>STUDENT_PASS_77B0ED28</v>
+        <v>STUDENT_PASS_CF5BB8FC</v>
       </c>
       <c r="T28" t="str">
-        <v>Saved (89.3 KB)</v>
+        <v>Saved (34.3 KB)</v>
       </c>
       <c r="U28" t="str">
-        <v>rejected_guest_documents/77b0ed28-574d-482f-8233-9d350438643c_school_id.jpg</v>
+        <v>rejected_guest_documents/cf5bb8fc-af79-4cc2-b849-0e1093ccd6a3_school_id.jpg</v>
       </c>
       <c r="V28" t="str">
-        <v>Saved (89.3 KB)</v>
+        <v>Saved (99.8 KB)</v>
       </c>
       <c r="W28" t="str">
-        <v>rejected_guest_documents/77b0ed28-574d-482f-8233-9d350438643c_aadhar.jpg</v>
+        <v>rejected_guest_documents/cf5bb8fc-af79-4cc2-b849-0e1093ccd6a3_aadhar.jpg</v>
       </c>
       <c r="X28" t="str">
         <v>No</v>
       </c>
       <c r="Y28" t="str">
-        <v>2/10/2026, 1:31:23 pm</v>
+        <v>3/10/2026, 10:11:25 am</v>
       </c>
       <c r="Z28" t="str">
-        <v>2/10/2026, 3:42:39 pm</v>
+        <v>3/10/2026, 12:00:29 pm</v>
       </c>
       <c r="AA28" t="str">
-        <v>6abf64d396ffc6b1174b86ca</v>
+        <v>6ac08775b279e4c6630e7d36</v>
       </c>
     </row>
     <row r="29">
@@ -2757,22 +2757,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>68d6438e-7a9a-428b-8556-6b60c103cd6f</v>
+        <v>6d25a9b7-02f0-4cc0-b69c-0b26cfa450b5</v>
       </c>
       <c r="C29" t="str">
-        <v>Shuvam</v>
+        <v>Dishu</v>
       </c>
       <c r="D29" t="str">
-        <v>kumarshivam40034@gmail.com</v>
+        <v>dishu8015@gmail.com</v>
       </c>
       <c r="E29" t="str">
-        <v>8930018601</v>
+        <v>8930305504</v>
       </c>
       <c r="F29" t="str">
-        <v>8930018601</v>
+        <v>8930305504</v>
       </c>
       <c r="G29" t="str">
-        <v>Dr mkk public school</v>
+        <v>Pratap public school</v>
       </c>
       <c r="H29" t="str">
         <v>Yes</v>
@@ -2808,31 +2808,31 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>STUDENT_PASS_68D6438E</v>
+        <v>STUDENT_PASS_6D25A9B7</v>
       </c>
       <c r="T29" t="str">
-        <v>Saved (61.4 KB)</v>
+        <v>Saved (107.3 KB)</v>
       </c>
       <c r="U29" t="str">
-        <v>rejected_guest_documents/68d6438e-7a9a-428b-8556-6b60c103cd6f_school_id.jpg</v>
+        <v>rejected_guest_documents/6d25a9b7-02f0-4cc0-b69c-0b26cfa450b5_school_id.jpg</v>
       </c>
       <c r="V29" t="str">
-        <v>Saved (43.3 KB)</v>
+        <v>Saved (85.2 KB)</v>
       </c>
       <c r="W29" t="str">
-        <v>rejected_guest_documents/68d6438e-7a9a-428b-8556-6b60c103cd6f_aadhar.jpg</v>
+        <v>rejected_guest_documents/6d25a9b7-02f0-4cc0-b69c-0b26cfa450b5_aadhar.jpg</v>
       </c>
       <c r="X29" t="str">
         <v>No</v>
       </c>
       <c r="Y29" t="str">
-        <v>2/10/2026, 12:59:19 pm</v>
+        <v>3/10/2026, 10:10:45 am</v>
       </c>
       <c r="Z29" t="str">
-        <v>2/10/2026, 3:44:06 pm</v>
+        <v>3/10/2026, 12:00:51 pm</v>
       </c>
       <c r="AA29" t="str">
-        <v>6abf5d4f96ffc6b1174b86b6</v>
+        <v>6ac0874db279e4c6630e7d2e</v>
       </c>
     </row>
     <row r="30">
@@ -2840,28 +2840,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>511c4af3-004e-4ed7-9f9f-c92793fb7a9c</v>
+        <v>55cacae6-2e16-4714-92de-0ae2e55af1c4</v>
       </c>
       <c r="C30" t="str">
-        <v>Govind Arora</v>
+        <v>Shivam</v>
       </c>
       <c r="D30" t="str">
-        <v>govindarora20441@gmail.com</v>
+        <v>harshitsharma5820@gmail.com</v>
       </c>
       <c r="E30" t="str">
-        <v>+91 70827 69442</v>
+        <v>9350304003</v>
       </c>
       <c r="F30" t="str">
-        <v>+91 70827 69442</v>
+        <v>9350304003</v>
       </c>
       <c r="G30" t="str">
-        <v>Government school</v>
+        <v>Govt. Sr.Sec.School Khalkha</v>
       </c>
       <c r="H30" t="str">
         <v>Yes</v>
       </c>
       <c r="I30" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J30" t="str">
         <v>Haryana</v>
@@ -2891,31 +2891,31 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>STUDENT_PASS_511C4AF3</v>
+        <v>STUDENT_PASS_55CACAE6</v>
       </c>
       <c r="T30" t="str">
+        <v>Saved (34.3 KB)</v>
+      </c>
+      <c r="U30" t="str">
+        <v>rejected_guest_documents/55cacae6-2e16-4714-92de-0ae2e55af1c4_school_id.jpg</v>
+      </c>
+      <c r="V30" t="str">
         <v>Saved (190.0 KB)</v>
       </c>
-      <c r="U30" t="str">
-        <v>rejected_guest_documents/511c4af3-004e-4ed7-9f9f-c92793fb7a9c_school_id.jpg</v>
-      </c>
-      <c r="V30" t="str">
-        <v>Saved (154.9 KB)</v>
-      </c>
       <c r="W30" t="str">
-        <v>rejected_guest_documents/511c4af3-004e-4ed7-9f9f-c92793fb7a9c_aadhar.jpg</v>
+        <v>rejected_guest_documents/55cacae6-2e16-4714-92de-0ae2e55af1c4_aadhar.jpg</v>
       </c>
       <c r="X30" t="str">
         <v>No</v>
       </c>
       <c r="Y30" t="str">
-        <v>2/10/2026, 12:26:15 pm</v>
+        <v>3/10/2026, 10:09:42 am</v>
       </c>
       <c r="Z30" t="str">
-        <v>2/10/2026, 3:44:52 pm</v>
+        <v>3/10/2026, 12:01:49 pm</v>
       </c>
       <c r="AA30" t="str">
-        <v>6abf558f037e79b3dc9d9022</v>
+        <v>6ac0870eb279e4c6630e7d1f</v>
       </c>
     </row>
     <row r="31">
@@ -2923,22 +2923,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>b9a9b667-4eff-480e-8ec9-40138ec19d46</v>
+        <v>70a25e8f-242e-4d5f-bb20-5fae987b0b64</v>
       </c>
       <c r="C31" t="str">
-        <v>Govt. Model sanskriti sr. Sec. School panipat</v>
+        <v>Aaditya</v>
       </c>
       <c r="D31" t="str">
-        <v>akshayruhal908@gmail.com</v>
+        <v>kaditya27127@gmail.com</v>
       </c>
       <c r="E31" t="str">
-        <v>7056480061</v>
+        <v>+91 97291 79847</v>
       </c>
       <c r="F31" t="str">
-        <v>7056480061</v>
+        <v>+91 97291 79847</v>
       </c>
       <c r="G31" t="str">
-        <v>Govt. Model sanskriti sr. Sec. School panipat</v>
+        <v>GOVT.SR.SEC SCHOOL TEHSIL CAMP PANIPAT</v>
       </c>
       <c r="H31" t="str">
         <v>Yes</v>
@@ -2974,31 +2974,31 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>STUDENT_PASS_B9A9B667</v>
+        <v>STUDENT_PASS_70A25E8F</v>
       </c>
       <c r="T31" t="str">
-        <v>Saved (147.3 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U31" t="str">
-        <v>rejected_guest_documents/b9a9b667-4eff-480e-8ec9-40138ec19d46_school_id.jpg</v>
+        <v>rejected_guest_documents/70a25e8f-242e-4d5f-bb20-5fae987b0b64_school_id.jpg</v>
       </c>
       <c r="V31" t="str">
-        <v>Saved (75.9 KB)</v>
+        <v>Saved (54.8 KB)</v>
       </c>
       <c r="W31" t="str">
-        <v>rejected_guest_documents/b9a9b667-4eff-480e-8ec9-40138ec19d46_aadhar.jpg</v>
+        <v>rejected_guest_documents/70a25e8f-242e-4d5f-bb20-5fae987b0b64_aadhar.jpg</v>
       </c>
       <c r="X31" t="str">
         <v>No</v>
       </c>
       <c r="Y31" t="str">
-        <v>2/10/2026, 12:22:21 pm</v>
+        <v>3/10/2026, 10:08:21 am</v>
       </c>
       <c r="Z31" t="str">
-        <v>2/10/2026, 3:45:49 pm</v>
+        <v>3/10/2026, 12:02:08 pm</v>
       </c>
       <c r="AA31" t="str">
-        <v>6abf54a5037e79b3dc9d9019</v>
+        <v>6ac086bdb279e4c6630e7d0b</v>
       </c>
     </row>
     <row r="32">
@@ -3006,22 +3006,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>8df52941-3a84-4a12-b0a4-ffa272900e60</v>
+        <v>d137e733-95da-4a72-ab46-a508ff794274</v>
       </c>
       <c r="C32" t="str">
-        <v>Akshay ruhal</v>
+        <v>Raushan kumar</v>
       </c>
       <c r="D32" t="str">
-        <v>akshayruhal908@gmail.com</v>
+        <v>rk2394533@gmail.com</v>
       </c>
       <c r="E32" t="str">
-        <v>7056480061</v>
+        <v>8307844816</v>
       </c>
       <c r="F32" t="str">
-        <v>7056480061</v>
+        <v>8307844816</v>
       </c>
       <c r="G32" t="str">
-        <v>Govt. Model sanskriti sr. Sec. School panipat</v>
+        <v>GOVT.SR.SEC.SCHOOL</v>
       </c>
       <c r="H32" t="str">
         <v>Yes</v>
@@ -3033,10 +3033,10 @@
         <v>Haryana</v>
       </c>
       <c r="K32" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L32" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M32" t="str">
         <v>failed</v>
@@ -3057,31 +3057,31 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>STUDENT_PASS_8DF52941</v>
+        <v>STUDENT_PASS_D137E733</v>
       </c>
       <c r="T32" t="str">
-        <v>Saved (147.3 KB)</v>
+        <v>Saved (106.3 KB)</v>
       </c>
       <c r="U32" t="str">
-        <v>rejected_guest_documents/8df52941-3a84-4a12-b0a4-ffa272900e60_school_id.jpg</v>
+        <v>rejected_guest_documents/d137e733-95da-4a72-ab46-a508ff794274_school_id.jpg</v>
       </c>
       <c r="V32" t="str">
-        <v>Saved (75.9 KB)</v>
+        <v>Saved (100.9 KB)</v>
       </c>
       <c r="W32" t="str">
-        <v>rejected_guest_documents/8df52941-3a84-4a12-b0a4-ffa272900e60_aadhar.jpg</v>
+        <v>rejected_guest_documents/d137e733-95da-4a72-ab46-a508ff794274_aadhar.jpg</v>
       </c>
       <c r="X32" t="str">
         <v>No</v>
       </c>
       <c r="Y32" t="str">
-        <v>2/10/2026, 12:19:01 pm</v>
+        <v>3/10/2026, 10:06:28 am</v>
       </c>
       <c r="Z32" t="str">
-        <v>2/10/2026, 3:46:05 pm</v>
+        <v>3/10/2026, 10:08:27 am</v>
       </c>
       <c r="AA32" t="str">
-        <v>6abf53dd037e79b3dc9d9011</v>
+        <v>6ac0864cb279e4c6630e7d04</v>
       </c>
     </row>
     <row r="33">
@@ -3089,25 +3089,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>2c344f85-3cc1-4b00-8b09-6624a3d9870a</v>
+        <v>a897a040-644d-4d70-8877-f829ab7b8990</v>
       </c>
       <c r="C33" t="str">
-        <v>Priya</v>
+        <v>Raushan kumar</v>
       </c>
       <c r="D33" t="str">
-        <v>priya83989@gmail.com</v>
+        <v>rk2394533@gmail.com</v>
       </c>
       <c r="E33" t="str">
-        <v>8865926608</v>
+        <v>8307844816</v>
       </c>
       <c r="F33" t="str">
-        <v>8865926608</v>
+        <v>8307844816</v>
       </c>
       <c r="G33" t="str">
-        <v>Arya Sr Sec School Panipat</v>
+        <v>GOVT.SR.SEC.SCHOOL</v>
       </c>
       <c r="H33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I33" t="str">
         <v>12th</v>
@@ -3140,31 +3140,31 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>STUDENT_PASS_2C344F85</v>
+        <v>STUDENT_PASS_A897A040</v>
       </c>
       <c r="T33" t="str">
-        <v>Saved (122.6 KB)</v>
+        <v>Saved (106.3 KB)</v>
       </c>
       <c r="U33" t="str">
-        <v>rejected_guest_documents/2c344f85-3cc1-4b00-8b09-6624a3d9870a_school_id.jpg</v>
+        <v>rejected_guest_documents/a897a040-644d-4d70-8877-f829ab7b8990_school_id.jpg</v>
       </c>
       <c r="V33" t="str">
-        <v>Saved (132.5 KB)</v>
+        <v>Saved (100.9 KB)</v>
       </c>
       <c r="W33" t="str">
-        <v>rejected_guest_documents/2c344f85-3cc1-4b00-8b09-6624a3d9870a_aadhar.jpg</v>
+        <v>rejected_guest_documents/a897a040-644d-4d70-8877-f829ab7b8990_aadhar.jpg</v>
       </c>
       <c r="X33" t="str">
         <v>No</v>
       </c>
       <c r="Y33" t="str">
-        <v>2/10/2026, 12:16:50 pm</v>
+        <v>3/10/2026, 10:05:59 am</v>
       </c>
       <c r="Z33" t="str">
-        <v>2/10/2026, 3:46:46 pm</v>
+        <v>3/10/2026, 10:08:42 am</v>
       </c>
       <c r="AA33" t="str">
-        <v>6abf535a037e79b3dc9d900e</v>
+        <v>6ac0862fb279e4c6630e7d00</v>
       </c>
     </row>
     <row r="34">
@@ -3172,22 +3172,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>91f80954-f70a-40ff-9816-3ae3b28085a8</v>
+        <v>185b63ae-d232-40de-b80d-1b6f33660d0e</v>
       </c>
       <c r="C34" t="str">
-        <v>Nishu</v>
+        <v>Aaditya</v>
       </c>
       <c r="D34" t="str">
-        <v>gg1063178@gmail.com</v>
+        <v>kaditya27127@gmail.com</v>
       </c>
       <c r="E34" t="str">
-        <v>9996659025</v>
+        <v>+91 97291 79847</v>
       </c>
       <c r="F34" t="str">
-        <v>9996659025</v>
+        <v>+91 97291 79847</v>
       </c>
       <c r="G34" t="str">
-        <v>Government senior secondary School</v>
+        <v>Government hight school Tehsil camp</v>
       </c>
       <c r="H34" t="str">
         <v>Yes</v>
@@ -3223,31 +3223,31 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>STUDENT_PASS_91F80954</v>
+        <v>STUDENT_PASS_185B63AE</v>
       </c>
       <c r="T34" t="str">
-        <v>Saved (215.8 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U34" t="str">
-        <v>rejected_guest_documents/91f80954-f70a-40ff-9816-3ae3b28085a8_school_id.jpg</v>
+        <v>rejected_guest_documents/185b63ae-d232-40de-b80d-1b6f33660d0e_school_id.jpg</v>
       </c>
       <c r="V34" t="str">
-        <v>Saved (198.1 KB)</v>
+        <v>Saved (54.8 KB)</v>
       </c>
       <c r="W34" t="str">
-        <v>rejected_guest_documents/91f80954-f70a-40ff-9816-3ae3b28085a8_aadhar.jpg</v>
+        <v>rejected_guest_documents/185b63ae-d232-40de-b80d-1b6f33660d0e_aadhar.jpg</v>
       </c>
       <c r="X34" t="str">
         <v>No</v>
       </c>
       <c r="Y34" t="str">
-        <v>1/10/2026, 10:46:45 pm</v>
+        <v>3/10/2026, 10:02:33 am</v>
       </c>
       <c r="Z34" t="str">
-        <v>2/10/2026, 3:31:57 pm</v>
+        <v>3/10/2026, 10:09:29 am</v>
       </c>
       <c r="AA34" t="str">
-        <v>6abe957da4c406488f4d3795</v>
+        <v>6ac08561b279e4c6630e7cf8</v>
       </c>
     </row>
     <row r="35">
@@ -3255,25 +3255,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>91adb560-2263-45a3-9bbb-3b47ec8d78a2</v>
+        <v>a30af938-3707-4323-b62b-12109fb2fc7a</v>
       </c>
       <c r="C35" t="str">
-        <v>Shan Maharaj</v>
+        <v>Pushkar chauhan</v>
       </c>
       <c r="D35" t="str">
-        <v>mitumaharaj817@gmail.com</v>
+        <v>pushkarch2008@gmail.com</v>
       </c>
       <c r="E35" t="str">
-        <v>8307614852</v>
+        <v>9253553193</v>
       </c>
       <c r="F35" t="str">
-        <v>8307614852</v>
+        <v>9253553193</v>
       </c>
       <c r="G35" t="str">
-        <v>Arya Sr Sec School Panipat</v>
+        <v>Himgiri public school</v>
       </c>
       <c r="H35" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I35" t="str">
         <v>12th</v>
@@ -3306,31 +3306,31 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>STUDENT_PASS_91ADB560</v>
+        <v>STUDENT_PASS_A30AF938</v>
       </c>
       <c r="T35" t="str">
-        <v>Saved (131.9 KB)</v>
+        <v>Saved (60.3 KB)</v>
       </c>
       <c r="U35" t="str">
-        <v>rejected_guest_documents/91adb560-2263-45a3-9bbb-3b47ec8d78a2_school_id.jpg</v>
+        <v>rejected_guest_documents/a30af938-3707-4323-b62b-12109fb2fc7a_school_id.jpg</v>
       </c>
       <c r="V35" t="str">
-        <v>Saved (66.0 KB)</v>
+        <v>Saved (53.5 KB)</v>
       </c>
       <c r="W35" t="str">
-        <v>rejected_guest_documents/91adb560-2263-45a3-9bbb-3b47ec8d78a2_aadhar.jpg</v>
+        <v>rejected_guest_documents/a30af938-3707-4323-b62b-12109fb2fc7a_aadhar.jpg</v>
       </c>
       <c r="X35" t="str">
         <v>No</v>
       </c>
       <c r="Y35" t="str">
-        <v>1/10/2026, 10:36:21 pm</v>
+        <v>3/10/2026, 9:58:44 am</v>
       </c>
       <c r="Z35" t="str">
-        <v>2/10/2026, 3:32:17 pm</v>
+        <v>3/10/2026, 10:10:08 am</v>
       </c>
       <c r="AA35" t="str">
-        <v>6abe930da4c406488f4d376d</v>
+        <v>6ac0847cb279e4c6630e7cf1</v>
       </c>
     </row>
     <row r="36">
@@ -3338,22 +3338,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>003d1859-641d-47ad-822c-b5e5448b2f92</v>
+        <v>713623a0-238c-495c-bc91-785b217f8839</v>
       </c>
       <c r="C36" t="str">
-        <v>Vansh</v>
+        <v>Dishu</v>
       </c>
       <c r="D36" t="str">
-        <v>panditseema249@gmail.com</v>
+        <v>dishu8015@gmail.com</v>
       </c>
       <c r="E36" t="str">
-        <v>8684968092</v>
+        <v>8930405504</v>
       </c>
       <c r="F36" t="str">
-        <v>8684968092</v>
+        <v>8930405504</v>
       </c>
       <c r="G36" t="str">
-        <v>Gautam vidya peeth sr sec school</v>
+        <v>Pratap public school</v>
       </c>
       <c r="H36" t="str">
         <v>Yes</v>
@@ -3389,31 +3389,31 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>STUDENT_PASS_003D1859</v>
+        <v>STUDENT_PASS_713623A0</v>
       </c>
       <c r="T36" t="str">
-        <v>Saved (86.1 KB)</v>
+        <v>Saved (151.2 KB)</v>
       </c>
       <c r="U36" t="str">
-        <v>rejected_guest_documents/003d1859-641d-47ad-822c-b5e5448b2f92_school_id.jpg</v>
+        <v>rejected_guest_documents/713623a0-238c-495c-bc91-785b217f8839_school_id.jpg</v>
       </c>
       <c r="V36" t="str">
-        <v>Saved (30.8 KB)</v>
+        <v>Saved (121.0 KB)</v>
       </c>
       <c r="W36" t="str">
-        <v>rejected_guest_documents/003d1859-641d-47ad-822c-b5e5448b2f92_aadhar.jpg</v>
+        <v>rejected_guest_documents/713623a0-238c-495c-bc91-785b217f8839_aadhar.jpg</v>
       </c>
       <c r="X36" t="str">
         <v>No</v>
       </c>
       <c r="Y36" t="str">
-        <v>1/10/2026, 10:27:30 pm</v>
+        <v>3/10/2026, 9:55:22 am</v>
       </c>
       <c r="Z36" t="str">
-        <v>2/10/2026, 3:32:29 pm</v>
+        <v>3/10/2026, 12:20:16 pm</v>
       </c>
       <c r="AA36" t="str">
-        <v>6abe90fab19ec19a5c0f3d36</v>
+        <v>6ac083b2b279e4c6630e7ceb</v>
       </c>
     </row>
     <row r="37">
@@ -3421,22 +3421,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>1626151d-b6cf-40d6-9d66-de9404e41433</v>
+        <v>7328afb4-b177-4835-b1b0-841b2e91c258</v>
       </c>
       <c r="C37" t="str">
-        <v>VINAY KUMAR</v>
+        <v>Raushan kumar</v>
       </c>
       <c r="D37" t="str">
-        <v>vini07921@gmail.com</v>
+        <v>rk2394533@gmail.com</v>
       </c>
       <c r="E37" t="str">
-        <v>9034237165</v>
+        <v>8307844816</v>
       </c>
       <c r="F37" t="str">
-        <v>9034237165</v>
+        <v>8307844816</v>
       </c>
       <c r="G37" t="str">
-        <v>Navyug senior secondary school</v>
+        <v>Government hight school Tehsil camp Panipat</v>
       </c>
       <c r="H37" t="str">
         <v>Yes</v>
@@ -3457,7 +3457,7 @@
         <v>failed</v>
       </c>
       <c r="N37" t="str">
-        <v>Your name is incorrect, Please correct it.</v>
+        <v>NA</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>STUDENT_PASS_1626151D</v>
+        <v>STUDENT_PASS_7328AFB4</v>
       </c>
       <c r="T37" t="str">
-        <v>Saved (279.3 KB)</v>
+        <v>Saved (106.0 KB)</v>
       </c>
       <c r="U37" t="str">
-        <v>rejected_guest_documents/1626151d-b6cf-40d6-9d66-de9404e41433_school_id.jpg</v>
+        <v>rejected_guest_documents/7328afb4-b177-4835-b1b0-841b2e91c258_school_id.jpg</v>
       </c>
       <c r="V37" t="str">
-        <v>Saved (377.0 KB)</v>
+        <v>Saved (100.7 KB)</v>
       </c>
       <c r="W37" t="str">
-        <v>rejected_guest_documents/1626151d-b6cf-40d6-9d66-de9404e41433_aadhar.jpg</v>
+        <v>rejected_guest_documents/7328afb4-b177-4835-b1b0-841b2e91c258_aadhar.jpg</v>
       </c>
       <c r="X37" t="str">
         <v>No</v>
       </c>
       <c r="Y37" t="str">
-        <v>1/10/2026, 10:24:49 pm</v>
+        <v>3/10/2026, 9:54:46 am</v>
       </c>
       <c r="Z37" t="str">
-        <v>1/10/2026, 10:48:04 pm</v>
+        <v>3/10/2026, 10:10:58 am</v>
       </c>
       <c r="AA37" t="str">
-        <v>6abe9059b19ec19a5c0f3d1c</v>
+        <v>6ac0838eb279e4c6630e7ce7</v>
       </c>
     </row>
     <row r="38">
@@ -3504,25 +3504,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>a558be25-fce8-4e24-a3df-ef5a513b876d</v>
+        <v>ee7d8706-0a86-4c8c-ba49-6fb911ed9388</v>
       </c>
       <c r="C38" t="str">
-        <v>Nitesh</v>
+        <v>Dishu</v>
       </c>
       <c r="D38" t="str">
-        <v>dfhvxhjhggghfvgmvfxbh@gmail.com</v>
+        <v>vipinkumar00786786@gmail.com</v>
       </c>
       <c r="E38" t="str">
-        <v>7355895366</v>
+        <v>8930405504</v>
       </c>
       <c r="F38" t="str">
-        <v>7355895366</v>
+        <v>8930405504</v>
       </c>
       <c r="G38" t="str">
-        <v>gyandeep senior secondary school</v>
+        <v>Pratap public school</v>
       </c>
       <c r="H38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I38" t="str">
         <v>12th</v>
@@ -3555,31 +3555,31 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>STUDENT_PASS_A558BE25</v>
+        <v>STUDENT_PASS_EE7D8706</v>
       </c>
       <c r="T38" t="str">
-        <v>Saved (174.4 KB)</v>
+        <v>Saved (151.2 KB)</v>
       </c>
       <c r="U38" t="str">
-        <v>rejected_guest_documents/a558be25-fce8-4e24-a3df-ef5a513b876d_school_id.jpg</v>
+        <v>rejected_guest_documents/ee7d8706-0a86-4c8c-ba49-6fb911ed9388_school_id.jpg</v>
       </c>
       <c r="V38" t="str">
-        <v>Saved (141.4 KB)</v>
+        <v>Saved (121.0 KB)</v>
       </c>
       <c r="W38" t="str">
-        <v>rejected_guest_documents/a558be25-fce8-4e24-a3df-ef5a513b876d_aadhar.jpg</v>
+        <v>rejected_guest_documents/ee7d8706-0a86-4c8c-ba49-6fb911ed9388_aadhar.jpg</v>
       </c>
       <c r="X38" t="str">
         <v>No</v>
       </c>
       <c r="Y38" t="str">
-        <v>1/10/2026, 10:14:20 pm</v>
+        <v>3/10/2026, 9:52:14 am</v>
       </c>
       <c r="Z38" t="str">
-        <v>2/10/2026, 3:32:49 pm</v>
+        <v>3/10/2026, 12:20:50 pm</v>
       </c>
       <c r="AA38" t="str">
-        <v>6abe8de4b19ec19a5c0f3ceb</v>
+        <v>6ac082f6b279e4c6630e7ce4</v>
       </c>
     </row>
     <row r="39">
@@ -3587,25 +3587,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>6416d158-7ede-40a6-b8f4-8535e7dc3745</v>
+        <v>3a713f73-c94d-48f0-bee3-6aaf1d023299</v>
       </c>
       <c r="C39" t="str">
-        <v>pavani</v>
+        <v>Aniket</v>
       </c>
       <c r="D39" t="str">
-        <v>pavanibatra50@gmail.com</v>
+        <v>aniketsaini7872@gmail.com</v>
       </c>
       <c r="E39" t="str">
-        <v>9037701313</v>
+        <v>90503 31509‬</v>
       </c>
       <c r="F39" t="str">
-        <v>9037701313</v>
+        <v>90503 31509‬</v>
       </c>
       <c r="G39" t="str">
-        <v>Delhi Public School Karnal</v>
+        <v>Panipat international school</v>
       </c>
       <c r="H39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I39" t="str">
         <v>12th</v>
@@ -3614,16 +3614,16 @@
         <v>Haryana</v>
       </c>
       <c r="K39" t="str">
-        <v>Karnal</v>
+        <v>Panipat</v>
       </c>
       <c r="L39" t="str">
-        <v>Karnal, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M39" t="str">
         <v>failed</v>
       </c>
       <c r="N39" t="str">
-        <v>please share your proper documents.</v>
+        <v>please check your school name.</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -3638,31 +3638,31 @@
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>STUDENT_PASS_6416D158</v>
+        <v>STUDENT_PASS_3A713F73</v>
       </c>
       <c r="T39" t="str">
-        <v>Saved (340.8 KB)</v>
+        <v>Saved (248.9 KB)</v>
       </c>
       <c r="U39" t="str">
-        <v>rejected_guest_documents/6416d158-7ede-40a6-b8f4-8535e7dc3745_school_id.jpg</v>
+        <v>rejected_guest_documents/3a713f73-c94d-48f0-bee3-6aaf1d023299_school_id.jpg</v>
       </c>
       <c r="V39" t="str">
-        <v>Saved (199.6 KB)</v>
+        <v>Saved (111.9 KB)</v>
       </c>
       <c r="W39" t="str">
-        <v>rejected_guest_documents/6416d158-7ede-40a6-b8f4-8535e7dc3745_aadhar.jpg</v>
+        <v>rejected_guest_documents/3a713f73-c94d-48f0-bee3-6aaf1d023299_aadhar.jpg</v>
       </c>
       <c r="X39" t="str">
         <v>No</v>
       </c>
       <c r="Y39" t="str">
-        <v>1/10/2026, 9:35:26 pm</v>
+        <v>3/10/2026, 9:52:09 am</v>
       </c>
       <c r="Z39" t="str">
-        <v>1/10/2026, 10:26:42 pm</v>
+        <v>3/10/2026, 10:12:33 am</v>
       </c>
       <c r="AA39" t="str">
-        <v>6abe84c690a48fcc35951578</v>
+        <v>6ac082f1b279e4c6630e7ce1</v>
       </c>
     </row>
     <row r="40">
@@ -3670,25 +3670,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>6e38d358-dfd1-4b65-985a-c17e3cc9f607</v>
+        <v>250557ef-e9bc-4ae6-b0e3-7325aa01360f</v>
       </c>
       <c r="C40" t="str">
-        <v>sawan kumar</v>
+        <v>Lucky Ali</v>
       </c>
       <c r="D40" t="str">
-        <v>mrsawanparjapat47@gmail.com</v>
+        <v>aasukhark@gmail.com</v>
       </c>
       <c r="E40" t="str">
-        <v>9729465288</v>
+        <v>7082671024</v>
       </c>
       <c r="F40" t="str">
-        <v>9729465288</v>
+        <v>7082671024</v>
       </c>
       <c r="G40" t="str">
-        <v>CRM High School Chulkana Samalkha</v>
+        <v>Govt Model Sanskriti Sr Sec School Israna Panipat</v>
       </c>
       <c r="H40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I40" t="str">
         <v>12th</v>
@@ -3697,16 +3697,16 @@
         <v>Haryana</v>
       </c>
       <c r="K40" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L40" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M40" t="str">
         <v>failed</v>
       </c>
       <c r="N40" t="str">
-        <v>please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -3721,31 +3721,31 @@
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>STUDENT_PASS_6E38D358</v>
+        <v>STUDENT_PASS_250557EF</v>
       </c>
       <c r="T40" t="str">
-        <v>Saved (92.5 KB)</v>
+        <v>Saved (51.2 KB)</v>
       </c>
       <c r="U40" t="str">
-        <v>rejected_guest_documents/6e38d358-dfd1-4b65-985a-c17e3cc9f607_school_id.jpg</v>
+        <v>rejected_guest_documents/250557ef-e9bc-4ae6-b0e3-7325aa01360f_school_id.jpg</v>
       </c>
       <c r="V40" t="str">
-        <v>Saved (92.5 KB)</v>
+        <v>Saved (143.0 KB)</v>
       </c>
       <c r="W40" t="str">
-        <v>rejected_guest_documents/6e38d358-dfd1-4b65-985a-c17e3cc9f607_aadhar.jpg</v>
+        <v>rejected_guest_documents/250557ef-e9bc-4ae6-b0e3-7325aa01360f_aadhar.jpg</v>
       </c>
       <c r="X40" t="str">
         <v>No</v>
       </c>
       <c r="Y40" t="str">
-        <v>1/10/2026, 9:16:32 pm</v>
+        <v>3/10/2026, 8:06:39 am</v>
       </c>
       <c r="Z40" t="str">
-        <v>1/10/2026, 10:23:39 pm</v>
+        <v>3/10/2026, 9:39:32 am</v>
       </c>
       <c r="AA40" t="str">
-        <v>6abe8058345de819518e4582</v>
+        <v>6ac06a37f6c0179b5d9704c1</v>
       </c>
     </row>
     <row r="41">
@@ -3753,25 +3753,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>dfa91dfe-ca2c-44f9-9177-9984ea108f37</v>
+        <v>6245112b-e070-4959-8694-484aa5ae7709</v>
       </c>
       <c r="C41" t="str">
-        <v>Ritik yadav</v>
+        <v>Manit</v>
       </c>
       <c r="D41" t="str">
-        <v>ritikyadav09801@gmail.com</v>
+        <v>neerajkumar6636ygrj@gmail.com</v>
       </c>
       <c r="E41" t="str">
-        <v>9518278081</v>
+        <v>8818044051</v>
       </c>
       <c r="F41" t="str">
-        <v>9518278081</v>
+        <v>8818044051</v>
       </c>
       <c r="G41" t="str">
-        <v>LSBT Public Sr Sec School Saundhapur</v>
+        <v>Government senior secondary School Gohana</v>
       </c>
       <c r="H41" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I41" t="str">
         <v>12th</v>
@@ -3780,16 +3780,16 @@
         <v>Haryana</v>
       </c>
       <c r="K41" t="str">
-        <v>Panipat</v>
+        <v>Gohana</v>
       </c>
       <c r="L41" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Gohana, Haryana</v>
       </c>
       <c r="M41" t="str">
         <v>failed</v>
       </c>
       <c r="N41" t="str">
-        <v>please your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3804,31 +3804,31 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>STUDENT_PASS_DFA91DFE</v>
+        <v>STUDENT_PASS_6245112B</v>
       </c>
       <c r="T41" t="str">
-        <v>Saved (28.6 KB)</v>
+        <v>Saved (146.2 KB)</v>
       </c>
       <c r="U41" t="str">
-        <v>rejected_guest_documents/dfa91dfe-ca2c-44f9-9177-9984ea108f37_school_id.jpg</v>
+        <v>rejected_guest_documents/6245112b-e070-4959-8694-484aa5ae7709_school_id.jpg</v>
       </c>
       <c r="V41" t="str">
-        <v>Saved (80.9 KB)</v>
+        <v>Saved (52.3 KB)</v>
       </c>
       <c r="W41" t="str">
-        <v>rejected_guest_documents/dfa91dfe-ca2c-44f9-9177-9984ea108f37_aadhar.jpg</v>
+        <v>rejected_guest_documents/6245112b-e070-4959-8694-484aa5ae7709_aadhar.jpg</v>
       </c>
       <c r="X41" t="str">
         <v>No</v>
       </c>
       <c r="Y41" t="str">
-        <v>1/10/2026, 8:34:28 pm</v>
+        <v>3/10/2026, 7:59:03 am</v>
       </c>
       <c r="Z41" t="str">
-        <v>1/10/2026, 10:04:52 pm</v>
+        <v>3/10/2026, 9:40:00 am</v>
       </c>
       <c r="AA41" t="str">
-        <v>6abe767c857a8358ce896a5d</v>
+        <v>6ac0686ff6c0179b5d9704bb</v>
       </c>
     </row>
     <row r="42">
@@ -3836,25 +3836,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>44f19776-3ba4-4336-a254-b72dc50a4e45</v>
+        <v>cd8e76c8-62f3-4859-96c7-9bf4a1dd8757</v>
       </c>
       <c r="C42" t="str">
-        <v>Vansh Narang</v>
+        <v>Priya</v>
       </c>
       <c r="D42" t="str">
-        <v>harshnarang60152@gmail.com</v>
+        <v>manujapriya44@gmail.com</v>
       </c>
       <c r="E42" t="str">
-        <v>8528596096</v>
+        <v>9350369824</v>
       </c>
       <c r="F42" t="str">
-        <v>8528596096</v>
+        <v>9350369824</v>
       </c>
       <c r="G42" t="str">
-        <v>Navyug Public school</v>
+        <v>SD Modern Sr Sec School Panipat</v>
       </c>
       <c r="H42" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I42" t="str">
         <v>12th</v>
@@ -3872,7 +3872,7 @@
         <v>failed</v>
       </c>
       <c r="N42" t="str">
-        <v>sorry your name is not correct please correct your name.</v>
+        <v>NA</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -3887,31 +3887,31 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>STUDENT_PASS_44F19776</v>
+        <v>STUDENT_PASS_CD8E76C8</v>
       </c>
       <c r="T42" t="str">
-        <v>Saved (120.5 KB)</v>
+        <v>Saved (172.1 KB)</v>
       </c>
       <c r="U42" t="str">
-        <v>rejected_guest_documents/44f19776-3ba4-4336-a254-b72dc50a4e45_school_id.jpg</v>
+        <v>rejected_guest_documents/cd8e76c8-62f3-4859-96c7-9bf4a1dd8757_school_id.jpg</v>
       </c>
       <c r="V42" t="str">
-        <v>Saved (20.1 KB)</v>
+        <v>Saved (80.3 KB)</v>
       </c>
       <c r="W42" t="str">
-        <v>rejected_guest_documents/44f19776-3ba4-4336-a254-b72dc50a4e45_aadhar.jpg</v>
+        <v>rejected_guest_documents/cd8e76c8-62f3-4859-96c7-9bf4a1dd8757_aadhar.jpg</v>
       </c>
       <c r="X42" t="str">
         <v>No</v>
       </c>
       <c r="Y42" t="str">
-        <v>1/10/2026, 7:53:32 pm</v>
+        <v>3/10/2026, 6:48:44 am</v>
       </c>
       <c r="Z42" t="str">
-        <v>1/10/2026, 9:54:10 pm</v>
+        <v>3/10/2026, 9:51:54 am</v>
       </c>
       <c r="AA42" t="str">
-        <v>6abe6ce4857a8358ce896a29</v>
+        <v>6ac057f4797a587cf0f2fd1e</v>
       </c>
     </row>
     <row r="43">
@@ -3919,25 +3919,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>26e660d5-d79b-424c-93a5-3f8acae41a16</v>
+        <v>2f51ca13-2057-46a9-9a12-3d3c89290d9b</v>
       </c>
       <c r="C43" t="str">
-        <v>Harsh</v>
+        <v>Mayank</v>
       </c>
       <c r="D43" t="str">
-        <v>harshpruthi.in@gmail.com</v>
+        <v>ranimanju38952@gmail.com</v>
       </c>
       <c r="E43" t="str">
-        <v>8950177980</v>
+        <v>9034774449</v>
       </c>
       <c r="F43" t="str">
-        <v>8950177980</v>
+        <v>9034774449</v>
       </c>
       <c r="G43" t="str">
-        <v>Dr. mkk arya model school</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I43" t="str">
         <v>12th</v>
@@ -3955,7 +3955,7 @@
         <v>failed</v>
       </c>
       <c r="N43" t="str">
-        <v>please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -3970,31 +3970,31 @@
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>STUDENT_PASS_26E660D5</v>
+        <v>STUDENT_PASS_2F51CA13</v>
       </c>
       <c r="T43" t="str">
-        <v>Saved (72.1 KB)</v>
+        <v>Saved (71.0 KB)</v>
       </c>
       <c r="U43" t="str">
-        <v>rejected_guest_documents/26e660d5-d79b-424c-93a5-3f8acae41a16_school_id.jpg</v>
+        <v>rejected_guest_documents/2f51ca13-2057-46a9-9a12-3d3c89290d9b_school_id.jpg</v>
       </c>
       <c r="V43" t="str">
-        <v>Saved (129.9 KB)</v>
+        <v>Saved (109.8 KB)</v>
       </c>
       <c r="W43" t="str">
-        <v>rejected_guest_documents/26e660d5-d79b-424c-93a5-3f8acae41a16_aadhar.jpg</v>
+        <v>rejected_guest_documents/2f51ca13-2057-46a9-9a12-3d3c89290d9b_aadhar.jpg</v>
       </c>
       <c r="X43" t="str">
         <v>No</v>
       </c>
       <c r="Y43" t="str">
-        <v>1/10/2026, 7:43:27 pm</v>
+        <v>3/10/2026, 6:08:34 am</v>
       </c>
       <c r="Z43" t="str">
-        <v>1/10/2026, 9:51:46 pm</v>
+        <v>3/10/2026, 10:13:43 am</v>
       </c>
       <c r="AA43" t="str">
-        <v>6abe6a87857a8358ce896a1d</v>
+        <v>6ac04e8af467e17e3be78fcd</v>
       </c>
     </row>
     <row r="44">
@@ -4002,22 +4002,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>599c6af7-9daa-438e-810c-aeb7ff4e7685</v>
+        <v>1ca23f48-8a42-4eb6-90a4-de3cf2c20071</v>
       </c>
       <c r="C44" t="str">
-        <v>Anurag</v>
+        <v>Latesh</v>
       </c>
       <c r="D44" t="str">
-        <v>anujghangas7@gmail.com</v>
+        <v>latesh362@gmail.com</v>
       </c>
       <c r="E44" t="str">
-        <v>9729433894</v>
+        <v>9813983404</v>
       </c>
       <c r="F44" t="str">
-        <v>9729433894</v>
+        <v>9813983404</v>
       </c>
       <c r="G44" t="str">
-        <v>Shivalik modran sr sec school</v>
+        <v>Government model sanskriti senior secondary school Nehar kothi , Barwala (Hisar)</v>
       </c>
       <c r="H44" t="str">
         <v>Yes</v>
@@ -4029,16 +4029,16 @@
         <v>Haryana</v>
       </c>
       <c r="K44" t="str">
-        <v>Panipat</v>
+        <v>Barwala</v>
       </c>
       <c r="L44" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Barwala, Haryana</v>
       </c>
       <c r="M44" t="str">
         <v>failed</v>
       </c>
       <c r="N44" t="str">
-        <v>please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -4053,31 +4053,31 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>STUDENT_PASS_599C6AF7</v>
+        <v>STUDENT_PASS_1CA23F48</v>
       </c>
       <c r="T44" t="str">
-        <v>Saved (139.3 KB)</v>
+        <v>Saved (87.2 KB)</v>
       </c>
       <c r="U44" t="str">
-        <v>rejected_guest_documents/599c6af7-9daa-438e-810c-aeb7ff4e7685_school_id.jpg</v>
+        <v>rejected_guest_documents/1ca23f48-8a42-4eb6-90a4-de3cf2c20071_school_id.jpg</v>
       </c>
       <c r="V44" t="str">
-        <v>Saved (113.5 KB)</v>
+        <v>Saved (105.2 KB)</v>
       </c>
       <c r="W44" t="str">
-        <v>rejected_guest_documents/599c6af7-9daa-438e-810c-aeb7ff4e7685_aadhar.jpg</v>
+        <v>rejected_guest_documents/1ca23f48-8a42-4eb6-90a4-de3cf2c20071_aadhar.jpg</v>
       </c>
       <c r="X44" t="str">
         <v>No</v>
       </c>
       <c r="Y44" t="str">
-        <v>1/10/2026, 7:42:35 pm</v>
+        <v>3/10/2026, 4:37:01 am</v>
       </c>
       <c r="Z44" t="str">
-        <v>1/10/2026, 9:50:52 pm</v>
+        <v>3/10/2026, 10:13:57 am</v>
       </c>
       <c r="AA44" t="str">
-        <v>6abe6a53857a8358ce896a16</v>
+        <v>6ac03915e49335010548a5f2</v>
       </c>
     </row>
     <row r="45">
@@ -4085,43 +4085,43 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>33758e94-87d0-49f5-9523-202b5675d209</v>
+        <v>0d364a24-22e8-4208-9979-543628cb329a</v>
       </c>
       <c r="C45" t="str">
-        <v>Avneet Panchal</v>
+        <v>Latesh</v>
       </c>
       <c r="D45" t="str">
-        <v>panchalavneet71@gmail.com</v>
+        <v>latesh362@gmail.com</v>
       </c>
       <c r="E45" t="str">
-        <v>918168978575</v>
+        <v>9813983404</v>
       </c>
       <c r="F45" t="str">
-        <v>918168978575</v>
+        <v>9813983404</v>
       </c>
       <c r="G45" t="str">
-        <v>Avneet Panchal</v>
+        <v>Government model sanskriti senior secondary school , Barwala (Hisar)</v>
       </c>
       <c r="H45" t="str">
         <v>Yes</v>
       </c>
       <c r="I45" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J45" t="str">
         <v>Haryana</v>
       </c>
       <c r="K45" t="str">
-        <v>Panipat</v>
+        <v>Barwala</v>
       </c>
       <c r="L45" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Barwala, Haryana</v>
       </c>
       <c r="M45" t="str">
         <v>failed</v>
       </c>
       <c r="N45" t="str">
-        <v>please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -4136,31 +4136,31 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>STUDENT_PASS_33758E94</v>
+        <v>STUDENT_PASS_0D364A24</v>
       </c>
       <c r="T45" t="str">
-        <v>Saved (80.9 KB)</v>
+        <v>Saved (87.2 KB)</v>
       </c>
       <c r="U45" t="str">
-        <v>rejected_guest_documents/33758e94-87d0-49f5-9523-202b5675d209_school_id.jpg</v>
+        <v>rejected_guest_documents/0d364a24-22e8-4208-9979-543628cb329a_school_id.jpg</v>
       </c>
       <c r="V45" t="str">
-        <v>Saved (65.6 KB)</v>
+        <v>Saved (105.2 KB)</v>
       </c>
       <c r="W45" t="str">
-        <v>rejected_guest_documents/33758e94-87d0-49f5-9523-202b5675d209_aadhar.jpg</v>
+        <v>rejected_guest_documents/0d364a24-22e8-4208-9979-543628cb329a_aadhar.jpg</v>
       </c>
       <c r="X45" t="str">
         <v>No</v>
       </c>
       <c r="Y45" t="str">
-        <v>1/10/2026, 7:38:32 pm</v>
+        <v>3/10/2026, 4:35:03 am</v>
       </c>
       <c r="Z45" t="str">
-        <v>1/10/2026, 9:50:06 pm</v>
+        <v>3/10/2026, 10:14:10 am</v>
       </c>
       <c r="AA45" t="str">
-        <v>6abe6960857a8358ce896a10</v>
+        <v>6ac0389fe49335010548a5eb</v>
       </c>
     </row>
     <row r="46">
@@ -4168,22 +4168,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>d1f0f1e1-b2a2-4ce2-bfcc-ad89feee6706</v>
+        <v>ed4cce05-acd4-41c6-bd69-a38e075c659a</v>
       </c>
       <c r="C46" t="str">
-        <v>Sanawwer Ansari</v>
+        <v>Dhruvchugh</v>
       </c>
       <c r="D46" t="str">
-        <v>sanawweransari7@gmail.com</v>
+        <v>pariyarprkash56@gmail.com</v>
       </c>
       <c r="E46" t="str">
-        <v>7988462840</v>
+        <v>8199005202</v>
       </c>
       <c r="F46" t="str">
-        <v>7988462840</v>
+        <v>8199005202</v>
       </c>
       <c r="G46" t="str">
-        <v>R.S public school</v>
+        <v>Govment school thasil camp panipat</v>
       </c>
       <c r="H46" t="str">
         <v>Yes</v>
@@ -4204,7 +4204,7 @@
         <v>failed</v>
       </c>
       <c r="N46" t="str">
-        <v>please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -4219,31 +4219,31 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>STUDENT_PASS_D1F0F1E1</v>
+        <v>STUDENT_PASS_ED4CCE05</v>
       </c>
       <c r="T46" t="str">
-        <v>Saved (92.0 KB)</v>
+        <v>Saved (50.6 KB)</v>
       </c>
       <c r="U46" t="str">
-        <v>rejected_guest_documents/d1f0f1e1-b2a2-4ce2-bfcc-ad89feee6706_school_id.jpg</v>
+        <v>rejected_guest_documents/ed4cce05-acd4-41c6-bd69-a38e075c659a_school_id.jpg</v>
       </c>
       <c r="V46" t="str">
-        <v>Saved (66.4 KB)</v>
+        <v>Saved (50.6 KB)</v>
       </c>
       <c r="W46" t="str">
-        <v>rejected_guest_documents/d1f0f1e1-b2a2-4ce2-bfcc-ad89feee6706_aadhar.jpg</v>
+        <v>rejected_guest_documents/ed4cce05-acd4-41c6-bd69-a38e075c659a_aadhar.jpg</v>
       </c>
       <c r="X46" t="str">
         <v>No</v>
       </c>
       <c r="Y46" t="str">
-        <v>1/10/2026, 7:29:32 pm</v>
+        <v>3/10/2026, 12:24:50 am</v>
       </c>
       <c r="Z46" t="str">
-        <v>1/10/2026, 9:47:53 pm</v>
+        <v>3/10/2026, 10:18:49 am</v>
       </c>
       <c r="AA46" t="str">
-        <v>6abe6744857a8358ce8969fc</v>
+        <v>6abffdfa54a0b78692f9664e</v>
       </c>
     </row>
     <row r="47">
@@ -4251,25 +4251,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>3e0e8fba-2187-42d1-9d0d-40e4bd299672</v>
+        <v>2f9daccf-d98b-4f16-9eac-fc7db97ab4a7</v>
       </c>
       <c r="C47" t="str">
-        <v>VINAY KUMAR</v>
+        <v>Mayank</v>
       </c>
       <c r="D47" t="str">
-        <v>vini07921@gmail.com</v>
+        <v>ranimanju38952@gmail.com</v>
       </c>
       <c r="E47" t="str">
-        <v>9034237165</v>
+        <v>9034774449</v>
       </c>
       <c r="F47" t="str">
-        <v>9034237165</v>
+        <v>9034774449</v>
       </c>
       <c r="G47" t="str">
-        <v>Navyug public school</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I47" t="str">
         <v>12th</v>
@@ -4287,7 +4287,7 @@
         <v>failed</v>
       </c>
       <c r="N47" t="str">
-        <v>Please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -4302,31 +4302,31 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>STUDENT_PASS_3E0E8FBA</v>
+        <v>STUDENT_PASS_2F9DACCF</v>
       </c>
       <c r="T47" t="str">
-        <v>Saved (279.3 KB)</v>
+        <v>Saved (71.0 KB)</v>
       </c>
       <c r="U47" t="str">
-        <v>rejected_guest_documents/3e0e8fba-2187-42d1-9d0d-40e4bd299672_school_id.jpg</v>
+        <v>rejected_guest_documents/2f9daccf-d98b-4f16-9eac-fc7db97ab4a7_school_id.jpg</v>
       </c>
       <c r="V47" t="str">
-        <v>Saved (257.3 KB)</v>
+        <v>Saved (109.8 KB)</v>
       </c>
       <c r="W47" t="str">
-        <v>rejected_guest_documents/3e0e8fba-2187-42d1-9d0d-40e4bd299672_aadhar.jpg</v>
+        <v>rejected_guest_documents/2f9daccf-d98b-4f16-9eac-fc7db97ab4a7_aadhar.jpg</v>
       </c>
       <c r="X47" t="str">
         <v>No</v>
       </c>
       <c r="Y47" t="str">
-        <v>1/10/2026, 7:07:27 pm</v>
+        <v>3/10/2026, 12:12:30 am</v>
       </c>
       <c r="Z47" t="str">
-        <v>1/10/2026, 9:45:57 pm</v>
+        <v>3/10/2026, 10:19:57 am</v>
       </c>
       <c r="AA47" t="str">
-        <v>6abe6217620ca5a5bd190ea5</v>
+        <v>6abffb1654a0b78692f96644</v>
       </c>
     </row>
     <row r="48">
@@ -4334,19 +4334,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>5083712c-9314-4bca-a84d-878b5ee276bb</v>
+        <v>23ead757-4f54-4f0f-aa5a-f63743e966ac</v>
       </c>
       <c r="C48" t="str">
-        <v>Amaan seth</v>
+        <v>Gourav</v>
       </c>
       <c r="D48" t="str">
-        <v>ganiamaan7@gmail.com</v>
+        <v>gourav89choudhary@gmail.com</v>
       </c>
       <c r="E48" t="str">
-        <v>+44919306421672</v>
+        <v>9468100014</v>
       </c>
       <c r="F48" t="str">
-        <v>+44919306421672</v>
+        <v>9468100014</v>
       </c>
       <c r="G48" t="str">
         <v>Arya Sr Sec School Panipat</v>
@@ -4370,7 +4370,7 @@
         <v>failed</v>
       </c>
       <c r="N48" t="str">
-        <v>please share proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -4385,31 +4385,31 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>STUDENT_PASS_5083712C</v>
+        <v>STUDENT_PASS_23EAD757</v>
       </c>
       <c r="T48" t="str">
-        <v>Saved (107.7 KB)</v>
+        <v>Saved (145.2 KB)</v>
       </c>
       <c r="U48" t="str">
-        <v>rejected_guest_documents/5083712c-9314-4bca-a84d-878b5ee276bb_school_id.jpg</v>
+        <v>rejected_guest_documents/23ead757-4f54-4f0f-aa5a-f63743e966ac_school_id.jpg</v>
       </c>
       <c r="V48" t="str">
-        <v>Saved (63.6 KB)</v>
+        <v>Saved (124.1 KB)</v>
       </c>
       <c r="W48" t="str">
-        <v>rejected_guest_documents/5083712c-9314-4bca-a84d-878b5ee276bb_aadhar.jpg</v>
+        <v>rejected_guest_documents/23ead757-4f54-4f0f-aa5a-f63743e966ac_aadhar.jpg</v>
       </c>
       <c r="X48" t="str">
         <v>No</v>
       </c>
       <c r="Y48" t="str">
-        <v>1/10/2026, 6:56:23 pm</v>
+        <v>2/10/2026, 11:44:11 pm</v>
       </c>
       <c r="Z48" t="str">
-        <v>1/10/2026, 9:44:28 pm</v>
+        <v>3/10/2026, 10:21:38 am</v>
       </c>
       <c r="AA48" t="str">
-        <v>6abe5f7f620ca5a5bd190e99</v>
+        <v>6abff4737edb78c219831fb4</v>
       </c>
     </row>
     <row r="49">
@@ -4417,22 +4417,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>a616579c-b696-41b9-a3db-f02e4f7fc19c</v>
+        <v>06d01bc1-2e6a-40b7-aa13-2f71e1010bfb</v>
       </c>
       <c r="C49" t="str">
-        <v>Lavish kataria</v>
+        <v>Vrinda</v>
       </c>
       <c r="D49" t="str">
-        <v>lavishkataria077@gmail.com</v>
+        <v>vrinda@09gmail.com</v>
       </c>
       <c r="E49" t="str">
-        <v>8571998221</v>
+        <v>9671095624</v>
       </c>
       <c r="F49" t="str">
-        <v>8571998221</v>
+        <v>9671095624</v>
       </c>
       <c r="G49" t="str">
-        <v>Dr mkk arya model school</v>
+        <v>Maharaja aggrsain sanatan dharm public school</v>
       </c>
       <c r="H49" t="str">
         <v>Yes</v>
@@ -4453,7 +4453,7 @@
         <v>failed</v>
       </c>
       <c r="N49" t="str">
-        <v>please share proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -4468,31 +4468,31 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>STUDENT_PASS_A616579C</v>
+        <v>STUDENT_PASS_06D01BC1</v>
       </c>
       <c r="T49" t="str">
-        <v>Saved (175.5 KB)</v>
+        <v>Saved (103.0 KB)</v>
       </c>
       <c r="U49" t="str">
-        <v>rejected_guest_documents/a616579c-b696-41b9-a3db-f02e4f7fc19c_school_id.jpg</v>
+        <v>rejected_guest_documents/06d01bc1-2e6a-40b7-aa13-2f71e1010bfb_school_id.jpg</v>
       </c>
       <c r="V49" t="str">
-        <v>Saved (251.1 KB)</v>
+        <v>Saved (216.4 KB)</v>
       </c>
       <c r="W49" t="str">
-        <v>rejected_guest_documents/a616579c-b696-41b9-a3db-f02e4f7fc19c_aadhar.jpg</v>
+        <v>rejected_guest_documents/06d01bc1-2e6a-40b7-aa13-2f71e1010bfb_aadhar.jpg</v>
       </c>
       <c r="X49" t="str">
         <v>No</v>
       </c>
       <c r="Y49" t="str">
-        <v>1/10/2026, 6:34:20 pm</v>
+        <v>2/10/2026, 11:24:40 pm</v>
       </c>
       <c r="Z49" t="str">
-        <v>1/10/2026, 9:42:44 pm</v>
+        <v>3/10/2026, 10:23:15 am</v>
       </c>
       <c r="AA49" t="str">
-        <v>6abe5a54620ca5a5bd190e8a</v>
+        <v>6abfefe07edb78c219831f75</v>
       </c>
     </row>
     <row r="50">
@@ -4500,43 +4500,43 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>55c316bf-3619-446e-a3a0-27988f118a1b</v>
+        <v>75fb55c6-c603-45a1-b695-0261c07e7b68</v>
       </c>
       <c r="C50" t="str">
-        <v>Depu Kumar</v>
+        <v>Jyoti</v>
       </c>
       <c r="D50" t="str">
-        <v>depu44330@gmail.com</v>
+        <v>mayankarora11245@gmail.com</v>
       </c>
       <c r="E50" t="str">
-        <v>8168253160</v>
+        <v>8708299100</v>
       </c>
       <c r="F50" t="str">
-        <v>8168253160</v>
+        <v>8708299100</v>
       </c>
       <c r="G50" t="str">
-        <v>CRM High School Chulkana Samalkha</v>
+        <v>DAV Police Public School Police Line Panipat</v>
       </c>
       <c r="H50" t="str">
         <v>No</v>
       </c>
       <c r="I50" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J50" t="str">
         <v>Haryana</v>
       </c>
       <c r="K50" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L50" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M50" t="str">
         <v>failed</v>
       </c>
       <c r="N50" t="str">
-        <v>Please share student ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -4551,31 +4551,31 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>STUDENT_PASS_55C316BF</v>
+        <v>STUDENT_PASS_75FB55C6</v>
       </c>
       <c r="T50" t="str">
-        <v>Saved (132.3 KB)</v>
+        <v>Saved (120.9 KB)</v>
       </c>
       <c r="U50" t="str">
-        <v>rejected_guest_documents/55c316bf-3619-446e-a3a0-27988f118a1b_school_id.jpg</v>
+        <v>rejected_guest_documents/75fb55c6-c603-45a1-b695-0261c07e7b68_school_id.jpg</v>
       </c>
       <c r="V50" t="str">
-        <v>Saved (132.3 KB)</v>
+        <v>Saved (124.1 KB)</v>
       </c>
       <c r="W50" t="str">
-        <v>rejected_guest_documents/55c316bf-3619-446e-a3a0-27988f118a1b_aadhar.jpg</v>
+        <v>rejected_guest_documents/75fb55c6-c603-45a1-b695-0261c07e7b68_aadhar.jpg</v>
       </c>
       <c r="X50" t="str">
         <v>No</v>
       </c>
       <c r="Y50" t="str">
-        <v>1/10/2026, 6:27:25 pm</v>
+        <v>2/10/2026, 11:12:50 pm</v>
       </c>
       <c r="Z50" t="str">
-        <v>1/10/2026, 9:40:44 pm</v>
+        <v>3/10/2026, 10:29:27 am</v>
       </c>
       <c r="AA50" t="str">
-        <v>6abe58b5620ca5a5bd190e7d</v>
+        <v>6abfed1a7edb78c219831f1c</v>
       </c>
     </row>
     <row r="51">
@@ -4583,22 +4583,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>b82310d9-f8a1-4fbc-b40a-5a0adbd26d2b</v>
+        <v>095793da-7bfa-497c-8f80-50ccf53df376</v>
       </c>
       <c r="C51" t="str">
-        <v>Jatin Kadyan</v>
+        <v>Shikha nagpal</v>
       </c>
       <c r="D51" t="str">
-        <v>jatinkadyanofficial@gmail.com</v>
+        <v>shikhanagpal26@gmail.com</v>
       </c>
       <c r="E51" t="str">
-        <v>9306566396</v>
+        <v>9991307957</v>
       </c>
       <c r="F51" t="str">
-        <v>9306566396</v>
+        <v>9991307957</v>
       </c>
       <c r="G51" t="str">
-        <v>Sanatan Dharam vidya mandir city panipat</v>
+        <v>Arya girls public school</v>
       </c>
       <c r="H51" t="str">
         <v>Yes</v>
@@ -4619,7 +4619,7 @@
         <v>failed</v>
       </c>
       <c r="N51" t="str">
-        <v>Please share your proper documents.</v>
+        <v>NA</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -4634,31 +4634,31 @@
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>STUDENT_PASS_B82310D9</v>
+        <v>STUDENT_PASS_095793DA</v>
       </c>
       <c r="T51" t="str">
-        <v>Saved (5.9 KB)</v>
+        <v>Saved (37.2 KB)</v>
       </c>
       <c r="U51" t="str">
-        <v>rejected_guest_documents/b82310d9-f8a1-4fbc-b40a-5a0adbd26d2b_school_id.jpg</v>
+        <v>rejected_guest_documents/095793da-7bfa-497c-8f80-50ccf53df376_school_id.jpg</v>
       </c>
       <c r="V51" t="str">
-        <v>Saved (62.9 KB)</v>
+        <v>Saved (159.2 KB)</v>
       </c>
       <c r="W51" t="str">
-        <v>rejected_guest_documents/b82310d9-f8a1-4fbc-b40a-5a0adbd26d2b_aadhar.jpg</v>
+        <v>rejected_guest_documents/095793da-7bfa-497c-8f80-50ccf53df376_aadhar.jpg</v>
       </c>
       <c r="X51" t="str">
         <v>No</v>
       </c>
       <c r="Y51" t="str">
-        <v>1/10/2026, 5:38:30 pm</v>
+        <v>2/10/2026, 11:10:44 pm</v>
       </c>
       <c r="Z51" t="str">
-        <v>1/10/2026, 9:09:24 pm</v>
+        <v>3/10/2026, 10:30:16 am</v>
       </c>
       <c r="AA51" t="str">
-        <v>6abe4d3e620ca5a5bd190e53</v>
+        <v>6abfec9c7edb78c219831f0e</v>
       </c>
     </row>
     <row r="52">
@@ -4666,22 +4666,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>35826231-e936-4b11-bca6-62b09c417221</v>
+        <v>5728d4a6-7ecb-4f21-a305-8a5b2f41a791</v>
       </c>
       <c r="C52" t="str">
-        <v>Lavish Gulati</v>
+        <v>Akash kumar</v>
       </c>
       <c r="D52" t="str">
-        <v>lavishgulati3@gmail.com</v>
+        <v>aakashkumar258258@gmail.com</v>
       </c>
       <c r="E52" t="str">
-        <v>+919729660344</v>
+        <v>8816975214</v>
       </c>
       <c r="F52" t="str">
-        <v>+919729660344</v>
+        <v>8816975214</v>
       </c>
       <c r="G52" t="str">
-        <v>Navyug school</v>
+        <v>Gsss krishnapura panipat</v>
       </c>
       <c r="H52" t="str">
         <v>Yes</v>
@@ -4702,7 +4702,7 @@
         <v>failed</v>
       </c>
       <c r="N52" t="str">
-        <v>Please share student ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -4717,31 +4717,31 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>STUDENT_PASS_35826231</v>
+        <v>STUDENT_PASS_5728D4A6</v>
       </c>
       <c r="T52" t="str">
-        <v>Saved (114.4 KB)</v>
+        <v>Saved (134.6 KB)</v>
       </c>
       <c r="U52" t="str">
-        <v>rejected_guest_documents/35826231-e936-4b11-bca6-62b09c417221_school_id.jpg</v>
+        <v>rejected_guest_documents/5728d4a6-7ecb-4f21-a305-8a5b2f41a791_school_id.jpg</v>
       </c>
       <c r="V52" t="str">
-        <v>Saved (114.1 KB)</v>
+        <v>Saved (73.4 KB)</v>
       </c>
       <c r="W52" t="str">
-        <v>rejected_guest_documents/35826231-e936-4b11-bca6-62b09c417221_aadhar.jpg</v>
+        <v>rejected_guest_documents/5728d4a6-7ecb-4f21-a305-8a5b2f41a791_aadhar.jpg</v>
       </c>
       <c r="X52" t="str">
         <v>No</v>
       </c>
       <c r="Y52" t="str">
-        <v>1/10/2026, 4:59:02 pm</v>
+        <v>2/10/2026, 11:06:56 pm</v>
       </c>
       <c r="Z52" t="str">
-        <v>1/10/2026, 5:17:57 pm</v>
+        <v>3/10/2026, 11:08:09 am</v>
       </c>
       <c r="AA52" t="str">
-        <v>6abe43fe8ddbedb68dbd6478</v>
+        <v>6abfebb87edb78c219831eee</v>
       </c>
     </row>
     <row r="53">
@@ -4749,22 +4749,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>d8084692-837a-466e-a172-da6030b82dff</v>
+        <v>5484dff6-8e1d-436b-8516-08b086f0dd68</v>
       </c>
       <c r="C53" t="str">
-        <v>Jaiyant Kadyan</v>
+        <v>Sawan</v>
       </c>
       <c r="D53" t="str">
-        <v>jaiyantofficial@gmail.com</v>
+        <v>kajalbhatti7082@gmail.com</v>
       </c>
       <c r="E53" t="str">
-        <v>9034977596</v>
+        <v>8901108346</v>
       </c>
       <c r="F53" t="str">
-        <v>9034977596</v>
+        <v>8901108346</v>
       </c>
       <c r="G53" t="str">
-        <v>Sanatan dharam vidya Mandir city panipat</v>
+        <v>Geeta Vidya mandir school nimbri panipat</v>
       </c>
       <c r="H53" t="str">
         <v>Yes</v>
@@ -4785,7 +4785,7 @@
         <v>failed</v>
       </c>
       <c r="N53" t="str">
-        <v>Please upload student ID card.</v>
+        <v>please share your proper documents.</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -4800,31 +4800,31 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>STUDENT_PASS_D8084692</v>
+        <v>STUDENT_PASS_5484DFF6</v>
       </c>
       <c r="T53" t="str">
-        <v>Saved (6.0 KB)</v>
+        <v>Saved (72.1 KB)</v>
       </c>
       <c r="U53" t="str">
-        <v>rejected_guest_documents/d8084692-837a-466e-a172-da6030b82dff_school_id.jpg</v>
+        <v>rejected_guest_documents/5484dff6-8e1d-436b-8516-08b086f0dd68_school_id.jpg</v>
       </c>
       <c r="V53" t="str">
-        <v>Saved (83.5 KB)</v>
+        <v>Saved (72.1 KB)</v>
       </c>
       <c r="W53" t="str">
-        <v>rejected_guest_documents/d8084692-837a-466e-a172-da6030b82dff_aadhar.jpg</v>
+        <v>rejected_guest_documents/5484dff6-8e1d-436b-8516-08b086f0dd68_aadhar.jpg</v>
       </c>
       <c r="X53" t="str">
         <v>No</v>
       </c>
       <c r="Y53" t="str">
-        <v>1/10/2026, 4:17:44 pm</v>
+        <v>2/10/2026, 11:06:47 pm</v>
       </c>
       <c r="Z53" t="str">
-        <v>1/10/2026, 4:35:47 pm</v>
+        <v>3/10/2026, 11:08:32 am</v>
       </c>
       <c r="AA53" t="str">
-        <v>6abe3a50008016067ea0622a</v>
+        <v>6abfebaf7edb78c219831eea</v>
       </c>
     </row>
     <row r="54">
@@ -4832,28 +4832,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>58439d9e-422d-4d10-ab62-750d95fb3d8c</v>
+        <v>d92d01bf-f4ab-48e5-9a08-15a4f1b28e70</v>
       </c>
       <c r="C54" t="str">
-        <v>Ritesh Kumar</v>
+        <v>Priya</v>
       </c>
       <c r="D54" t="str">
-        <v>riteshkumar9466652019@gmail.com</v>
+        <v>manujapriya44@gmail.com</v>
       </c>
       <c r="E54" t="str">
-        <v>9306469796</v>
+        <v>9350369824</v>
       </c>
       <c r="F54" t="str">
-        <v>9306469796</v>
+        <v>9350369824</v>
       </c>
       <c r="G54" t="str">
-        <v>SD Senior Secondary School</v>
+        <v>DAV Police Public School Police Line Panipat</v>
       </c>
       <c r="H54" t="str">
         <v>No</v>
       </c>
       <c r="I54" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J54" t="str">
         <v>Haryana</v>
@@ -4868,7 +4868,7 @@
         <v>failed</v>
       </c>
       <c r="N54" t="str">
-        <v>Upload proper douments.</v>
+        <v>please share your proper documents and please check your name.</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -4883,31 +4883,31 @@
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>STUDENT_PASS_58439D9E</v>
+        <v>STUDENT_PASS_D92D01BF</v>
       </c>
       <c r="T54" t="str">
-        <v>Saved (71.7 KB)</v>
+        <v>Saved (161.7 KB)</v>
       </c>
       <c r="U54" t="str">
-        <v>rejected_guest_documents/58439d9e-422d-4d10-ab62-750d95fb3d8c_school_id.jpg</v>
+        <v>rejected_guest_documents/d92d01bf-f4ab-48e5-9a08-15a4f1b28e70_school_id.jpg</v>
       </c>
       <c r="V54" t="str">
-        <v>Saved (105.0 KB)</v>
+        <v>Saved (157.4 KB)</v>
       </c>
       <c r="W54" t="str">
-        <v>rejected_guest_documents/58439d9e-422d-4d10-ab62-750d95fb3d8c_aadhar.jpg</v>
+        <v>rejected_guest_documents/d92d01bf-f4ab-48e5-9a08-15a4f1b28e70_aadhar.jpg</v>
       </c>
       <c r="X54" t="str">
         <v>No</v>
       </c>
       <c r="Y54" t="str">
-        <v>1/10/2026, 3:46:34 pm</v>
+        <v>2/10/2026, 11:05:36 pm</v>
       </c>
       <c r="Z54" t="str">
-        <v>1/10/2026, 5:29:21 pm</v>
+        <v>3/10/2026, 11:09:16 am</v>
       </c>
       <c r="AA54" t="str">
-        <v>6abe3302008016067ea061ce</v>
+        <v>6abfeb687edb78c219831ee3</v>
       </c>
     </row>
     <row r="55">
@@ -4915,43 +4915,43 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>b6f5684c-a832-4f69-9468-29446b6b68aa</v>
+        <v>0ef23ad7-c2fd-4c54-8899-005c7e01ef8a</v>
       </c>
       <c r="C55" t="str">
-        <v>Jatin Kadyan</v>
+        <v>Golu Banjara</v>
       </c>
       <c r="D55" t="str">
-        <v>jatinkadyanofficial@gmail.com</v>
+        <v>nayakgolu03@gmail.com</v>
       </c>
       <c r="E55" t="str">
-        <v>9306566396</v>
+        <v>9509466494</v>
       </c>
       <c r="F55" t="str">
-        <v>9306566396</v>
+        <v>9509466494</v>
       </c>
       <c r="G55" t="str">
-        <v>Sanatan Dharam vidya mandir city panipat</v>
+        <v>Universe Public Sr Sec School Jaipur</v>
       </c>
       <c r="H55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I55" t="str">
         <v>12th</v>
       </c>
       <c r="J55" t="str">
-        <v>Haryana</v>
+        <v>Rajasthan</v>
       </c>
       <c r="K55" t="str">
-        <v>Panipat</v>
+        <v>Jaipur</v>
       </c>
       <c r="L55" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Jaipur, Rajasthan</v>
       </c>
       <c r="M55" t="str">
         <v>failed</v>
       </c>
       <c r="N55" t="str">
-        <v>Please upload student ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -4966,31 +4966,31 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>STUDENT_PASS_B6F5684C</v>
+        <v>STUDENT_PASS_0EF23AD7</v>
       </c>
       <c r="T55" t="str">
-        <v>Saved (5.9 KB)</v>
+        <v>Saved (87.7 KB)</v>
       </c>
       <c r="U55" t="str">
-        <v>rejected_guest_documents/b6f5684c-a832-4f69-9468-29446b6b68aa_school_id.jpg</v>
+        <v>rejected_guest_documents/0ef23ad7-c2fd-4c54-8899-005c7e01ef8a_school_id.jpg</v>
       </c>
       <c r="V55" t="str">
-        <v>Saved (62.9 KB)</v>
+        <v>Saved (79.5 KB)</v>
       </c>
       <c r="W55" t="str">
-        <v>rejected_guest_documents/b6f5684c-a832-4f69-9468-29446b6b68aa_aadhar.jpg</v>
+        <v>rejected_guest_documents/0ef23ad7-c2fd-4c54-8899-005c7e01ef8a_aadhar.jpg</v>
       </c>
       <c r="X55" t="str">
         <v>No</v>
       </c>
       <c r="Y55" t="str">
-        <v>1/10/2026, 3:41:17 pm</v>
+        <v>2/10/2026, 11:00:20 pm</v>
       </c>
       <c r="Z55" t="str">
-        <v>1/10/2026, 4:26:35 pm</v>
+        <v>3/10/2026, 12:28:44 pm</v>
       </c>
       <c r="AA55" t="str">
-        <v>6abe31c5008016067ea061c7</v>
+        <v>6abfea2c7edb78c219831ebc</v>
       </c>
     </row>
     <row r="56">
@@ -4998,28 +4998,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>9a92beeb-3283-4f61-9a98-547ce539d05e</v>
+        <v>4f786adf-80a6-4da4-99c6-c2a9460daba9</v>
       </c>
       <c r="C56" t="str">
-        <v>Jyoti arora</v>
+        <v>Himanshu Verma</v>
       </c>
       <c r="D56" t="str">
-        <v>Jyotiarora292008@gmail.con</v>
+        <v>himashver@gmail.com</v>
       </c>
       <c r="E56" t="str">
-        <v>8708299100</v>
+        <v>7404954489</v>
       </c>
       <c r="F56" t="str">
-        <v>8708299100</v>
+        <v>7404954489</v>
       </c>
       <c r="G56" t="str">
-        <v>I.b.(L)public school</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H56" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I56" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J56" t="str">
         <v>Haryana</v>
@@ -5034,7 +5034,7 @@
         <v>failed</v>
       </c>
       <c r="N56" t="str">
-        <v>Please upload Student ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -5049,31 +5049,31 @@
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>STUDENT_PASS_9A92BEEB</v>
+        <v>STUDENT_PASS_4F786ADF</v>
       </c>
       <c r="T56" t="str">
-        <v>Saved (69.0 KB)</v>
+        <v>Saved (98.0 KB)</v>
       </c>
       <c r="U56" t="str">
-        <v>rejected_guest_documents/9a92beeb-3283-4f61-9a98-547ce539d05e_school_id.jpg</v>
+        <v>rejected_guest_documents/4f786adf-80a6-4da4-99c6-c2a9460daba9_school_id.jpg</v>
       </c>
       <c r="V56" t="str">
-        <v>Saved (123.1 KB)</v>
+        <v>Saved (50.5 KB)</v>
       </c>
       <c r="W56" t="str">
-        <v>rejected_guest_documents/9a92beeb-3283-4f61-9a98-547ce539d05e_aadhar.jpg</v>
+        <v>rejected_guest_documents/4f786adf-80a6-4da4-99c6-c2a9460daba9_aadhar.jpg</v>
       </c>
       <c r="X56" t="str">
         <v>No</v>
       </c>
       <c r="Y56" t="str">
-        <v>1/10/2026, 3:37:04 pm</v>
+        <v>2/10/2026, 10:58:32 pm</v>
       </c>
       <c r="Z56" t="str">
-        <v>1/10/2026, 4:23:57 pm</v>
+        <v>3/10/2026, 12:28:59 pm</v>
       </c>
       <c r="AA56" t="str">
-        <v>6abe30c8008016067ea061bd</v>
+        <v>6abfe9c07ef9e5b5deaae477</v>
       </c>
     </row>
     <row r="57">
@@ -5081,22 +5081,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>88f71693-f2b7-4f35-ae62-2e123b511680</v>
+        <v>89221669-8356-46ce-ac1c-47b79ddf819e</v>
       </c>
       <c r="C57" t="str">
-        <v>Paramjeet</v>
+        <v>himanshu</v>
       </c>
       <c r="D57" t="str">
-        <v>kuharparamjeet@gmail.com</v>
+        <v>hv86500@gmail.com</v>
       </c>
       <c r="E57" t="str">
-        <v>7206502324</v>
+        <v>7206756174</v>
       </c>
       <c r="F57" t="str">
-        <v>7206502324</v>
+        <v>7206756174</v>
       </c>
       <c r="G57" t="str">
-        <v>Chandan bal vikas public school</v>
+        <v>Jawahar Navodaya Vidyalaya Panipat</v>
       </c>
       <c r="H57" t="str">
         <v>Yes</v>
@@ -5108,16 +5108,16 @@
         <v>Haryana</v>
       </c>
       <c r="K57" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L57" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M57" t="str">
         <v>failed</v>
       </c>
       <c r="N57" t="str">
-        <v>Please share student ID card.</v>
+        <v>NA</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -5132,31 +5132,31 @@
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>STUDENT_PASS_88F71693</v>
+        <v>STUDENT_PASS_89221669</v>
       </c>
       <c r="T57" t="str">
-        <v>Saved (230.6 KB)</v>
+        <v>Saved (50.8 KB)</v>
       </c>
       <c r="U57" t="str">
-        <v>rejected_guest_documents/88f71693-f2b7-4f35-ae62-2e123b511680_school_id.jpg</v>
+        <v>rejected_guest_documents/89221669-8356-46ce-ac1c-47b79ddf819e_school_id.jpg</v>
       </c>
       <c r="V57" t="str">
-        <v>Saved (162.7 KB)</v>
+        <v>Saved (86.7 KB)</v>
       </c>
       <c r="W57" t="str">
-        <v>rejected_guest_documents/88f71693-f2b7-4f35-ae62-2e123b511680_aadhar.jpg</v>
+        <v>rejected_guest_documents/89221669-8356-46ce-ac1c-47b79ddf819e_aadhar.jpg</v>
       </c>
       <c r="X57" t="str">
         <v>No</v>
       </c>
       <c r="Y57" t="str">
-        <v>1/10/2026, 12:09:30 pm</v>
+        <v>2/10/2026, 10:57:34 pm</v>
       </c>
       <c r="Z57" t="str">
-        <v>1/10/2026, 12:45:18 pm</v>
+        <v>3/10/2026, 12:29:25 pm</v>
       </c>
       <c r="AA57" t="str">
-        <v>6abe0022711ab1766147eb9a</v>
+        <v>6abfe9867ef9e5b5deaae470</v>
       </c>
     </row>
     <row r="58">
@@ -5164,25 +5164,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>9ab8841c-c236-420c-a536-16e2749b8e95</v>
+        <v>4b022588-79c7-4920-9368-942dbe5e5f55</v>
       </c>
       <c r="C58" t="str">
-        <v>Jashan</v>
+        <v>Rohit</v>
       </c>
       <c r="D58" t="str">
-        <v>kartikparihar2007@gmail.com</v>
+        <v>amarsingh8059921372@gmail.com</v>
       </c>
       <c r="E58" t="str">
-        <v>9306707438</v>
+        <v>7988514138</v>
       </c>
       <c r="F58" t="str">
-        <v>9306707438</v>
+        <v>7988514138</v>
       </c>
       <c r="G58" t="str">
-        <v>Dr..MKK sr. Sec. School</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H58" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I58" t="str">
         <v>12th</v>
@@ -5200,7 +5200,7 @@
         <v>failed</v>
       </c>
       <c r="N58" t="str">
-        <v>Please upload School ID card</v>
+        <v>NA</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -5215,31 +5215,31 @@
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>STUDENT_PASS_9AB8841C</v>
+        <v>STUDENT_PASS_4B022588</v>
       </c>
       <c r="T58" t="str">
-        <v>Saved (73.4 KB)</v>
+        <v>Saved (123.8 KB)</v>
       </c>
       <c r="U58" t="str">
-        <v>rejected_guest_documents/9ab8841c-c236-420c-a536-16e2749b8e95_school_id.jpg</v>
+        <v>rejected_guest_documents/4b022588-79c7-4920-9368-942dbe5e5f55_school_id.jpg</v>
       </c>
       <c r="V58" t="str">
-        <v>Saved (73.4 KB)</v>
+        <v>Saved (44.0 KB)</v>
       </c>
       <c r="W58" t="str">
-        <v>rejected_guest_documents/9ab8841c-c236-420c-a536-16e2749b8e95_aadhar.jpg</v>
+        <v>rejected_guest_documents/4b022588-79c7-4920-9368-942dbe5e5f55_aadhar.jpg</v>
       </c>
       <c r="X58" t="str">
         <v>No</v>
       </c>
       <c r="Y58" t="str">
-        <v>1/10/2026, 11:42:34 am</v>
+        <v>2/10/2026, 10:16:20 pm</v>
       </c>
       <c r="Z58" t="str">
-        <v>1/10/2026, 11:50:24 am</v>
+        <v>3/10/2026, 11:06:46 am</v>
       </c>
       <c r="AA58" t="str">
-        <v>6abdf9d1f8ae424d39319aba</v>
+        <v>6abfdfdcc75b2c080a827ba9</v>
       </c>
     </row>
     <row r="59">
@@ -5247,28 +5247,28 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>41e61dc1-7b9a-4ed0-a713-b6d0eff4c376</v>
+        <v>abc327b2-bebf-4dfa-9f09-971629a370c3</v>
       </c>
       <c r="C59" t="str">
-        <v>Ritik kumar</v>
+        <v>Rishab</v>
       </c>
       <c r="D59" t="str">
-        <v>ritikkumarsah366@gmail.com</v>
+        <v>amanantal08@gmail.com</v>
       </c>
       <c r="E59" t="str">
-        <v>8950627476</v>
+        <v>+919315453564</v>
       </c>
       <c r="F59" t="str">
-        <v>8950627476</v>
+        <v>+919315453564</v>
       </c>
       <c r="G59" t="str">
-        <v>Arya Sr Sec School Panipat</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H59" t="str">
         <v>No</v>
       </c>
       <c r="I59" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J59" t="str">
         <v>Haryana</v>
@@ -5283,7 +5283,7 @@
         <v>failed</v>
       </c>
       <c r="N59" t="str">
-        <v>please upload correct ID card</v>
+        <v>NA</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -5298,31 +5298,31 @@
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>STUDENT_PASS_41E61DC1</v>
+        <v>STUDENT_PASS_ABC327B2</v>
       </c>
       <c r="T59" t="str">
-        <v>Saved (47.6 KB)</v>
+        <v>Saved (57.9 KB)</v>
       </c>
       <c r="U59" t="str">
-        <v>rejected_guest_documents/41e61dc1-7b9a-4ed0-a713-b6d0eff4c376_school_id.jpg</v>
+        <v>rejected_guest_documents/abc327b2-bebf-4dfa-9f09-971629a370c3_school_id.jpg</v>
       </c>
       <c r="V59" t="str">
-        <v>Saved (73.8 KB)</v>
+        <v>Saved (55.2 KB)</v>
       </c>
       <c r="W59" t="str">
-        <v>rejected_guest_documents/41e61dc1-7b9a-4ed0-a713-b6d0eff4c376_aadhar.jpg</v>
+        <v>rejected_guest_documents/abc327b2-bebf-4dfa-9f09-971629a370c3_aadhar.jpg</v>
       </c>
       <c r="X59" t="str">
         <v>No</v>
       </c>
       <c r="Y59" t="str">
-        <v>1/10/2026, 11:28:41 am</v>
+        <v>2/10/2026, 9:49:52 pm</v>
       </c>
       <c r="Z59" t="str">
-        <v>1/10/2026, 11:34:40 am</v>
+        <v>3/10/2026, 11:17:10 am</v>
       </c>
       <c r="AA59" t="str">
-        <v>6abdf691f8ae424d39319a36</v>
+        <v>6abfd9a86ef58853bae13227</v>
       </c>
     </row>
     <row r="60">
@@ -5330,22 +5330,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>cbfcc436-7c75-4235-b3c6-2ee634cc55f5</v>
+        <v>b6448fa9-e6f3-4fbe-9ead-729f08469cdd</v>
       </c>
       <c r="C60" t="str">
-        <v>Vedika</v>
+        <v>Jatin Koli</v>
       </c>
       <c r="D60" t="str">
-        <v>nagpalrajani1981@gmail.com</v>
+        <v>jatinkoli1366@gmail.com</v>
       </c>
       <c r="E60" t="str">
-        <v>9034414300</v>
+        <v>+919991836995</v>
       </c>
       <c r="F60" t="str">
-        <v>9034414300</v>
+        <v>+919991836995</v>
       </c>
       <c r="G60" t="str">
-        <v>Dr. M. K. K. Arya model school</v>
+        <v>Shri Mahabir Adarsh Sr. Sec. School</v>
       </c>
       <c r="H60" t="str">
         <v>Yes</v>
@@ -5366,7 +5366,7 @@
         <v>failed</v>
       </c>
       <c r="N60" t="str">
-        <v>you passout student of class 12th</v>
+        <v>NA</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -5381,31 +5381,31 @@
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>STUDENT_PASS_CBFCC436</v>
+        <v>STUDENT_PASS_B6448FA9</v>
       </c>
       <c r="T60" t="str">
-        <v>Saved (98.4 KB)</v>
+        <v>Saved (223.3 KB)</v>
       </c>
       <c r="U60" t="str">
-        <v>rejected_guest_documents/cbfcc436-7c75-4235-b3c6-2ee634cc55f5_school_id.jpg</v>
+        <v>rejected_guest_documents/b6448fa9-e6f3-4fbe-9ead-729f08469cdd_school_id.jpg</v>
       </c>
       <c r="V60" t="str">
-        <v>Saved (109.6 KB)</v>
+        <v>Saved (204.2 KB)</v>
       </c>
       <c r="W60" t="str">
-        <v>rejected_guest_documents/cbfcc436-7c75-4235-b3c6-2ee634cc55f5_aadhar.jpg</v>
+        <v>rejected_guest_documents/b6448fa9-e6f3-4fbe-9ead-729f08469cdd_aadhar.jpg</v>
       </c>
       <c r="X60" t="str">
         <v>No</v>
       </c>
       <c r="Y60" t="str">
-        <v>30/9/2026, 8:22:37 pm</v>
+        <v>2/10/2026, 9:40:54 pm</v>
       </c>
       <c r="Z60" t="str">
-        <v>1/10/2026, 11:18:18 am</v>
+        <v>3/10/2026, 11:17:44 am</v>
       </c>
       <c r="AA60" t="str">
-        <v>6abd2235e4dcb6569db10992</v>
+        <v>6abfd78e5a573fe1dd58fab9</v>
       </c>
     </row>
     <row r="61">
@@ -5413,22 +5413,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>0ebf464f-9a07-4310-853d-f556fbf08b72</v>
+        <v>63fdf676-7d95-45ac-a94d-dd788c69e5b3</v>
       </c>
       <c r="C61" t="str">
-        <v>Dev jaglan</v>
+        <v>Dharmveer kumar</v>
       </c>
       <c r="D61" t="str">
-        <v>devjaglan780@gmail.com</v>
+        <v>kumardharmveer9435@gmail.com</v>
       </c>
       <c r="E61" t="str">
-        <v>9813437895</v>
+        <v>8708848515</v>
       </c>
       <c r="F61" t="str">
-        <v>9813437895</v>
+        <v>8708848515</v>
       </c>
       <c r="G61" t="str">
-        <v>R.N.M.Se.Ser.school isarana (panipat)</v>
+        <v>Gyandeep Sr, Sec, School</v>
       </c>
       <c r="H61" t="str">
         <v>Yes</v>
@@ -5449,7 +5449,7 @@
         <v>failed</v>
       </c>
       <c r="N61" t="str">
-        <v>please upload 12th id card</v>
+        <v>NA</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -5464,31 +5464,31 @@
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>STUDENT_PASS_0EBF464F</v>
+        <v>STUDENT_PASS_63FDF676</v>
       </c>
       <c r="T61" t="str">
-        <v>Saved (147.8 KB)</v>
+        <v>Saved (97.9 KB)</v>
       </c>
       <c r="U61" t="str">
-        <v>rejected_guest_documents/0ebf464f-9a07-4310-853d-f556fbf08b72_school_id.jpg</v>
+        <v>rejected_guest_documents/63fdf676-7d95-45ac-a94d-dd788c69e5b3_school_id.jpg</v>
       </c>
       <c r="V61" t="str">
-        <v>Saved (147.8 KB)</v>
+        <v>Saved (105.8 KB)</v>
       </c>
       <c r="W61" t="str">
-        <v>rejected_guest_documents/0ebf464f-9a07-4310-853d-f556fbf08b72_aadhar.jpg</v>
+        <v>rejected_guest_documents/63fdf676-7d95-45ac-a94d-dd788c69e5b3_aadhar.jpg</v>
       </c>
       <c r="X61" t="str">
         <v>No</v>
       </c>
       <c r="Y61" t="str">
-        <v>30/9/2026, 6:47:46 pm</v>
+        <v>2/10/2026, 9:23:27 pm</v>
       </c>
       <c r="Z61" t="str">
-        <v>1/10/2026, 11:25:51 am</v>
+        <v>3/10/2026, 11:20:09 am</v>
       </c>
       <c r="AA61" t="str">
-        <v>6abd0bfafc212791ce097d13</v>
+        <v>6abfd3773a9e89587a0eb060</v>
       </c>
     </row>
     <row r="62">
@@ -5496,25 +5496,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>4b0082ed-67b6-4a4e-a508-d5dd4e6ee22f</v>
+        <v>1bfd6ad0-b76b-4323-85f2-d4c123b2304a</v>
       </c>
       <c r="C62" t="str">
-        <v>Keshav Lakra</v>
+        <v>Aryan Rajput</v>
       </c>
       <c r="D62" t="str">
-        <v>lakraaarti052@gmail.com</v>
+        <v>arynrjpt08@gmail.com</v>
       </c>
       <c r="E62" t="str">
-        <v>08684964577</v>
+        <v>9817018353</v>
       </c>
       <c r="F62" t="str">
-        <v>08684964577</v>
+        <v>9817018353</v>
       </c>
       <c r="G62" t="str">
-        <v>Spring era public school</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I62" t="str">
         <v>12th</v>
@@ -5523,16 +5523,16 @@
         <v>Haryana</v>
       </c>
       <c r="K62" t="str">
-        <v>Sonipat</v>
+        <v>Panipat</v>
       </c>
       <c r="L62" t="str">
-        <v>Sonipat, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M62" t="str">
         <v>failed</v>
       </c>
       <c r="N62" t="str">
-        <v>please upload Studnet ID</v>
+        <v>NA</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -5547,31 +5547,31 @@
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>STUDENT_PASS_4B0082ED</v>
+        <v>STUDENT_PASS_1BFD6AD0</v>
       </c>
       <c r="T62" t="str">
-        <v>Saved (46.6 KB)</v>
+        <v>Saved (70.2 KB)</v>
       </c>
       <c r="U62" t="str">
-        <v>rejected_guest_documents/4b0082ed-67b6-4a4e-a508-d5dd4e6ee22f_school_id.jpg</v>
+        <v>rejected_guest_documents/1bfd6ad0-b76b-4323-85f2-d4c123b2304a_school_id.jpg</v>
       </c>
       <c r="V62" t="str">
-        <v>Saved (161.5 KB)</v>
+        <v>Saved (49.1 KB)</v>
       </c>
       <c r="W62" t="str">
-        <v>rejected_guest_documents/4b0082ed-67b6-4a4e-a508-d5dd4e6ee22f_aadhar.jpg</v>
+        <v>rejected_guest_documents/1bfd6ad0-b76b-4323-85f2-d4c123b2304a_aadhar.jpg</v>
       </c>
       <c r="X62" t="str">
         <v>No</v>
       </c>
       <c r="Y62" t="str">
-        <v>30/9/2026, 6:47:41 pm</v>
+        <v>2/10/2026, 9:18:19 pm</v>
       </c>
       <c r="Z62" t="str">
-        <v>1/10/2026, 11:28:28 am</v>
+        <v>3/10/2026, 11:20:25 am</v>
       </c>
       <c r="AA62" t="str">
-        <v>6abd0bf5fc212791ce097d10</v>
+        <v>6abfd243cb951662a13369d7</v>
       </c>
     </row>
     <row r="63">
@@ -5579,22 +5579,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>79bf4cb9-d8e1-46a0-b372-6bfd79f1a565</v>
+        <v>16410d6a-67d7-4c85-baa3-9c2f454bb3fd</v>
       </c>
       <c r="C63" t="str">
-        <v>Lavish bansal</v>
+        <v>Aryan Rajput</v>
       </c>
       <c r="D63" t="str">
-        <v>lavishb207@gmail.com</v>
+        <v>arynrjpt08@gmail.com</v>
       </c>
       <c r="E63" t="str">
-        <v>7206542165</v>
+        <v>9034382104</v>
       </c>
       <c r="F63" t="str">
-        <v>7206542165</v>
+        <v>9034382104</v>
       </c>
       <c r="G63" t="str">
-        <v>SD Public School Narwana</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H63" t="str">
         <v>No</v>
@@ -5606,16 +5606,16 @@
         <v>Haryana</v>
       </c>
       <c r="K63" t="str">
-        <v>Narwana</v>
+        <v>Panipat</v>
       </c>
       <c r="L63" t="str">
-        <v>Narwana, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M63" t="str">
         <v>failed</v>
       </c>
       <c r="N63" t="str">
-        <v>please upload School ID</v>
+        <v>NA</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -5630,31 +5630,31 @@
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>STUDENT_PASS_79BF4CB9</v>
+        <v>STUDENT_PASS_16410D6A</v>
       </c>
       <c r="T63" t="str">
-        <v>Saved (121.5 KB)</v>
+        <v>Saved (70.2 KB)</v>
       </c>
       <c r="U63" t="str">
-        <v>rejected_guest_documents/79bf4cb9-d8e1-46a0-b372-6bfd79f1a565_school_id.jpg</v>
+        <v>rejected_guest_documents/16410d6a-67d7-4c85-baa3-9c2f454bb3fd_school_id.jpg</v>
       </c>
       <c r="V63" t="str">
-        <v>Saved (104.5 KB)</v>
+        <v>Saved (49.1 KB)</v>
       </c>
       <c r="W63" t="str">
-        <v>rejected_guest_documents/79bf4cb9-d8e1-46a0-b372-6bfd79f1a565_aadhar.jpg</v>
+        <v>rejected_guest_documents/16410d6a-67d7-4c85-baa3-9c2f454bb3fd_aadhar.jpg</v>
       </c>
       <c r="X63" t="str">
         <v>No</v>
       </c>
       <c r="Y63" t="str">
-        <v>30/9/2026, 3:23:55 pm</v>
+        <v>2/10/2026, 9:16:59 pm</v>
       </c>
       <c r="Z63" t="str">
-        <v>1/10/2026, 11:46:52 am</v>
+        <v>3/10/2026, 11:20:59 am</v>
       </c>
       <c r="AA63" t="str">
-        <v>6abcdc331119fc00122e662e</v>
+        <v>6abfd1f3cb951662a13369d1</v>
       </c>
     </row>
     <row r="64">
@@ -5662,43 +5662,43 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>ef85d2ea-28b0-4ec0-a8e2-d532bdaec146</v>
+        <v>4f291640-e71f-438a-828c-80a1c878b804</v>
       </c>
       <c r="C64" t="str">
-        <v>Kanika panwar</v>
+        <v>Mohd Aasif</v>
       </c>
       <c r="D64" t="str">
-        <v>kuldeep.kanika2010@gmail.com</v>
+        <v>aasifkhark4@gmail.com</v>
       </c>
       <c r="E64" t="str">
-        <v>7906255605</v>
+        <v>8571895972</v>
       </c>
       <c r="F64" t="str">
-        <v>7906255605</v>
+        <v>8571895972</v>
       </c>
       <c r="G64" t="str">
-        <v>Jai parvati global school</v>
+        <v>Government Model Sanskriti Sr. Sec. School Israna, Panipat</v>
       </c>
       <c r="H64" t="str">
         <v>Yes</v>
       </c>
       <c r="I64" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J64" t="str">
-        <v>Uttar Pradesh</v>
+        <v>Haryana</v>
       </c>
       <c r="K64" t="str">
-        <v>Shamli</v>
+        <v>Panipat</v>
       </c>
       <c r="L64" t="str">
-        <v>Shamli, Uttar Pradesh</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M64" t="str">
         <v>failed</v>
       </c>
       <c r="N64" t="str">
-        <v>Please share school id card photo</v>
+        <v>NA</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -5713,31 +5713,31 @@
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>STUDENT_PASS_EF85D2EA</v>
+        <v>STUDENT_PASS_4F291640</v>
       </c>
       <c r="T64" t="str">
-        <v>Saved (49.4 KB)</v>
+        <v>Saved (76.2 KB)</v>
       </c>
       <c r="U64" t="str">
-        <v>rejected_guest_documents/ef85d2ea-28b0-4ec0-a8e2-d532bdaec146_school_id.jpg</v>
+        <v>rejected_guest_documents/4f291640-e71f-438a-828c-80a1c878b804_school_id.jpg</v>
       </c>
       <c r="V64" t="str">
-        <v>Saved (127.7 KB)</v>
+        <v>Saved (142.0 KB)</v>
       </c>
       <c r="W64" t="str">
-        <v>rejected_guest_documents/ef85d2ea-28b0-4ec0-a8e2-d532bdaec146_aadhar.jpg</v>
+        <v>rejected_guest_documents/4f291640-e71f-438a-828c-80a1c878b804_aadhar.jpg</v>
       </c>
       <c r="X64" t="str">
         <v>No</v>
       </c>
       <c r="Y64" t="str">
-        <v>30/9/2026, 2:10:18 pm</v>
+        <v>2/10/2026, 8:21:25 pm</v>
       </c>
       <c r="Z64" t="str">
-        <v>30/9/2026, 2:39:08 pm</v>
+        <v>3/10/2026, 11:27:45 am</v>
       </c>
       <c r="AA64" t="str">
-        <v>6abccaf2a039e3629411cfff</v>
+        <v>6abfc4ed94af8bf10a1b23ca</v>
       </c>
     </row>
     <row r="65">
@@ -5745,28 +5745,28 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>1db7b434-4754-4075-b684-eaba609a53df</v>
+        <v>8c2029fc-eeca-4140-b838-2a037271cefc</v>
       </c>
       <c r="C65" t="str">
-        <v>Jatin Sharma</v>
+        <v>Diya goel</v>
       </c>
       <c r="D65" t="str">
-        <v>s.jatin.gautam@gmail.com</v>
+        <v>kansalvardaan00@gmail.com</v>
       </c>
       <c r="E65" t="str">
-        <v>7015165157</v>
+        <v>9255920135</v>
       </c>
       <c r="F65" t="str">
-        <v>7015165157</v>
+        <v>9255920135</v>
       </c>
       <c r="G65" t="str">
-        <v>Arya Sr Sec School Panipat</v>
+        <v>SD Modern Sr Sec School Panipat</v>
       </c>
       <c r="H65" t="str">
         <v>No</v>
       </c>
       <c r="I65" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J65" t="str">
         <v>Haryana</v>
@@ -5796,31 +5796,31 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>STUDENT_PASS_1DB7B434</v>
+        <v>STUDENT_PASS_8C2029FC</v>
       </c>
       <c r="T65" t="str">
-        <v>Saved (87.4 KB)</v>
+        <v>Saved (169.0 KB)</v>
       </c>
       <c r="U65" t="str">
-        <v>rejected_guest_documents/1db7b434-4754-4075-b684-eaba609a53df_school_id.jpg</v>
+        <v>rejected_guest_documents/8c2029fc-eeca-4140-b838-2a037271cefc_school_id.jpg</v>
       </c>
       <c r="V65" t="str">
-        <v>Saved (60.1 KB)</v>
+        <v>Saved (296.5 KB)</v>
       </c>
       <c r="W65" t="str">
-        <v>rejected_guest_documents/1db7b434-4754-4075-b684-eaba609a53df_aadhar.jpg</v>
+        <v>rejected_guest_documents/8c2029fc-eeca-4140-b838-2a037271cefc_aadhar.jpg</v>
       </c>
       <c r="X65" t="str">
         <v>No</v>
       </c>
       <c r="Y65" t="str">
-        <v>30/9/2026, 1:45:49 pm</v>
+        <v>2/10/2026, 7:58:34 pm</v>
       </c>
       <c r="Z65" t="str">
-        <v>2/10/2026, 3:24:17 pm</v>
+        <v>3/10/2026, 11:31:00 am</v>
       </c>
       <c r="AA65" t="str">
-        <v>6abcc535083b87ff8a3f636a</v>
+        <v>6abfbf9294af8bf10a1b23c1</v>
       </c>
     </row>
     <row r="66">
@@ -5828,22 +5828,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>1e640bf2-8f0c-49cd-8181-f9208c09a885</v>
+        <v>bb54a14e-1045-4b32-adea-852b33baaf5d</v>
       </c>
       <c r="C66" t="str">
-        <v>DHRUV PANWAR</v>
+        <v>Jatin Sharma</v>
       </c>
       <c r="D66" t="str">
-        <v>djpanwar90@gmail.com</v>
+        <v>s.jatin.gautam@gmail.com</v>
       </c>
       <c r="E66" t="str">
-        <v>8930132852</v>
+        <v>7015165157</v>
       </c>
       <c r="F66" t="str">
-        <v>8930132852</v>
+        <v>7015165157</v>
       </c>
       <c r="G66" t="str">
-        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
+        <v>Arya Sr Sec School Panipat</v>
       </c>
       <c r="H66" t="str">
         <v>No</v>
@@ -5864,7 +5864,7 @@
         <v>failed</v>
       </c>
       <c r="N66" t="str">
-        <v>NA</v>
+        <v>please share your proper documents.</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -5879,31 +5879,31 @@
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>STUDENT_PASS_1E640BF2</v>
+        <v>STUDENT_PASS_BB54A14E</v>
       </c>
       <c r="T66" t="str">
-        <v>Saved (80.5 KB)</v>
+        <v>Saved (87.4 KB)</v>
       </c>
       <c r="U66" t="str">
-        <v>rejected_guest_documents/1e640bf2-8f0c-49cd-8181-f9208c09a885_school_id.jpg</v>
+        <v>rejected_guest_documents/bb54a14e-1045-4b32-adea-852b33baaf5d_school_id.jpg</v>
       </c>
       <c r="V66" t="str">
-        <v>Saved (114.4 KB)</v>
+        <v>Saved (60.1 KB)</v>
       </c>
       <c r="W66" t="str">
-        <v>rejected_guest_documents/1e640bf2-8f0c-49cd-8181-f9208c09a885_aadhar.jpg</v>
+        <v>rejected_guest_documents/bb54a14e-1045-4b32-adea-852b33baaf5d_aadhar.jpg</v>
       </c>
       <c r="X66" t="str">
         <v>No</v>
       </c>
       <c r="Y66" t="str">
-        <v>30/9/2026, 1:39:50 pm</v>
+        <v>2/10/2026, 7:56:37 pm</v>
       </c>
       <c r="Z66" t="str">
-        <v>2/10/2026, 3:22:42 pm</v>
+        <v>3/10/2026, 11:32:17 am</v>
       </c>
       <c r="AA66" t="str">
-        <v>6abcc3cea039e3629411cfed</v>
+        <v>6abfbf1d94af8bf10a1b23be</v>
       </c>
     </row>
     <row r="67">
@@ -5911,28 +5911,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>9850c90a-a1fd-4540-a0b2-bb7400bc9b3c</v>
+        <v>0c60e62d-5247-428d-b4b0-341c65ecc9dd</v>
       </c>
       <c r="C67" t="str">
-        <v>ANUJ</v>
+        <v>Savleen Kaur</v>
       </c>
       <c r="D67" t="str">
-        <v>anujsaini7969@gmail.com</v>
+        <v>kaursavi2191@gmail.com</v>
       </c>
       <c r="E67" t="str">
-        <v>9466796949</v>
+        <v>8059769171</v>
       </c>
       <c r="F67" t="str">
-        <v>9466796949</v>
+        <v>8059769171</v>
       </c>
       <c r="G67" t="str">
-        <v>Seva siksha sadan school</v>
+        <v>SD Vidya mandir city</v>
       </c>
       <c r="H67" t="str">
         <v>Yes</v>
       </c>
       <c r="I67" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J67" t="str">
         <v>Haryana</v>
@@ -5962,31 +5962,31 @@
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>STUDENT_PASS_9850C90A</v>
+        <v>STUDENT_PASS_0C60E62D</v>
       </c>
       <c r="T67" t="str">
-        <v>Saved (66.1 KB)</v>
+        <v>Saved (211.9 KB)</v>
       </c>
       <c r="U67" t="str">
-        <v>rejected_guest_documents/9850c90a-a1fd-4540-a0b2-bb7400bc9b3c_school_id.jpg</v>
+        <v>rejected_guest_documents/0c60e62d-5247-428d-b4b0-341c65ecc9dd_school_id.jpg</v>
       </c>
       <c r="V67" t="str">
-        <v>Saved (176.1 KB)</v>
+        <v>Saved (201.5 KB)</v>
       </c>
       <c r="W67" t="str">
-        <v>rejected_guest_documents/9850c90a-a1fd-4540-a0b2-bb7400bc9b3c_aadhar.jpg</v>
+        <v>rejected_guest_documents/0c60e62d-5247-428d-b4b0-341c65ecc9dd_aadhar.jpg</v>
       </c>
       <c r="X67" t="str">
         <v>No</v>
       </c>
       <c r="Y67" t="str">
-        <v>30/9/2026, 12:39:15 pm</v>
+        <v>2/10/2026, 7:54:36 pm</v>
       </c>
       <c r="Z67" t="str">
-        <v>2/10/2026, 3:22:15 pm</v>
+        <v>3/10/2026, 11:32:49 am</v>
       </c>
       <c r="AA67" t="str">
-        <v>6abcb59bc219be34be1f5cc0</v>
+        <v>6abfbea47225d9a2ec9349d2</v>
       </c>
     </row>
     <row r="68">
@@ -5994,25 +5994,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>8856df2f-d895-414d-b70c-94cb7bacbd62</v>
+        <v>e81d632c-3651-4673-87a5-8eea4fb12c99</v>
       </c>
       <c r="C68" t="str">
-        <v>Keshav singla</v>
+        <v>Vardaan Kansal</v>
       </c>
       <c r="D68" t="str">
-        <v>singlak622@gmail.com</v>
+        <v>kansalvardaan00@gmail.com</v>
       </c>
       <c r="E68" t="str">
-        <v>7015661901</v>
+        <v>9255920135</v>
       </c>
       <c r="F68" t="str">
-        <v>7015661901</v>
+        <v>9255920135</v>
       </c>
       <c r="G68" t="str">
-        <v>Holy family convent school</v>
+        <v>SD Modern Sr Sec School Panipat</v>
       </c>
       <c r="H68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I68" t="str">
         <v>11th</v>
@@ -6021,16 +6021,16 @@
         <v>Haryana</v>
       </c>
       <c r="K68" t="str">
-        <v>Gohana</v>
+        <v>Panipat</v>
       </c>
       <c r="L68" t="str">
-        <v>Gohana, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M68" t="str">
         <v>failed</v>
       </c>
       <c r="N68" t="str">
-        <v>not eligible</v>
+        <v>NA</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -6045,31 +6045,31 @@
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>STUDENT_PASS_8856DF2F</v>
+        <v>STUDENT_PASS_E81D632C</v>
       </c>
       <c r="T68" t="str">
-        <v>Saved (213.4 KB)</v>
+        <v>Saved (169.0 KB)</v>
       </c>
       <c r="U68" t="str">
-        <v>rejected_guest_documents/8856df2f-d895-414d-b70c-94cb7bacbd62_school_id.jpg</v>
+        <v>rejected_guest_documents/e81d632c-3651-4673-87a5-8eea4fb12c99_school_id.jpg</v>
       </c>
       <c r="V68" t="str">
-        <v>Saved (212.8 KB)</v>
+        <v>Saved (296.5 KB)</v>
       </c>
       <c r="W68" t="str">
-        <v>rejected_guest_documents/8856df2f-d895-414d-b70c-94cb7bacbd62_aadhar.jpg</v>
+        <v>rejected_guest_documents/e81d632c-3651-4673-87a5-8eea4fb12c99_aadhar.jpg</v>
       </c>
       <c r="X68" t="str">
         <v>No</v>
       </c>
       <c r="Y68" t="str">
-        <v>30/9/2026, 10:57:09 am</v>
+        <v>2/10/2026, 7:49:13 pm</v>
       </c>
       <c r="Z68" t="str">
-        <v>30/9/2026, 12:56:16 pm</v>
+        <v>3/10/2026, 11:34:20 am</v>
       </c>
       <c r="AA68" t="str">
-        <v>6abc9dad8f1aecbf8ef6ff13</v>
+        <v>6abfbd617225d9a2ec9349c9</v>
       </c>
     </row>
     <row r="69">
@@ -6077,28 +6077,28 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>977f3891-c857-4c21-a938-cbe94ef88906</v>
+        <v>f3100d15-fa0b-4671-8eda-a5c33b80e58d</v>
       </c>
       <c r="C69" t="str">
-        <v>Nikhil arora</v>
+        <v>Vardaan Kansal</v>
       </c>
       <c r="D69" t="str">
-        <v>na4570183@gmail.com</v>
+        <v>kansalvardaan00@gmail.com</v>
       </c>
       <c r="E69" t="str">
-        <v>9053938601</v>
+        <v>9255920135</v>
       </c>
       <c r="F69" t="str">
-        <v>9053938601</v>
+        <v>9255920135</v>
       </c>
       <c r="G69" t="str">
-        <v>I.B.(l) public school</v>
+        <v>SD Modern Sr Sec School Panipat</v>
       </c>
       <c r="H69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I69" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J69" t="str">
         <v>Haryana</v>
@@ -6113,7 +6113,7 @@
         <v>failed</v>
       </c>
       <c r="N69" t="str">
-        <v>not eligible</v>
+        <v>NA</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -6128,31 +6128,31 @@
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>STUDENT_PASS_977F3891</v>
+        <v>STUDENT_PASS_F3100D15</v>
       </c>
       <c r="T69" t="str">
-        <v>Saved (114.2 KB)</v>
+        <v>Saved (169.0 KB)</v>
       </c>
       <c r="U69" t="str">
-        <v>rejected_guest_documents/977f3891-c857-4c21-a938-cbe94ef88906_school_id.jpg</v>
+        <v>rejected_guest_documents/f3100d15-fa0b-4671-8eda-a5c33b80e58d_school_id.jpg</v>
       </c>
       <c r="V69" t="str">
-        <v>Saved (22.6 KB)</v>
+        <v>Saved (296.5 KB)</v>
       </c>
       <c r="W69" t="str">
-        <v>rejected_guest_documents/977f3891-c857-4c21-a938-cbe94ef88906_aadhar.jpg</v>
+        <v>rejected_guest_documents/f3100d15-fa0b-4671-8eda-a5c33b80e58d_aadhar.jpg</v>
       </c>
       <c r="X69" t="str">
         <v>No</v>
       </c>
       <c r="Y69" t="str">
-        <v>30/9/2026, 10:21:08 am</v>
+        <v>2/10/2026, 7:49:00 pm</v>
       </c>
       <c r="Z69" t="str">
-        <v>30/9/2026, 12:55:16 pm</v>
+        <v>3/10/2026, 11:34:41 am</v>
       </c>
       <c r="AA69" t="str">
-        <v>6abc953c8f1aecbf8ef6fe8b</v>
+        <v>6abfbd547225d9a2ec9349c6</v>
       </c>
     </row>
     <row r="70">
@@ -6160,22 +6160,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>a3ff163c-19b1-4d93-abf2-ca2faf158f9d</v>
+        <v>f683e013-8344-4c82-8ade-39ab42dfb46b</v>
       </c>
       <c r="C70" t="str">
-        <v>Nikhil arora</v>
+        <v>Nitin kadyan</v>
       </c>
       <c r="D70" t="str">
-        <v>na4570183@gmail.com</v>
+        <v>nitinkadyan73@gmail.com</v>
       </c>
       <c r="E70" t="str">
-        <v>9053938601</v>
+        <v>7404433194</v>
       </c>
       <c r="F70" t="str">
-        <v>9053938601</v>
+        <v>7404433194</v>
       </c>
       <c r="G70" t="str">
-        <v>DAV Huda Panipat</v>
+        <v>Arya Sr Sec School Panipat</v>
       </c>
       <c r="H70" t="str">
         <v>No</v>
@@ -6196,7 +6196,7 @@
         <v>failed</v>
       </c>
       <c r="N70" t="str">
-        <v>PLease upload DAV HUda ID card</v>
+        <v>NA</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -6211,31 +6211,31 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>STUDENT_PASS_A3FF163C</v>
+        <v>STUDENT_PASS_F683E013</v>
       </c>
       <c r="T70" t="str">
-        <v>Saved (114.2 KB)</v>
+        <v>Saved (136.9 KB)</v>
       </c>
       <c r="U70" t="str">
-        <v>rejected_guest_documents/a3ff163c-19b1-4d93-abf2-ca2faf158f9d_school_id.jpg</v>
+        <v>rejected_guest_documents/f683e013-8344-4c82-8ade-39ab42dfb46b_school_id.jpg</v>
       </c>
       <c r="V70" t="str">
-        <v>Saved (31.3 KB)</v>
+        <v>Saved (135.0 KB)</v>
       </c>
       <c r="W70" t="str">
-        <v>rejected_guest_documents/a3ff163c-19b1-4d93-abf2-ca2faf158f9d_aadhar.jpg</v>
+        <v>rejected_guest_documents/f683e013-8344-4c82-8ade-39ab42dfb46b_aadhar.jpg</v>
       </c>
       <c r="X70" t="str">
         <v>No</v>
       </c>
       <c r="Y70" t="str">
-        <v>30/9/2026, 9:55:55 am</v>
+        <v>2/10/2026, 7:16:43 pm</v>
       </c>
       <c r="Z70" t="str">
-        <v>30/9/2026, 10:03:10 am</v>
+        <v>3/10/2026, 11:37:00 am</v>
       </c>
       <c r="AA70" t="str">
-        <v>6abc8f528f1aecbf8ef6fdee</v>
+        <v>6abfb5c3024f6ad9ec22d540</v>
       </c>
     </row>
     <row r="71">
@@ -6243,22 +6243,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>4c731feb-5baa-4f5d-95e7-0e0e4b578032</v>
+        <v>f6ef6bbf-31cc-4fa6-bd59-28d02bf5d872</v>
       </c>
       <c r="C71" t="str">
-        <v>Aaditya Kumar</v>
+        <v>Lucky Ali</v>
       </c>
       <c r="D71" t="str">
-        <v>sahanisonia717@gmail.com</v>
+        <v>luckykhark05@gmail.com</v>
       </c>
       <c r="E71" t="str">
-        <v>9254556364</v>
+        <v>7082671024</v>
       </c>
       <c r="F71" t="str">
-        <v>9254556364</v>
+        <v>7082671024</v>
       </c>
       <c r="G71" t="str">
-        <v>Government senior secondary school Krishanpura</v>
+        <v>Govt Model Sanskriti Sr Sec School Israna Panipat</v>
       </c>
       <c r="H71" t="str">
         <v>Yes</v>
@@ -6279,7 +6279,7 @@
         <v>failed</v>
       </c>
       <c r="N71" t="str">
-        <v>NA</v>
+        <v>Na</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>STUDENT_PASS_4C731FEB</v>
+        <v>STUDENT_PASS_F6EF6BBF</v>
       </c>
       <c r="T71" t="str">
-        <v>Saved (165.5 KB)</v>
+        <v>Saved (89.0 KB)</v>
       </c>
       <c r="U71" t="str">
-        <v>rejected_guest_documents/4c731feb-5baa-4f5d-95e7-0e0e4b578032_school_id.jpg</v>
+        <v>rejected_guest_documents/f6ef6bbf-31cc-4fa6-bd59-28d02bf5d872_school_id.jpg</v>
       </c>
       <c r="V71" t="str">
-        <v>Saved (82.7 KB)</v>
+        <v>Saved (143.0 KB)</v>
       </c>
       <c r="W71" t="str">
-        <v>rejected_guest_documents/4c731feb-5baa-4f5d-95e7-0e0e4b578032_aadhar.jpg</v>
+        <v>rejected_guest_documents/f6ef6bbf-31cc-4fa6-bd59-28d02bf5d872_aadhar.jpg</v>
       </c>
       <c r="X71" t="str">
         <v>No</v>
       </c>
       <c r="Y71" t="str">
-        <v>30/9/2026, 9:46:57 am</v>
+        <v>2/10/2026, 6:53:44 pm</v>
       </c>
       <c r="Z71" t="str">
-        <v>2/10/2026, 3:21:56 pm</v>
+        <v>3/10/2026, 11:38:15 am</v>
       </c>
       <c r="AA71" t="str">
-        <v>6abc8d39af3e21b61e1dacde</v>
+        <v>6abfb060d14b9c464c2938f2</v>
       </c>
     </row>
     <row r="72">
@@ -6326,25 +6326,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>7d6e6845-7227-4405-9577-6276de3a8643</v>
+        <v>c29a6cec-db35-4149-a987-f52be181c6dd</v>
       </c>
       <c r="C72" t="str">
-        <v>Amit sharma</v>
+        <v>Vansh rawal</v>
       </c>
       <c r="D72" t="str">
-        <v>amitsharma721286@gmail.com</v>
+        <v>khatanareetu0@gmail.com</v>
       </c>
       <c r="E72" t="str">
-        <v>8756835463</v>
+        <v>7027017157</v>
       </c>
       <c r="F72" t="str">
-        <v>8756835463</v>
+        <v>7027017157</v>
       </c>
       <c r="G72" t="str">
-        <v>SVN</v>
+        <v>Aarohi Model Sr Sec School Chhajpur Kalan Panipat</v>
       </c>
       <c r="H72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I72" t="str">
         <v>12th</v>
@@ -6353,16 +6353,16 @@
         <v>Haryana</v>
       </c>
       <c r="K72" t="str">
-        <v>Shamli</v>
+        <v>Panipat</v>
       </c>
       <c r="L72" t="str">
-        <v>Shamli, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M72" t="str">
         <v>failed</v>
       </c>
       <c r="N72" t="str">
-        <v>fake id card</v>
+        <v>NA</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -6377,31 +6377,31 @@
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>STUDENT_PASS_7D6E6845</v>
+        <v>STUDENT_PASS_C29A6CEC</v>
       </c>
       <c r="T72" t="str">
-        <v>Saved (6.1 KB)</v>
+        <v>Saved (87.0 KB)</v>
       </c>
       <c r="U72" t="str">
-        <v>rejected_guest_documents/7d6e6845-7227-4405-9577-6276de3a8643_school_id.jpg</v>
+        <v>rejected_guest_documents/c29a6cec-db35-4149-a987-f52be181c6dd_school_id.jpg</v>
       </c>
       <c r="V72" t="str">
-        <v>Saved (6.1 KB)</v>
+        <v>Saved (207.5 KB)</v>
       </c>
       <c r="W72" t="str">
-        <v>rejected_guest_documents/7d6e6845-7227-4405-9577-6276de3a8643_aadhar.jpg</v>
+        <v>rejected_guest_documents/c29a6cec-db35-4149-a987-f52be181c6dd_aadhar.jpg</v>
       </c>
       <c r="X72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="Y72" t="str">
-        <v>30/9/2026, 9:03:47 am</v>
+        <v>2/10/2026, 6:27:09 pm</v>
       </c>
       <c r="Z72" t="str">
-        <v>30/9/2026, 9:04:34 am</v>
+        <v>3/10/2026, 11:39:20 am</v>
       </c>
       <c r="AA72" t="str">
-        <v>6abc831bfd1407dc1a69f94d</v>
+        <v>6abfaa25d14b9c464c2938e8</v>
       </c>
     </row>
     <row r="73">
@@ -6409,25 +6409,25 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>8679a67e-3dc9-4fbf-b14b-74edbd04b7c0</v>
+        <v>fd08660e-984c-4fd2-9405-9e49ffdb07a3</v>
       </c>
       <c r="C73" t="str">
-        <v>Ibl public school</v>
+        <v>Nikshay</v>
       </c>
       <c r="D73" t="str">
-        <v>na4570183@gmail.com</v>
+        <v>nikusharma77tt@gmail.com</v>
       </c>
       <c r="E73" t="str">
-        <v>9053938601</v>
+        <v>7404290565</v>
       </c>
       <c r="F73" t="str">
-        <v>9053938601</v>
+        <v>7404290565</v>
       </c>
       <c r="G73" t="str">
-        <v>DAV Huda Panipat</v>
+        <v>Savitri shiksha sadan sr sec school</v>
       </c>
       <c r="H73" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I73" t="str">
         <v>12th</v>
@@ -6445,7 +6445,7 @@
         <v>failed</v>
       </c>
       <c r="N73" t="str">
-        <v>Please upload you DAV huda ID card</v>
+        <v>NA</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -6460,31 +6460,31 @@
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>STUDENT_PASS_8679A67E</v>
+        <v>STUDENT_PASS_FD08660E</v>
       </c>
       <c r="T73" t="str">
-        <v>Saved (114.2 KB)</v>
+        <v>Saved (121.4 KB)</v>
       </c>
       <c r="U73" t="str">
-        <v>rejected_guest_documents/8679a67e-3dc9-4fbf-b14b-74edbd04b7c0_school_id.jpg</v>
+        <v>rejected_guest_documents/fd08660e-984c-4fd2-9405-9e49ffdb07a3_school_id.jpg</v>
       </c>
       <c r="V73" t="str">
-        <v>Saved (22.6 KB)</v>
+        <v>Saved (80.1 KB)</v>
       </c>
       <c r="W73" t="str">
-        <v>rejected_guest_documents/8679a67e-3dc9-4fbf-b14b-74edbd04b7c0_aadhar.jpg</v>
+        <v>rejected_guest_documents/fd08660e-984c-4fd2-9405-9e49ffdb07a3_aadhar.jpg</v>
       </c>
       <c r="X73" t="str">
         <v>No</v>
       </c>
       <c r="Y73" t="str">
-        <v>30/9/2026, 8:50:04 am</v>
+        <v>2/10/2026, 5:44:52 pm</v>
       </c>
       <c r="Z73" t="str">
-        <v>30/9/2026, 10:04:23 am</v>
+        <v>3/10/2026, 12:10:25 pm</v>
       </c>
       <c r="AA73" t="str">
-        <v>6abc7fe4fd1407dc1a69f945</v>
+        <v>6abfa03cd9286e3efe7ea984</v>
       </c>
     </row>
     <row r="74">
@@ -6492,22 +6492,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>05aa22a8-e580-4e4c-bef0-5a777fdf6f39</v>
+        <v>75bdf91d-6b51-452f-87e3-3d7d6b34ac00</v>
       </c>
       <c r="C74" t="str">
-        <v>Manit</v>
+        <v>Apurva</v>
       </c>
       <c r="D74" t="str">
-        <v>neerajkumar6636ygrj@gmail.com</v>
+        <v>apurvakapoor87@gmail.com</v>
       </c>
       <c r="E74" t="str">
-        <v>8818044051</v>
+        <v>9992340017</v>
       </c>
       <c r="F74" t="str">
-        <v>8818044051</v>
+        <v>9992340017</v>
       </c>
       <c r="G74" t="str">
-        <v>Gohana city</v>
+        <v>Govt model sanskriti senior secondary School israna Panipat</v>
       </c>
       <c r="H74" t="str">
         <v>Yes</v>
@@ -6519,10 +6519,10 @@
         <v>Haryana</v>
       </c>
       <c r="K74" t="str">
-        <v>Gohana</v>
+        <v>Panipat</v>
       </c>
       <c r="L74" t="str">
-        <v>Gohana, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M74" t="str">
         <v>failed</v>
@@ -6543,31 +6543,31 @@
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>STUDENT_PASS_05AA22A8</v>
+        <v>STUDENT_PASS_75BDF91D</v>
       </c>
       <c r="T74" t="str">
-        <v>Saved (112.8 KB)</v>
+        <v>Saved (85.6 KB)</v>
       </c>
       <c r="U74" t="str">
-        <v>rejected_guest_documents/05aa22a8-e580-4e4c-bef0-5a777fdf6f39_school_id.jpg</v>
+        <v>rejected_guest_documents/75bdf91d-6b51-452f-87e3-3d7d6b34ac00_school_id.jpg</v>
       </c>
       <c r="V74" t="str">
-        <v>Saved (97.4 KB)</v>
+        <v>Saved (69.2 KB)</v>
       </c>
       <c r="W74" t="str">
-        <v>rejected_guest_documents/05aa22a8-e580-4e4c-bef0-5a777fdf6f39_aadhar.jpg</v>
+        <v>rejected_guest_documents/75bdf91d-6b51-452f-87e3-3d7d6b34ac00_aadhar.jpg</v>
       </c>
       <c r="X74" t="str">
         <v>No</v>
       </c>
       <c r="Y74" t="str">
-        <v>29/9/2026, 9:25:14 pm</v>
+        <v>2/10/2026, 5:37:06 pm</v>
       </c>
       <c r="Z74" t="str">
-        <v>2/10/2026, 3:21:42 pm</v>
+        <v>3/10/2026, 12:10:38 pm</v>
       </c>
       <c r="AA74" t="str">
-        <v>6abbdf62c607490a6a5a0cee</v>
+        <v>6abf9e6ad9286e3efe7ea981</v>
       </c>
     </row>
     <row r="75">
@@ -6575,25 +6575,25 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>dbfe4113-614a-4209-b00c-fc7bd3c92c35</v>
+        <v>f2ef40a0-6020-4574-b706-7bb00cc9b35e</v>
       </c>
       <c r="C75" t="str">
-        <v>Shubham</v>
+        <v>Vishal</v>
       </c>
       <c r="D75" t="str">
-        <v>shubhamsharma08676@gmail.com</v>
+        <v>harshattri031204@gmail.com</v>
       </c>
       <c r="E75" t="str">
-        <v>8307724600</v>
+        <v>9138604638</v>
       </c>
       <c r="F75" t="str">
-        <v>8307724600</v>
+        <v>9138604638</v>
       </c>
       <c r="G75" t="str">
-        <v>Maharaja agersan public school</v>
+        <v>gyandeep senior secondary school</v>
       </c>
       <c r="H75" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I75" t="str">
         <v>12th</v>
@@ -6602,16 +6602,16 @@
         <v>Haryana</v>
       </c>
       <c r="K75" t="str">
-        <v>Samalkha</v>
+        <v>Panipat</v>
       </c>
       <c r="L75" t="str">
-        <v>Samalkha, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M75" t="str">
         <v>failed</v>
       </c>
       <c r="N75" t="str">
-        <v>you are 12th passout student</v>
+        <v>NA</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -6626,31 +6626,31 @@
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>STUDENT_PASS_DBFE4113</v>
+        <v>STUDENT_PASS_F2EF40A0</v>
       </c>
       <c r="T75" t="str">
-        <v>Saved (69.4 KB)</v>
+        <v>Saved (86.9 KB)</v>
       </c>
       <c r="U75" t="str">
-        <v>rejected_guest_documents/dbfe4113-614a-4209-b00c-fc7bd3c92c35_school_id.jpg</v>
+        <v>rejected_guest_documents/f2ef40a0-6020-4574-b706-7bb00cc9b35e_school_id.jpg</v>
       </c>
       <c r="V75" t="str">
-        <v>Saved (100.0 KB)</v>
+        <v>Saved (91.4 KB)</v>
       </c>
       <c r="W75" t="str">
-        <v>rejected_guest_documents/dbfe4113-614a-4209-b00c-fc7bd3c92c35_aadhar.jpg</v>
+        <v>rejected_guest_documents/f2ef40a0-6020-4574-b706-7bb00cc9b35e_aadhar.jpg</v>
       </c>
       <c r="X75" t="str">
         <v>No</v>
       </c>
       <c r="Y75" t="str">
-        <v>29/9/2026, 8:41:14 pm</v>
+        <v>2/10/2026, 5:35:36 pm</v>
       </c>
       <c r="Z75" t="str">
-        <v>30/9/2026, 10:14:42 am</v>
+        <v>3/10/2026, 12:10:51 pm</v>
       </c>
       <c r="AA75" t="str">
-        <v>6abbd512c607490a6a5a0ccd</v>
+        <v>6abf9e10d9286e3efe7ea97e</v>
       </c>
     </row>
     <row r="76">
@@ -6658,28 +6658,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>20f03213-cab8-4596-af15-ef3445da197e</v>
+        <v>aa8bed74-bd8c-453b-b9c6-2a8cf4eeb9ef</v>
       </c>
       <c r="C76" t="str">
-        <v>Aryan</v>
+        <v>Suksham Jaglan</v>
       </c>
       <c r="D76" t="str">
-        <v>itssurajss00@gmail.com</v>
+        <v>jaglansuksham@gmail.com</v>
       </c>
       <c r="E76" t="str">
-        <v>+918950104605</v>
+        <v>7497875266</v>
       </c>
       <c r="F76" t="str">
-        <v>+918950104605</v>
+        <v>7497875266</v>
       </c>
       <c r="G76" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Govt model sanskriti senior secondary School israna Panipat</v>
       </c>
       <c r="H76" t="str">
         <v>Yes</v>
       </c>
       <c r="I76" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J76" t="str">
         <v>Haryana</v>
@@ -6709,31 +6709,31 @@
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>STUDENT_PASS_20F03213</v>
+        <v>STUDENT_PASS_AA8BED74</v>
       </c>
       <c r="T76" t="str">
-        <v>Saved (110.8 KB)</v>
+        <v>Saved (91.3 KB)</v>
       </c>
       <c r="U76" t="str">
-        <v>rejected_guest_documents/20f03213-cab8-4596-af15-ef3445da197e_school_id.jpg</v>
+        <v>rejected_guest_documents/aa8bed74-bd8c-453b-b9c6-2a8cf4eeb9ef_school_id.jpg</v>
       </c>
       <c r="V76" t="str">
-        <v>Saved (156.2 KB)</v>
+        <v>Saved (127.1 KB)</v>
       </c>
       <c r="W76" t="str">
-        <v>rejected_guest_documents/20f03213-cab8-4596-af15-ef3445da197e_aadhar.jpg</v>
+        <v>rejected_guest_documents/aa8bed74-bd8c-453b-b9c6-2a8cf4eeb9ef_aadhar.jpg</v>
       </c>
       <c r="X76" t="str">
         <v>No</v>
       </c>
       <c r="Y76" t="str">
-        <v>29/9/2026, 8:37:03 pm</v>
+        <v>2/10/2026, 5:29:56 pm</v>
       </c>
       <c r="Z76" t="str">
-        <v>2/10/2026, 3:21:28 pm</v>
+        <v>3/10/2026, 12:11:05 pm</v>
       </c>
       <c r="AA76" t="str">
-        <v>6abbd417c607490a6a5a0cc7</v>
+        <v>6abf9cbcd9286e3efe7ea97b</v>
       </c>
     </row>
     <row r="77">
@@ -6741,25 +6741,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>6f6abd95-ab7b-45f0-8931-9b4e7fec7af3</v>
+        <v>a7fb27be-54f8-4ed0-a73e-e335e4af130a</v>
       </c>
       <c r="C77" t="str">
-        <v>Aaditya Kumar</v>
+        <v>Jyoti Singh</v>
       </c>
       <c r="D77" t="str">
-        <v>aadityacyrus@gmail.com</v>
+        <v>jyotisingh8053@gmail.com</v>
       </c>
       <c r="E77" t="str">
-        <v>9254556364</v>
+        <v>8950690688</v>
       </c>
       <c r="F77" t="str">
-        <v>9254556364</v>
+        <v>8950690688</v>
       </c>
       <c r="G77" t="str">
-        <v>Government senior secondary school Krishnanpura</v>
+        <v>SD Senior Secondary School</v>
       </c>
       <c r="H77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I77" t="str">
         <v>12th</v>
@@ -6792,31 +6792,31 @@
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>STUDENT_PASS_6F6ABD95</v>
+        <v>STUDENT_PASS_A7FB27BE</v>
       </c>
       <c r="T77" t="str">
-        <v>Saved (165.5 KB)</v>
+        <v>Saved (197.7 KB)</v>
       </c>
       <c r="U77" t="str">
-        <v>rejected_guest_documents/6f6abd95-ab7b-45f0-8931-9b4e7fec7af3_school_id.jpg</v>
+        <v>rejected_guest_documents/a7fb27be-54f8-4ed0-a73e-e335e4af130a_school_id.jpg</v>
       </c>
       <c r="V77" t="str">
-        <v>Saved (58.8 KB)</v>
+        <v>Saved (254.4 KB)</v>
       </c>
       <c r="W77" t="str">
-        <v>rejected_guest_documents/6f6abd95-ab7b-45f0-8931-9b4e7fec7af3_aadhar.jpg</v>
+        <v>rejected_guest_documents/a7fb27be-54f8-4ed0-a73e-e335e4af130a_aadhar.jpg</v>
       </c>
       <c r="X77" t="str">
         <v>No</v>
       </c>
       <c r="Y77" t="str">
-        <v>29/9/2026, 7:35:09 pm</v>
+        <v>2/10/2026, 5:27:11 pm</v>
       </c>
       <c r="Z77" t="str">
-        <v>2/10/2026, 3:21:11 pm</v>
+        <v>3/10/2026, 12:13:15 pm</v>
       </c>
       <c r="AA77" t="str">
-        <v>6abbc595cd2997dbf204a115</v>
+        <v>6abf9c17d9286e3efe7ea978</v>
       </c>
     </row>
     <row r="78">
@@ -6824,28 +6824,28 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>8008edab-4927-449f-a834-96eddcee7ee8</v>
+        <v>a6c72984-db8d-4be3-bcfd-8349b62c2e86</v>
       </c>
       <c r="C78" t="str">
-        <v>Akash Kumar</v>
+        <v>Suksham Jaglan</v>
       </c>
       <c r="D78" t="str">
-        <v>aakashkumar258258@gmail.com</v>
+        <v>jaglansuksham@gmail.com</v>
       </c>
       <c r="E78" t="str">
-        <v>8816975214</v>
+        <v>7497875266</v>
       </c>
       <c r="F78" t="str">
-        <v>8816975214</v>
+        <v>7497875266</v>
       </c>
       <c r="G78" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Govt model Sanskriti senior secondary School israna</v>
       </c>
       <c r="H78" t="str">
         <v>Yes</v>
       </c>
       <c r="I78" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J78" t="str">
         <v>Haryana</v>
@@ -6875,31 +6875,31 @@
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>STUDENT_PASS_8008EDAB</v>
+        <v>STUDENT_PASS_A6C72984</v>
       </c>
       <c r="T78" t="str">
-        <v>Saved (116.0 KB)</v>
+        <v>Saved (91.3 KB)</v>
       </c>
       <c r="U78" t="str">
-        <v>rejected_guest_documents/8008edab-4927-449f-a834-96eddcee7ee8_school_id.jpg</v>
+        <v>rejected_guest_documents/a6c72984-db8d-4be3-bcfd-8349b62c2e86_school_id.jpg</v>
       </c>
       <c r="V78" t="str">
-        <v>Saved (79.6 KB)</v>
+        <v>Saved (127.1 KB)</v>
       </c>
       <c r="W78" t="str">
-        <v>rejected_guest_documents/8008edab-4927-449f-a834-96eddcee7ee8_aadhar.jpg</v>
+        <v>rejected_guest_documents/a6c72984-db8d-4be3-bcfd-8349b62c2e86_aadhar.jpg</v>
       </c>
       <c r="X78" t="str">
         <v>No</v>
       </c>
       <c r="Y78" t="str">
-        <v>29/9/2026, 7:32:29 pm</v>
+        <v>2/10/2026, 5:22:33 pm</v>
       </c>
       <c r="Z78" t="str">
-        <v>2/10/2026, 3:20:51 pm</v>
+        <v>3/10/2026, 12:36:39 pm</v>
       </c>
       <c r="AA78" t="str">
-        <v>6abbc4f5cd2997dbf204a10f</v>
+        <v>6abf9b01d9286e3efe7ea972</v>
       </c>
     </row>
     <row r="79">
@@ -6907,22 +6907,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>e822ea2a-8bf9-4d13-acfe-8f7acd48986a</v>
+        <v>c586b9ee-5b84-4f2f-8865-b5f7708b83ba</v>
       </c>
       <c r="C79" t="str">
-        <v>Akash Kumar</v>
+        <v>Jatin Kadyan</v>
       </c>
       <c r="D79" t="str">
-        <v>aakashkumar258258@gmail.com</v>
+        <v>jatinkadyanofficial@gmail.com</v>
       </c>
       <c r="E79" t="str">
-        <v>8816975214</v>
+        <v>9306566396</v>
       </c>
       <c r="F79" t="str">
-        <v>8816975214</v>
+        <v>9306566396</v>
       </c>
       <c r="G79" t="str">
-        <v>Gsss krishanpura</v>
+        <v>Sanatan Dharam vidya mandir city panipat</v>
       </c>
       <c r="H79" t="str">
         <v>Yes</v>
@@ -6958,31 +6958,31 @@
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>STUDENT_PASS_E822EA2A</v>
+        <v>STUDENT_PASS_C586B9EE</v>
       </c>
       <c r="T79" t="str">
-        <v>Saved (116.0 KB)</v>
+        <v>Saved (117.6 KB)</v>
       </c>
       <c r="U79" t="str">
-        <v>rejected_guest_documents/e822ea2a-8bf9-4d13-acfe-8f7acd48986a_school_id.jpg</v>
+        <v>rejected_guest_documents/c586b9ee-5b84-4f2f-8865-b5f7708b83ba_school_id.jpg</v>
       </c>
       <c r="V79" t="str">
-        <v>Saved (79.6 KB)</v>
+        <v>Saved (62.9 KB)</v>
       </c>
       <c r="W79" t="str">
-        <v>rejected_guest_documents/e822ea2a-8bf9-4d13-acfe-8f7acd48986a_aadhar.jpg</v>
+        <v>rejected_guest_documents/c586b9ee-5b84-4f2f-8865-b5f7708b83ba_aadhar.jpg</v>
       </c>
       <c r="X79" t="str">
         <v>No</v>
       </c>
       <c r="Y79" t="str">
-        <v>29/9/2026, 7:32:00 pm</v>
+        <v>2/10/2026, 12:01:47 pm</v>
       </c>
       <c r="Z79" t="str">
-        <v>2/10/2026, 3:20:34 pm</v>
+        <v>3/10/2026, 12:30:47 pm</v>
       </c>
       <c r="AA79" t="str">
-        <v>6abbc4d8cd2997dbf204a10c</v>
+        <v>6abf4fd3037e79b3dc9d9005</v>
       </c>
     </row>
     <row r="80">
@@ -6990,22 +6990,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>2b0b1648-b801-4ab0-a057-0cd72b808431</v>
+        <v>13650c45-a723-412f-8455-ba7cd00f06c3</v>
       </c>
       <c r="C80" t="str">
-        <v>Kirt guraya</v>
+        <v>Prince malik</v>
       </c>
       <c r="D80" t="str">
-        <v>kirtguraya2008@gmail.com</v>
+        <v>princejat000006@gmail.com</v>
       </c>
       <c r="E80" t="str">
-        <v>9817593654</v>
+        <v>9992244420</v>
       </c>
       <c r="F80" t="str">
-        <v>9817593654</v>
+        <v>9992244420</v>
       </c>
       <c r="G80" t="str">
-        <v>Jps academy</v>
+        <v>Haryana sr sec school</v>
       </c>
       <c r="H80" t="str">
         <v>Yes</v>
@@ -7017,16 +7017,16 @@
         <v>Haryana</v>
       </c>
       <c r="K80" t="str">
-        <v>Karnal</v>
+        <v>Panipat</v>
       </c>
       <c r="L80" t="str">
-        <v>Karnal, Haryana</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M80" t="str">
         <v>failed</v>
       </c>
       <c r="N80" t="str">
-        <v>SHARE X MARSHEET</v>
+        <v>NA</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -7041,31 +7041,31 @@
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>STUDENT_PASS_2B0B1648</v>
+        <v>STUDENT_PASS_13650C45</v>
       </c>
       <c r="T80" t="str">
-        <v>Saved (226.8 KB)</v>
+        <v>Saved (163.7 KB)</v>
       </c>
       <c r="U80" t="str">
-        <v>rejected_guest_documents/2b0b1648-b801-4ab0-a057-0cd72b808431_school_id.jpg</v>
+        <v>rejected_guest_documents/13650c45-a723-412f-8455-ba7cd00f06c3_school_id.jpg</v>
       </c>
       <c r="V80" t="str">
-        <v>Saved (128.2 KB)</v>
+        <v>Saved (105.9 KB)</v>
       </c>
       <c r="W80" t="str">
-        <v>rejected_guest_documents/2b0b1648-b801-4ab0-a057-0cd72b808431_aadhar.jpg</v>
+        <v>rejected_guest_documents/13650c45-a723-412f-8455-ba7cd00f06c3_aadhar.jpg</v>
       </c>
       <c r="X80" t="str">
         <v>No</v>
       </c>
       <c r="Y80" t="str">
-        <v>29/9/2026, 4:07:46 pm</v>
+        <v>2/10/2026, 11:22:37 am</v>
       </c>
       <c r="Z80" t="str">
-        <v>29/9/2026, 6:01:04 pm</v>
+        <v>3/10/2026, 12:33:54 pm</v>
       </c>
       <c r="AA80" t="str">
-        <v>6abb94fa5f1c99302803a618</v>
+        <v>6abf46a51161b48766d06759</v>
       </c>
     </row>
     <row r="81">
@@ -7073,28 +7073,28 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>3a09fe02-e249-4ea1-8b77-0c218d9caf8c</v>
+        <v>9ab210c2-8bb1-4869-8b4a-d59d2abaaa1d</v>
       </c>
       <c r="C81" t="str">
-        <v>Manik Rewri</v>
+        <v>Anshi tyagi</v>
       </c>
       <c r="D81" t="str">
-        <v>manikrewri21@gmail.com</v>
+        <v>tyagianshi9090@gmail.com</v>
       </c>
       <c r="E81" t="str">
-        <v>8307543005</v>
+        <v>8816040085</v>
       </c>
       <c r="F81" t="str">
-        <v>8307543005</v>
+        <v>8816040085</v>
       </c>
       <c r="G81" t="str">
-        <v>Dr MKK arya model school panipat</v>
+        <v>SANSKAR VELLY PUBLIC SCHOOL</v>
       </c>
       <c r="H81" t="str">
         <v>Yes</v>
       </c>
       <c r="I81" t="str">
-        <v>12th</v>
+        <v>11th</v>
       </c>
       <c r="J81" t="str">
         <v>Haryana</v>
@@ -7109,7 +7109,7 @@
         <v>failed</v>
       </c>
       <c r="N81" t="str">
-        <v>share x marksheet</v>
+        <v>please update your adhar card.</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -7124,31 +7124,31 @@
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>STUDENT_PASS_3A09FE02</v>
+        <v>STUDENT_PASS_9AB210C2</v>
       </c>
       <c r="T81" t="str">
-        <v>Saved (201.3 KB)</v>
+        <v>Saved (58.3 KB)</v>
       </c>
       <c r="U81" t="str">
-        <v>rejected_guest_documents/3a09fe02-e249-4ea1-8b77-0c218d9caf8c_school_id.jpg</v>
+        <v>rejected_guest_documents/9ab210c2-8bb1-4869-8b4a-d59d2abaaa1d_school_id.jpg</v>
       </c>
       <c r="V81" t="str">
-        <v>Saved (196.4 KB)</v>
+        <v>Saved (86.8 KB)</v>
       </c>
       <c r="W81" t="str">
-        <v>rejected_guest_documents/3a09fe02-e249-4ea1-8b77-0c218d9caf8c_aadhar.jpg</v>
+        <v>rejected_guest_documents/9ab210c2-8bb1-4869-8b4a-d59d2abaaa1d_aadhar.jpg</v>
       </c>
       <c r="X81" t="str">
         <v>No</v>
       </c>
       <c r="Y81" t="str">
-        <v>29/9/2026, 2:09:33 pm</v>
+        <v>30/9/2026, 4:01:00 pm</v>
       </c>
       <c r="Z81" t="str">
-        <v>29/9/2026, 5:58:15 pm</v>
+        <v>3/10/2026, 11:51:49 am</v>
       </c>
       <c r="AA81" t="str">
-        <v>6abb7945a3a7c4705795c399</v>
+        <v>6abce4e4017857fc0e0685fc</v>
       </c>
     </row>
     <row r="82">
@@ -7156,22 +7156,22 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>201f534a-0a40-4b01-baaa-bb8abdf5df15</v>
+        <v>de62e8e9-166f-42b1-adda-b671ee3bb504</v>
       </c>
       <c r="C82" t="str">
-        <v>LAKSHAY</v>
+        <v>Himanshu</v>
       </c>
       <c r="D82" t="str">
-        <v>lakshaymiglani76@gmail.com</v>
+        <v>hv86500@gmail.com</v>
       </c>
       <c r="E82" t="str">
-        <v>8816828631</v>
+        <v>7206756174</v>
       </c>
       <c r="F82" t="str">
-        <v>8816828631</v>
+        <v>7206756174</v>
       </c>
       <c r="G82" t="str">
-        <v>Dr. Mkk. Arya model school</v>
+        <v>Jawahar Navodaya Vidyalaya ,Panipat</v>
       </c>
       <c r="H82" t="str">
         <v>Yes</v>
@@ -7192,7 +7192,7 @@
         <v>failed</v>
       </c>
       <c r="N82" t="str">
-        <v>share x marksheet</v>
+        <v>NA</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -7207,31 +7207,31 @@
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>STUDENT_PASS_201F534A</v>
+        <v>STUDENT_PASS_DE62E8E9</v>
       </c>
       <c r="T82" t="str">
-        <v>Saved (80.3 KB)</v>
+        <v>Saved (50.8 KB)</v>
       </c>
       <c r="U82" t="str">
-        <v>rejected_guest_documents/201f534a-0a40-4b01-baaa-bb8abdf5df15_school_id.jpg</v>
+        <v>rejected_guest_documents/de62e8e9-166f-42b1-adda-b671ee3bb504_school_id.jpg</v>
       </c>
       <c r="V82" t="str">
-        <v>Saved (155.8 KB)</v>
+        <v>Saved (86.7 KB)</v>
       </c>
       <c r="W82" t="str">
-        <v>rejected_guest_documents/201f534a-0a40-4b01-baaa-bb8abdf5df15_aadhar.jpg</v>
+        <v>rejected_guest_documents/de62e8e9-166f-42b1-adda-b671ee3bb504_aadhar.jpg</v>
       </c>
       <c r="X82" t="str">
         <v>No</v>
       </c>
       <c r="Y82" t="str">
-        <v>29/9/2026, 1:47:46 pm</v>
+        <v>30/9/2026, 3:55:53 pm</v>
       </c>
       <c r="Z82" t="str">
-        <v>29/9/2026, 5:57:28 pm</v>
+        <v>3/10/2026, 11:51:17 am</v>
       </c>
       <c r="AA82" t="str">
-        <v>6abb742aa3a7c4705795c38d</v>
+        <v>6abce3b1017857fc0e0685f9</v>
       </c>
     </row>
     <row r="83">
@@ -7239,43 +7239,43 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>1ce6c851-fee1-4be1-9cf5-3fdb28c8d56a</v>
+        <v>e91b89d9-4720-44f3-b510-321af0e5788c</v>
       </c>
       <c r="C83" t="str">
-        <v>Dhairya Kukreja</v>
+        <v>Priyanshu</v>
       </c>
       <c r="D83" t="str">
-        <v>dhairyakukreja155@gmail.com</v>
+        <v>priyanshusamdhyan370@gmail.com</v>
       </c>
       <c r="E83" t="str">
-        <v>9034620721</v>
+        <v>9991889951</v>
       </c>
       <c r="F83" t="str">
-        <v>9034620721</v>
+        <v>9991889951</v>
       </c>
       <c r="G83" t="str">
-        <v>Dr mkk arya model school</v>
+        <v>Govt Model Sanskriti Sr Sec School Pundri Kaithal</v>
       </c>
       <c r="H83" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I83" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J83" t="str">
         <v>Haryana</v>
       </c>
       <c r="K83" t="str">
-        <v>Panipat</v>
+        <v>Kaithal</v>
       </c>
       <c r="L83" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Kaithal, Haryana</v>
       </c>
       <c r="M83" t="str">
         <v>failed</v>
       </c>
       <c r="N83" t="str">
-        <v>duplicate</v>
+        <v>NA</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -7290,31 +7290,31 @@
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>STUDENT_PASS_1CE6C851</v>
+        <v>STUDENT_PASS_E91B89D9</v>
       </c>
       <c r="T83" t="str">
-        <v>Saved (79.1 KB)</v>
+        <v>Saved (95.9 KB)</v>
       </c>
       <c r="U83" t="str">
-        <v>rejected_guest_documents/1ce6c851-fee1-4be1-9cf5-3fdb28c8d56a_school_id.jpg</v>
+        <v>rejected_guest_documents/e91b89d9-4720-44f3-b510-321af0e5788c_school_id.jpg</v>
       </c>
       <c r="V83" t="str">
-        <v>Saved (63.0 KB)</v>
+        <v>Saved (178.8 KB)</v>
       </c>
       <c r="W83" t="str">
-        <v>rejected_guest_documents/1ce6c851-fee1-4be1-9cf5-3fdb28c8d56a_aadhar.jpg</v>
+        <v>rejected_guest_documents/e91b89d9-4720-44f3-b510-321af0e5788c_aadhar.jpg</v>
       </c>
       <c r="X83" t="str">
         <v>No</v>
       </c>
       <c r="Y83" t="str">
-        <v>29/9/2026, 1:07:30 pm</v>
+        <v>30/9/2026, 3:24:23 pm</v>
       </c>
       <c r="Z83" t="str">
-        <v>29/9/2026, 5:55:03 pm</v>
+        <v>3/10/2026, 11:50:28 am</v>
       </c>
       <c r="AA83" t="str">
-        <v>6abb6abaab60f9bcd4efbd36</v>
+        <v>6abcdc4f1119fc00122e6631</v>
       </c>
     </row>
     <row r="84">
@@ -7322,43 +7322,43 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>7c9c560b-7e11-414d-bd42-6308827e9345</v>
+        <v>d5f7d0b2-571e-447e-8a50-48ddb57a110c</v>
       </c>
       <c r="C84" t="str">
-        <v>Navish Arora</v>
+        <v>Priyanshu</v>
       </c>
       <c r="D84" t="str">
-        <v>navishshab@gmail.com</v>
+        <v>priyanshusamdhyan370@gmail.com</v>
       </c>
       <c r="E84" t="str">
-        <v>7404656641</v>
+        <v>9991889951</v>
       </c>
       <c r="F84" t="str">
-        <v>7404656641</v>
+        <v>9991889951</v>
       </c>
       <c r="G84" t="str">
-        <v>The Heritage convent school</v>
+        <v>Govt Model Sanskriti Sr Sec School Pundri Kaithal</v>
       </c>
       <c r="H84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I84" t="str">
-        <v>11th</v>
+        <v>12th</v>
       </c>
       <c r="J84" t="str">
         <v>Haryana</v>
       </c>
       <c r="K84" t="str">
-        <v>Panipat</v>
+        <v>Kaithal</v>
       </c>
       <c r="L84" t="str">
-        <v>Panipat, Haryana</v>
+        <v>Kaithal, Haryana</v>
       </c>
       <c r="M84" t="str">
         <v>failed</v>
       </c>
       <c r="N84" t="str">
-        <v>duplicate</v>
+        <v>NA</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -7373,31 +7373,31 @@
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>STUDENT_PASS_7C9C560B</v>
+        <v>STUDENT_PASS_D5F7D0B2</v>
       </c>
       <c r="T84" t="str">
-        <v>Saved (103.4 KB)</v>
+        <v>Saved (95.9 KB)</v>
       </c>
       <c r="U84" t="str">
-        <v>rejected_guest_documents/7c9c560b-7e11-414d-bd42-6308827e9345_school_id.jpg</v>
+        <v>rejected_guest_documents/d5f7d0b2-571e-447e-8a50-48ddb57a110c_school_id.jpg</v>
       </c>
       <c r="V84" t="str">
-        <v>Saved (83.0 KB)</v>
+        <v>Saved (178.8 KB)</v>
       </c>
       <c r="W84" t="str">
-        <v>rejected_guest_documents/7c9c560b-7e11-414d-bd42-6308827e9345_aadhar.jpg</v>
+        <v>rejected_guest_documents/d5f7d0b2-571e-447e-8a50-48ddb57a110c_aadhar.jpg</v>
       </c>
       <c r="X84" t="str">
         <v>No</v>
       </c>
       <c r="Y84" t="str">
-        <v>29/9/2026, 12:40:17 pm</v>
+        <v>30/9/2026, 3:23:09 pm</v>
       </c>
       <c r="Z84" t="str">
-        <v>29/9/2026, 5:53:40 pm</v>
+        <v>3/10/2026, 11:49:05 am</v>
       </c>
       <c r="AA84" t="str">
-        <v>6abb64591430d12c0ce52c52</v>
+        <v>6abcdc051119fc00122e662b</v>
       </c>
     </row>
     <row r="85">
@@ -7405,43 +7405,43 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>f9d2a13c-a7c1-4c2a-981c-4dfb0fc55415</v>
+        <v>55a1ef84-8b14-48e6-a973-d4e5f804dac3</v>
       </c>
       <c r="C85" t="str">
-        <v>Sahil Bhardwaj</v>
+        <v>Aman kashyap</v>
       </c>
       <c r="D85" t="str">
-        <v>sahilbhardwaj4488@gmail.com</v>
+        <v>kashyapji20102009@gmail.com</v>
       </c>
       <c r="E85" t="str">
-        <v>9053709750</v>
+        <v>9896716251</v>
       </c>
       <c r="F85" t="str">
-        <v>9053709750</v>
+        <v>9896716251</v>
       </c>
       <c r="G85" t="str">
-        <v>Bal Bharati Public School Ludhiana</v>
+        <v>Hindu high school</v>
       </c>
       <c r="H85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I85" t="str">
         <v>12th</v>
       </c>
       <c r="J85" t="str">
-        <v>Punjab</v>
+        <v>Haryana</v>
       </c>
       <c r="K85" t="str">
-        <v>Ludhiana</v>
+        <v>Panipat</v>
       </c>
       <c r="L85" t="str">
-        <v>Ludhiana, Punjab</v>
+        <v>Panipat, Haryana</v>
       </c>
       <c r="M85" t="str">
         <v>failed</v>
       </c>
       <c r="N85" t="str">
-        <v>share proper documents</v>
+        <v>NA</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -7456,31 +7456,31 @@
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>STUDENT_PASS_F9D2A13C</v>
+        <v>STUDENT_PASS_55A1EF84</v>
       </c>
       <c r="T85" t="str">
-        <v>Saved (82.9 KB)</v>
+        <v>Saved (319.9 KB)</v>
       </c>
       <c r="U85" t="str">
-        <v>rejected_guest_documents/f9d2a13c-a7c1-4c2a-981c-4dfb0fc55415_school_id.jpg</v>
+        <v>rejected_guest_documents/55a1ef84-8b14-48e6-a973-d4e5f804dac3_school_id.jpg</v>
       </c>
       <c r="V85" t="str">
-        <v>Saved (37.3 KB)</v>
+        <v>Saved (181.0 KB)</v>
       </c>
       <c r="W85" t="str">
-        <v>rejected_guest_documents/f9d2a13c-a7c1-4c2a-981c-4dfb0fc55415_aadhar.jpg</v>
+        <v>rejected_guest_documents/55a1ef84-8b14-48e6-a973-d4e5f804dac3_aadhar.jpg</v>
       </c>
       <c r="X85" t="str">
         <v>No</v>
       </c>
       <c r="Y85" t="str">
-        <v>29/9/2026, 12:01:26 pm</v>
+        <v>30/9/2026, 3:17:18 pm</v>
       </c>
       <c r="Z85" t="str">
-        <v>29/9/2026, 5:52:48 pm</v>
+        <v>3/10/2026, 11:11:55 am</v>
       </c>
       <c r="AA85" t="str">
-        <v>6abb5b3ec69c3e84f3b442bf</v>
+        <v>6abcdaa61119fc00122e6625</v>
       </c>
     </row>
     <row r="86">
@@ -7488,22 +7488,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>e6a1e5a8-fc3d-48ed-8936-5f4a3dd2c09a</v>
+        <v>db8b4435-a395-4de9-920a-71adf79f433e</v>
       </c>
       <c r="C86" t="str">
-        <v>Gitansh</v>
+        <v>Happy Malik</v>
       </c>
       <c r="D86" t="str">
-        <v>ranagitansh8@gmail.com</v>
+        <v>happymalik0031@gmail.com</v>
       </c>
       <c r="E86" t="str">
-        <v>7015922250</v>
+        <v>9992837107</v>
       </c>
       <c r="F86" t="str">
-        <v>7015922250</v>
+        <v>9992837107</v>
       </c>
       <c r="G86" t="str">
-        <v>Sdvm(huda)</v>
+        <v>Geeta vidhya mandir public school, Nimb</v>
       </c>
       <c r="H86" t="str">
         <v>Yes</v>
@@ -7524,7 +7524,7 @@
         <v>failed</v>
       </c>
       <c r="N86" t="str">
-        <v>share proper id card</v>
+        <v>please check you name.</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -7539,31 +7539,31 @@
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>STUDENT_PASS_E6A1E5A8</v>
+        <v>STUDENT_PASS_DB8B4435</v>
       </c>
       <c r="T86" t="str">
-        <v>Saved (381.7 KB)</v>
+        <v>Saved (288.9 KB)</v>
       </c>
       <c r="U86" t="str">
-        <v>rejected_guest_documents/e6a1e5a8-fc3d-48ed-8936-5f4a3dd2c09a_school_id.jpg</v>
+        <v>rejected_guest_documents/db8b4435-a395-4de9-920a-71adf79f433e_school_id.jpg</v>
       </c>
       <c r="V86" t="str">
-        <v>Saved (138.0 KB)</v>
+        <v>Saved (258.8 KB)</v>
       </c>
       <c r="W86" t="str">
-        <v>rejected_guest_documents/e6a1e5a8-fc3d-48ed-8936-5f4a3dd2c09a_aadhar.jpg</v>
+        <v>rejected_guest_documents/db8b4435-a395-4de9-920a-71adf79f433e_aadhar.jpg</v>
       </c>
       <c r="X86" t="str">
         <v>No</v>
       </c>
       <c r="Y86" t="str">
-        <v>29/9/2026, 11:55:08 am</v>
+        <v>30/9/2026, 3:14:34 pm</v>
       </c>
       <c r="Z86" t="str">
-        <v>29/9/2026, 5:52:22 pm</v>
+        <v>3/10/2026, 11:11:32 am</v>
       </c>
       <c r="AA86" t="str">
-        <v>6abb59c4c69c3e84f3b442ba</v>
+        <v>6abcda021119fc00122e6622</v>
       </c>
     </row>
     <row r="87">
@@ -7571,25 +7571,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>6ae3227a-7df2-4b3f-bfbc-568f11336559</v>
+        <v>4af926be-e7b6-4f89-8c73-876ff5626a5d</v>
       </c>
       <c r="C87" t="str">
-        <v>Harsh narang</v>
+        <v>Lakshaydeep</v>
       </c>
       <c r="D87" t="str">
-        <v>harshnarang60152@gmail.com</v>
+        <v>shantanugehot261@gmail.com</v>
       </c>
       <c r="E87" t="str">
-        <v>8528596096</v>
+        <v>9306811395</v>
       </c>
       <c r="F87" t="str">
-        <v>8528596096</v>
+        <v>9306811395</v>
       </c>
       <c r="G87" t="str">
-        <v>Navyug Public school</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I87" t="str">
         <v>12th</v>
@@ -7607,7 +7607,7 @@
         <v>failed</v>
       </c>
       <c r="N87" t="str">
-        <v>not eligible</v>
+        <v>NA</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -7622,31 +7622,31 @@
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>STUDENT_PASS_6AE3227A</v>
+        <v>STUDENT_PASS_4AF926BE</v>
       </c>
       <c r="T87" t="str">
-        <v>Saved (131.0 KB)</v>
+        <v>Saved (102.2 KB)</v>
       </c>
       <c r="U87" t="str">
-        <v>rejected_guest_documents/6ae3227a-7df2-4b3f-bfbc-568f11336559_school_id.jpg</v>
+        <v>rejected_guest_documents/4af926be-e7b6-4f89-8c73-876ff5626a5d_school_id.jpg</v>
       </c>
       <c r="V87" t="str">
-        <v>Saved (20.1 KB)</v>
+        <v>Saved (67.3 KB)</v>
       </c>
       <c r="W87" t="str">
-        <v>rejected_guest_documents/6ae3227a-7df2-4b3f-bfbc-568f11336559_aadhar.jpg</v>
+        <v>rejected_guest_documents/4af926be-e7b6-4f89-8c73-876ff5626a5d_aadhar.jpg</v>
       </c>
       <c r="X87" t="str">
         <v>No</v>
       </c>
       <c r="Y87" t="str">
-        <v>29/9/2026, 11:51:04 am</v>
+        <v>30/9/2026, 2:02:25 pm</v>
       </c>
       <c r="Z87" t="str">
-        <v>29/9/2026, 5:51:27 pm</v>
+        <v>3/10/2026, 11:11:06 am</v>
       </c>
       <c r="AA87" t="str">
-        <v>6abb58d0c69c3e84f3b442b2</v>
+        <v>6abcc919a039e3629411cff8</v>
       </c>
     </row>
     <row r="88">
@@ -7654,25 +7654,25 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>a4e8b124-24e0-430b-8b7f-e764a0911e3e</v>
+        <v>2af40987-6d6b-410d-afbf-e576e6f56113</v>
       </c>
       <c r="C88" t="str">
-        <v>Harshit</v>
+        <v>Jishan</v>
       </c>
       <c r="D88" t="str">
-        <v>harshitsharma5820@gmail.com</v>
+        <v>jishanansari1403@gmail.com</v>
       </c>
       <c r="E88" t="str">
-        <v>7082775820</v>
+        <v>9138064586</v>
       </c>
       <c r="F88" t="str">
-        <v>7082775820</v>
+        <v>9138064586</v>
       </c>
       <c r="G88" t="str">
-        <v>Jay International School Jondhan Kalan Panipat</v>
+        <v>Govt Model Sanskriti Sr Sec School Red Light Panipat</v>
       </c>
       <c r="H88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I88" t="str">
         <v>12th</v>
@@ -7690,7 +7690,7 @@
         <v>failed</v>
       </c>
       <c r="N88" t="str">
-        <v>not eligible</v>
+        <v>NA</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -7705,2692 +7705,36 @@
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>STUDENT_PASS_A4E8B124</v>
+        <v>STUDENT_PASS_2AF40987</v>
       </c>
       <c r="T88" t="str">
-        <v>Saved (112.2 KB)</v>
+        <v>Saved (76.7 KB)</v>
       </c>
       <c r="U88" t="str">
-        <v>rejected_guest_documents/a4e8b124-24e0-430b-8b7f-e764a0911e3e_school_id.jpg</v>
+        <v>rejected_guest_documents/2af40987-6d6b-410d-afbf-e576e6f56113_school_id.jpg</v>
       </c>
       <c r="V88" t="str">
-        <v>Saved (102.9 KB)</v>
+        <v>Saved (70.6 KB)</v>
       </c>
       <c r="W88" t="str">
-        <v>rejected_guest_documents/a4e8b124-24e0-430b-8b7f-e764a0911e3e_aadhar.jpg</v>
+        <v>rejected_guest_documents/2af40987-6d6b-410d-afbf-e576e6f56113_aadhar.jpg</v>
       </c>
       <c r="X88" t="str">
         <v>No</v>
       </c>
       <c r="Y88" t="str">
-        <v>29/9/2026, 10:17:37 am</v>
+        <v>30/9/2026, 1:48:21 pm</v>
       </c>
       <c r="Z88" t="str">
-        <v>29/9/2026, 5:49:50 pm</v>
+        <v>3/10/2026, 11:10:46 am</v>
       </c>
       <c r="AA88" t="str">
-        <v>6abb42e95b7b4a36daf185e8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="str">
-        <v>a1cecfcc-2840-4fde-8671-332a9a25a988</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Shubham</v>
-      </c>
-      <c r="D89" t="str">
-        <v>shubhamkashyap62671@gmail.com</v>
-      </c>
-      <c r="E89" t="str">
-        <v>9350304003</v>
-      </c>
-      <c r="F89" t="str">
-        <v>9350304003</v>
-      </c>
-      <c r="G89" t="str">
-        <v>Jattal pol technical</v>
-      </c>
-      <c r="H89" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I89" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J89" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K89" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L89" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M89" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N89" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89" t="str">
-        <v/>
-      </c>
-      <c r="S89" t="str">
-        <v>STUDENT_PASS_A1CECFCC</v>
-      </c>
-      <c r="T89" t="str">
-        <v>Saved (64.9 KB)</v>
-      </c>
-      <c r="U89" t="str">
-        <v>rejected_guest_documents/a1cecfcc-2840-4fde-8671-332a9a25a988_school_id.jpg</v>
-      </c>
-      <c r="V89" t="str">
-        <v>Saved (99.8 KB)</v>
-      </c>
-      <c r="W89" t="str">
-        <v>rejected_guest_documents/a1cecfcc-2840-4fde-8671-332a9a25a988_aadhar.jpg</v>
-      </c>
-      <c r="X89" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y89" t="str">
-        <v>29/9/2026, 10:04:00 am</v>
-      </c>
-      <c r="Z89" t="str">
-        <v>29/9/2026, 5:41:12 pm</v>
-      </c>
-      <c r="AA89" t="str">
-        <v>6abb3fb81c2d6e689023152a</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="str">
-        <v>82644dee-9b77-486d-9182-feff70277c90</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Rajeet bhurtta</v>
-      </c>
-      <c r="D90" t="str">
-        <v>rajeetbhurtta@gmail.com</v>
-      </c>
-      <c r="E90" t="str">
-        <v>8397846430</v>
-      </c>
-      <c r="F90" t="str">
-        <v>8397846430</v>
-      </c>
-      <c r="G90" t="str">
-        <v>govt model sanskriti sr. sec.school</v>
-      </c>
-      <c r="H90" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I90" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J90" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K90" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L90" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M90" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N90" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90" t="str">
-        <v/>
-      </c>
-      <c r="S90" t="str">
-        <v>STUDENT_PASS_82644DEE</v>
-      </c>
-      <c r="T90" t="str">
-        <v>Saved (117.7 KB)</v>
-      </c>
-      <c r="U90" t="str">
-        <v>rejected_guest_documents/82644dee-9b77-486d-9182-feff70277c90_school_id.jpg</v>
-      </c>
-      <c r="V90" t="str">
-        <v>Saved (55.7 KB)</v>
-      </c>
-      <c r="W90" t="str">
-        <v>rejected_guest_documents/82644dee-9b77-486d-9182-feff70277c90_aadhar.jpg</v>
-      </c>
-      <c r="X90" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y90" t="str">
-        <v>29/9/2026, 9:51:43 am</v>
-      </c>
-      <c r="Z90" t="str">
-        <v>29/9/2026, 5:59:40 pm</v>
-      </c>
-      <c r="AA90" t="str">
-        <v>6abb3cd7122baea60cd9e703</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="str">
-        <v>8b438be4-601a-45d9-8a76-3cd51037b8ef</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Ajay</v>
-      </c>
-      <c r="D91" t="str">
-        <v>dhimanshab143@gmail.com</v>
-      </c>
-      <c r="E91" t="str">
-        <v>7015803705</v>
-      </c>
-      <c r="F91" t="str">
-        <v>7015803705</v>
-      </c>
-      <c r="G91" t="str">
-        <v>Pioneer public school</v>
-      </c>
-      <c r="H91" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I91" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J91" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K91" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L91" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M91" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N91" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>0</v>
-      </c>
-      <c r="R91" t="str">
-        <v/>
-      </c>
-      <c r="S91" t="str">
-        <v>STUDENT_PASS_8B438BE4</v>
-      </c>
-      <c r="T91" t="str">
-        <v>Saved (156.3 KB)</v>
-      </c>
-      <c r="U91" t="str">
-        <v>rejected_guest_documents/8b438be4-601a-45d9-8a76-3cd51037b8ef_school_id.jpg</v>
-      </c>
-      <c r="V91" t="str">
-        <v>Saved (63.1 KB)</v>
-      </c>
-      <c r="W91" t="str">
-        <v>rejected_guest_documents/8b438be4-601a-45d9-8a76-3cd51037b8ef_aadhar.jpg</v>
-      </c>
-      <c r="X91" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y91" t="str">
-        <v>29/9/2026, 8:42:06 am</v>
-      </c>
-      <c r="Z91" t="str">
-        <v>29/9/2026, 5:40:37 pm</v>
-      </c>
-      <c r="AA91" t="str">
-        <v>6abb2c86c324bceee89aaeaa</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="str">
-        <v>7c81797d-c7c4-400f-b54f-e9214e61ca3d</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Aryan singh</v>
-      </c>
-      <c r="D92" t="str">
-        <v>skateraryan1@gmail.com</v>
-      </c>
-      <c r="E92" t="str">
-        <v>8708597436</v>
-      </c>
-      <c r="F92" t="str">
-        <v>8708597436</v>
-      </c>
-      <c r="G92" t="str">
-        <v>Paryas international school</v>
-      </c>
-      <c r="H92" t="str">
-        <v>No</v>
-      </c>
-      <c r="I92" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J92" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K92" t="str">
-        <v>Gannaur</v>
-      </c>
-      <c r="L92" t="str">
-        <v>Gannaur, Haryana</v>
-      </c>
-      <c r="M92" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N92" t="str">
-        <v>upload id card</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>0</v>
-      </c>
-      <c r="R92" t="str">
-        <v/>
-      </c>
-      <c r="S92" t="str">
-        <v>STUDENT_PASS_7C81797D</v>
-      </c>
-      <c r="T92" t="str">
-        <v>Saved (60.7 KB)</v>
-      </c>
-      <c r="U92" t="str">
-        <v>rejected_guest_documents/7c81797d-c7c4-400f-b54f-e9214e61ca3d_school_id.jpg</v>
-      </c>
-      <c r="V92" t="str">
-        <v>Saved (86.9 KB)</v>
-      </c>
-      <c r="W92" t="str">
-        <v>rejected_guest_documents/7c81797d-c7c4-400f-b54f-e9214e61ca3d_aadhar.jpg</v>
-      </c>
-      <c r="X92" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y92" t="str">
-        <v>29/9/2026, 7:18:37 am</v>
-      </c>
-      <c r="Z92" t="str">
-        <v>29/9/2026, 5:39:59 pm</v>
-      </c>
-      <c r="AA92" t="str">
-        <v>6abb18f54b172242adc931cb</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="str">
-        <v>c28dbbe4-016b-4d52-8c70-f5021baa0bee</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Aryan singhSkater Aryan</v>
-      </c>
-      <c r="D93" t="str">
-        <v>sp5807143@gmail.com</v>
-      </c>
-      <c r="E93" t="str">
-        <v>8708597439</v>
-      </c>
-      <c r="F93" t="str">
-        <v>8708597439</v>
-      </c>
-      <c r="G93" t="str">
-        <v>Paryas international school</v>
-      </c>
-      <c r="H93" t="str">
-        <v>No</v>
-      </c>
-      <c r="I93" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J93" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K93" t="str">
-        <v>Gannaur</v>
-      </c>
-      <c r="L93" t="str">
-        <v>Gannaur, Haryana</v>
-      </c>
-      <c r="M93" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N93" t="str">
-        <v>upload id card</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>0</v>
-      </c>
-      <c r="R93" t="str">
-        <v/>
-      </c>
-      <c r="S93" t="str">
-        <v>STUDENT_PASS_C28DBBE4</v>
-      </c>
-      <c r="T93" t="str">
-        <v>Saved (151.3 KB)</v>
-      </c>
-      <c r="U93" t="str">
-        <v>rejected_guest_documents/c28dbbe4-016b-4d52-8c70-f5021baa0bee_school_id.jpg</v>
-      </c>
-      <c r="V93" t="str">
-        <v>Saved (86.9 KB)</v>
-      </c>
-      <c r="W93" t="str">
-        <v>rejected_guest_documents/c28dbbe4-016b-4d52-8c70-f5021baa0bee_aadhar.jpg</v>
-      </c>
-      <c r="X93" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y93" t="str">
-        <v>29/9/2026, 7:16:39 am</v>
-      </c>
-      <c r="Z93" t="str">
-        <v>29/9/2026, 5:39:34 pm</v>
-      </c>
-      <c r="AA93" t="str">
-        <v>6abb187f4b172242adc931c6</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="str">
-        <v>888455a9-fc62-4bbe-aeba-9199c545beeb</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Ridhiman</v>
-      </c>
-      <c r="D94" t="str">
-        <v>ridhimanarora6@gmail.com</v>
-      </c>
-      <c r="E94" t="str">
-        <v>9350065015</v>
-      </c>
-      <c r="F94" t="str">
-        <v>9350065015</v>
-      </c>
-      <c r="G94" t="str">
-        <v>Bal Vikas school</v>
-      </c>
-      <c r="H94" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I94" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J94" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K94" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L94" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M94" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N94" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>0</v>
-      </c>
-      <c r="R94" t="str">
-        <v/>
-      </c>
-      <c r="S94" t="str">
-        <v>STUDENT_PASS_888455A9</v>
-      </c>
-      <c r="T94" t="str">
-        <v>Saved (194.5 KB)</v>
-      </c>
-      <c r="U94" t="str">
-        <v>rejected_guest_documents/888455a9-fc62-4bbe-aeba-9199c545beeb_school_id.jpg</v>
-      </c>
-      <c r="V94" t="str">
-        <v>Saved (160.9 KB)</v>
-      </c>
-      <c r="W94" t="str">
-        <v>rejected_guest_documents/888455a9-fc62-4bbe-aeba-9199c545beeb_aadhar.jpg</v>
-      </c>
-      <c r="X94" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y94" t="str">
-        <v>29/9/2026, 1:22:39 am</v>
-      </c>
-      <c r="Z94" t="str">
-        <v>29/9/2026, 5:38:09 pm</v>
-      </c>
-      <c r="AA94" t="str">
-        <v>6abac587d5dcbe5172641562</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="str">
-        <v>f51e850c-b3c7-4a0a-88bd-6554c773ac5a</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Daksh Jaglan</v>
-      </c>
-      <c r="D95" t="str">
-        <v>dakshjaglan2008@gmail.com</v>
-      </c>
-      <c r="E95" t="str">
-        <v>9253270660</v>
-      </c>
-      <c r="F95" t="str">
-        <v>9253270660</v>
-      </c>
-      <c r="G95" t="str">
-        <v>Savitri shiksha Sadan</v>
-      </c>
-      <c r="H95" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I95" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J95" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K95" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L95" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M95" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N95" t="str">
-        <v>duplicate</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>0</v>
-      </c>
-      <c r="R95" t="str">
-        <v/>
-      </c>
-      <c r="S95" t="str">
-        <v>STUDENT_PASS_F51E850C</v>
-      </c>
-      <c r="T95" t="str">
-        <v>Saved (118.1 KB)</v>
-      </c>
-      <c r="U95" t="str">
-        <v>rejected_guest_documents/f51e850c-b3c7-4a0a-88bd-6554c773ac5a_school_id.jpg</v>
-      </c>
-      <c r="V95" t="str">
-        <v>Saved (52.9 KB)</v>
-      </c>
-      <c r="W95" t="str">
-        <v>rejected_guest_documents/f51e850c-b3c7-4a0a-88bd-6554c773ac5a_aadhar.jpg</v>
-      </c>
-      <c r="X95" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y95" t="str">
-        <v>29/9/2026, 1:22:14 am</v>
-      </c>
-      <c r="Z95" t="str">
-        <v>29/9/2026, 5:37:24 pm</v>
-      </c>
-      <c r="AA95" t="str">
-        <v>6abac56ed5dcbe517264155f</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="str">
-        <v>de6b8594-279a-4520-8a4b-65196f37dc77</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Anuvansh Bhatia</v>
-      </c>
-      <c r="D96" t="str">
-        <v>Anuvanshbhatia73@gmail.com</v>
-      </c>
-      <c r="E96" t="str">
-        <v>+91 98965 28893</v>
-      </c>
-      <c r="F96" t="str">
-        <v>+91 98965 28893</v>
-      </c>
-      <c r="G96" t="str">
-        <v>Bal vikas school</v>
-      </c>
-      <c r="H96" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I96" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J96" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K96" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L96" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M96" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N96" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>0</v>
-      </c>
-      <c r="R96" t="str">
-        <v/>
-      </c>
-      <c r="S96" t="str">
-        <v>STUDENT_PASS_DE6B8594</v>
-      </c>
-      <c r="T96" t="str">
-        <v>Saved (49.6 KB)</v>
-      </c>
-      <c r="U96" t="str">
-        <v>rejected_guest_documents/de6b8594-279a-4520-8a4b-65196f37dc77_school_id.jpg</v>
-      </c>
-      <c r="V96" t="str">
-        <v>Saved (125.0 KB)</v>
-      </c>
-      <c r="W96" t="str">
-        <v>rejected_guest_documents/de6b8594-279a-4520-8a4b-65196f37dc77_aadhar.jpg</v>
-      </c>
-      <c r="X96" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y96" t="str">
-        <v>28/9/2026, 11:13:56 pm</v>
-      </c>
-      <c r="Z96" t="str">
-        <v>29/9/2026, 5:35:53 pm</v>
-      </c>
-      <c r="AA96" t="str">
-        <v>6abaa75c235d876d8e37ccc7</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="str">
-        <v>71ba66fe-f403-4428-a94d-d908eae3f07c</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Onkar singh</v>
-      </c>
-      <c r="D97" t="str">
-        <v>tirthvirk105@gmail.com</v>
-      </c>
-      <c r="E97" t="str">
-        <v>7015322513</v>
-      </c>
-      <c r="F97" t="str">
-        <v>7015322513</v>
-      </c>
-      <c r="G97" t="str">
-        <v>Max international school</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I97" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J97" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K97" t="str">
-        <v>Assandh</v>
-      </c>
-      <c r="L97" t="str">
-        <v>Assandh, Haryana</v>
-      </c>
-      <c r="M97" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N97" t="str">
-        <v>duplicate</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>0</v>
-      </c>
-      <c r="R97" t="str">
-        <v/>
-      </c>
-      <c r="S97" t="str">
-        <v>STUDENT_PASS_71BA66FE</v>
-      </c>
-      <c r="T97" t="str">
-        <v>Saved (153.0 KB)</v>
-      </c>
-      <c r="U97" t="str">
-        <v>rejected_guest_documents/71ba66fe-f403-4428-a94d-d908eae3f07c_school_id.jpg</v>
-      </c>
-      <c r="V97" t="str">
-        <v>Saved (85.8 KB)</v>
-      </c>
-      <c r="W97" t="str">
-        <v>rejected_guest_documents/71ba66fe-f403-4428-a94d-d908eae3f07c_aadhar.jpg</v>
-      </c>
-      <c r="X97" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y97" t="str">
-        <v>28/9/2026, 11:12:10 pm</v>
-      </c>
-      <c r="Z97" t="str">
-        <v>29/9/2026, 5:35:19 pm</v>
-      </c>
-      <c r="AA97" t="str">
-        <v>6abaa6f2235d876d8e37ccc4</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="str">
-        <v>b801f5bf-60df-45bb-a62d-4278cc12e161</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Arnav Goyal</v>
-      </c>
-      <c r="D98" t="str">
-        <v>goyalarnav322@gmail.com</v>
-      </c>
-      <c r="E98" t="str">
-        <v>9518453768</v>
-      </c>
-      <c r="F98" t="str">
-        <v>9518453768</v>
-      </c>
-      <c r="G98" t="str">
-        <v>Delhi Public School Karnal</v>
-      </c>
-      <c r="H98" t="str">
-        <v>No</v>
-      </c>
-      <c r="I98" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J98" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K98" t="str">
-        <v>Karnal</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Karnal, Haryana</v>
-      </c>
-      <c r="M98" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N98" t="str">
-        <v>share X MARKSHEET</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>0</v>
-      </c>
-      <c r="R98" t="str">
-        <v/>
-      </c>
-      <c r="S98" t="str">
-        <v>STUDENT_PASS_B801F5BF</v>
-      </c>
-      <c r="T98" t="str">
-        <v>Saved (49.2 KB)</v>
-      </c>
-      <c r="U98" t="str">
-        <v>rejected_guest_documents/b801f5bf-60df-45bb-a62d-4278cc12e161_school_id.jpg</v>
-      </c>
-      <c r="V98" t="str">
-        <v>Saved (59.0 KB)</v>
-      </c>
-      <c r="W98" t="str">
-        <v>rejected_guest_documents/b801f5bf-60df-45bb-a62d-4278cc12e161_aadhar.jpg</v>
-      </c>
-      <c r="X98" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y98" t="str">
-        <v>28/9/2026, 11:03:02 pm</v>
-      </c>
-      <c r="Z98" t="str">
-        <v>29/9/2026, 5:58:59 pm</v>
-      </c>
-      <c r="AA98" t="str">
-        <v>6abaa4ce235d876d8e37ccc1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="str">
-        <v>2f4f5382-a0e4-4dad-ae82-3da57aaf5cae</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Pari</v>
-      </c>
-      <c r="D99" t="str">
-        <v>parigoyal1309@gmail.com</v>
-      </c>
-      <c r="E99" t="str">
-        <v>7015183785</v>
-      </c>
-      <c r="F99" t="str">
-        <v>7015183785</v>
-      </c>
-      <c r="G99" t="str">
-        <v>Delhi Public School Karnal</v>
-      </c>
-      <c r="H99" t="str">
-        <v>No</v>
-      </c>
-      <c r="I99" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J99" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K99" t="str">
-        <v>Karnal</v>
-      </c>
-      <c r="L99" t="str">
-        <v>Karnal, Haryana</v>
-      </c>
-      <c r="M99" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N99" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
-      <c r="R99" t="str">
-        <v/>
-      </c>
-      <c r="S99" t="str">
-        <v>STUDENT_PASS_2F4F5382</v>
-      </c>
-      <c r="T99" t="str">
-        <v>Saved (52.1 KB)</v>
-      </c>
-      <c r="U99" t="str">
-        <v>rejected_guest_documents/2f4f5382-a0e4-4dad-ae82-3da57aaf5cae_school_id.jpg</v>
-      </c>
-      <c r="V99" t="str">
-        <v>Saved (24.3 KB)</v>
-      </c>
-      <c r="W99" t="str">
-        <v>rejected_guest_documents/2f4f5382-a0e4-4dad-ae82-3da57aaf5cae_aadhar.jpg</v>
-      </c>
-      <c r="X99" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y99" t="str">
-        <v>28/9/2026, 10:55:34 pm</v>
-      </c>
-      <c r="Z99" t="str">
-        <v>29/9/2026, 5:33:28 pm</v>
-      </c>
-      <c r="AA99" t="str">
-        <v>6abaa30e235d876d8e37ccbb</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="str">
-        <v>2158e236-de9e-4aa7-8e92-5bda1a0a2682</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Vansh Narang</v>
-      </c>
-      <c r="D100" t="str">
-        <v>vanshnarang9646@gmail.com</v>
-      </c>
-      <c r="E100" t="str">
-        <v>9646451200</v>
-      </c>
-      <c r="F100" t="str">
-        <v>9646451200</v>
-      </c>
-      <c r="G100" t="str">
-        <v>Navyug Public school</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I100" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J100" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K100" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L100" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M100" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N100" t="str">
-        <v>upload complete id card</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>0</v>
-      </c>
-      <c r="R100" t="str">
-        <v/>
-      </c>
-      <c r="S100" t="str">
-        <v>STUDENT_PASS_2158E236</v>
-      </c>
-      <c r="T100" t="str">
-        <v>Saved (67.1 KB)</v>
-      </c>
-      <c r="U100" t="str">
-        <v>rejected_guest_documents/2158e236-de9e-4aa7-8e92-5bda1a0a2682_school_id.jpg</v>
-      </c>
-      <c r="V100" t="str">
-        <v>Saved (138.8 KB)</v>
-      </c>
-      <c r="W100" t="str">
-        <v>rejected_guest_documents/2158e236-de9e-4aa7-8e92-5bda1a0a2682_aadhar.jpg</v>
-      </c>
-      <c r="X100" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y100" t="str">
-        <v>28/9/2026, 10:34:46 pm</v>
-      </c>
-      <c r="Z100" t="str">
-        <v>29/9/2026, 5:31:23 pm</v>
-      </c>
-      <c r="AA100" t="str">
-        <v>6aba9e2e931c10fb5b465fce</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="str">
-        <v>e5c997a3-6b5a-4369-bd23-dd6bbf0ac791</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Vansh narang</v>
-      </c>
-      <c r="D101" t="str">
-        <v>vanshnarang9646@gmail.com</v>
-      </c>
-      <c r="E101" t="str">
-        <v>9646451200</v>
-      </c>
-      <c r="F101" t="str">
-        <v>9646451200</v>
-      </c>
-      <c r="G101" t="str">
-        <v>Navyug Public school</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I101" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J101" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K101" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L101" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M101" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N101" t="str">
-        <v>upload proper id card</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>0</v>
-      </c>
-      <c r="R101" t="str">
-        <v/>
-      </c>
-      <c r="S101" t="str">
-        <v>STUDENT_PASS_E5C997A3</v>
-      </c>
-      <c r="T101" t="str">
-        <v>Saved (67.1 KB)</v>
-      </c>
-      <c r="U101" t="str">
-        <v>rejected_guest_documents/e5c997a3-6b5a-4369-bd23-dd6bbf0ac791_school_id.jpg</v>
-      </c>
-      <c r="V101" t="str">
-        <v>Saved (138.8 KB)</v>
-      </c>
-      <c r="W101" t="str">
-        <v>rejected_guest_documents/e5c997a3-6b5a-4369-bd23-dd6bbf0ac791_aadhar.jpg</v>
-      </c>
-      <c r="X101" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y101" t="str">
-        <v>28/9/2026, 10:29:45 pm</v>
-      </c>
-      <c r="Z101" t="str">
-        <v>29/9/2026, 5:30:49 pm</v>
-      </c>
-      <c r="AA101" t="str">
-        <v>6aba9d01931c10fb5b465fcb</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="str">
-        <v>eba5d9dd-33a8-460b-ba7c-2ddeee23007c</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Charit</v>
-      </c>
-      <c r="D102" t="str">
-        <v>charitkaushik22@gmail.com</v>
-      </c>
-      <c r="E102" t="str">
-        <v>8053444004</v>
-      </c>
-      <c r="F102" t="str">
-        <v>8053444004</v>
-      </c>
-      <c r="G102" t="str">
-        <v>Hindu high school</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I102" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J102" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K102" t="str">
-        <v>Samalkha</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Samalkha, Haryana</v>
-      </c>
-      <c r="M102" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N102" t="str">
-        <v>not eligible</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>0</v>
-      </c>
-      <c r="R102" t="str">
-        <v/>
-      </c>
-      <c r="S102" t="str">
-        <v>STUDENT_PASS_EBA5D9DD</v>
-      </c>
-      <c r="T102" t="str">
-        <v>Saved (65.0 KB)</v>
-      </c>
-      <c r="U102" t="str">
-        <v>rejected_guest_documents/eba5d9dd-33a8-460b-ba7c-2ddeee23007c_school_id.jpg</v>
-      </c>
-      <c r="V102" t="str">
-        <v>Saved (65.9 KB)</v>
-      </c>
-      <c r="W102" t="str">
-        <v>rejected_guest_documents/eba5d9dd-33a8-460b-ba7c-2ddeee23007c_aadhar.jpg</v>
-      </c>
-      <c r="X102" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y102" t="str">
-        <v>28/9/2026, 10:13:49 pm</v>
-      </c>
-      <c r="Z102" t="str">
-        <v>29/9/2026, 5:29:25 pm</v>
-      </c>
-      <c r="AA102" t="str">
-        <v>6aba9945931c10fb5b465fc5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="str">
-        <v>16cfc622-efaa-40b0-a669-7493cb183368</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Arshad Khan</v>
-      </c>
-      <c r="D103" t="str">
-        <v>arshadk9683@gmail.com</v>
-      </c>
-      <c r="E103" t="str">
-        <v>9891104033</v>
-      </c>
-      <c r="F103" t="str">
-        <v>9891104033</v>
-      </c>
-      <c r="G103" t="str">
-        <v>Delhi University</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I103" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J103" t="str">
-        <v>Delhi</v>
-      </c>
-      <c r="K103" t="str">
-        <v>New Delhi</v>
-      </c>
-      <c r="L103" t="str">
-        <v>New Delhi, Delhi</v>
-      </c>
-      <c r="M103" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N103" t="str">
-        <v>only xii students are allowed</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>0</v>
-      </c>
-      <c r="R103" t="str">
-        <v/>
-      </c>
-      <c r="S103" t="str">
-        <v>STUDENT_PASS_16CFC622</v>
-      </c>
-      <c r="T103" t="str">
-        <v>Saved (103.3 KB)</v>
-      </c>
-      <c r="U103" t="str">
-        <v>rejected_guest_documents/16cfc622-efaa-40b0-a669-7493cb183368_school_id.jpg</v>
-      </c>
-      <c r="V103" t="str">
-        <v>Saved (38.2 KB)</v>
-      </c>
-      <c r="W103" t="str">
-        <v>rejected_guest_documents/16cfc622-efaa-40b0-a669-7493cb183368_aadhar.jpg</v>
-      </c>
-      <c r="X103" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y103" t="str">
-        <v>28/9/2026, 10:12:41 pm</v>
-      </c>
-      <c r="Z103" t="str">
-        <v>29/9/2026, 5:28:08 pm</v>
-      </c>
-      <c r="AA103" t="str">
-        <v>6aba9901931c10fb5b465fc2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104" t="str">
-        <v>e028578a-633a-4d59-bc20-8192458d7558</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Mayank</v>
-      </c>
-      <c r="D104" t="str">
-        <v>mayankkaushik2709@gmail.com</v>
-      </c>
-      <c r="E104" t="str">
-        <v>7015032007</v>
-      </c>
-      <c r="F104" t="str">
-        <v>7015032007</v>
-      </c>
-      <c r="G104" t="str">
-        <v>Maharaj agarsen public school</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I104" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J104" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K104" t="str">
-        <v>Samalkha</v>
-      </c>
-      <c r="L104" t="str">
-        <v>Samalkha, Haryana</v>
-      </c>
-      <c r="M104" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N104" t="str">
-        <v>please upload proper documents</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>0</v>
-      </c>
-      <c r="R104" t="str">
-        <v/>
-      </c>
-      <c r="S104" t="str">
-        <v>STUDENT_PASS_E028578A</v>
-      </c>
-      <c r="T104" t="str">
-        <v>Saved (51.6 KB)</v>
-      </c>
-      <c r="U104" t="str">
-        <v>rejected_guest_documents/e028578a-633a-4d59-bc20-8192458d7558_school_id.jpg</v>
-      </c>
-      <c r="V104" t="str">
-        <v>Saved (75.8 KB)</v>
-      </c>
-      <c r="W104" t="str">
-        <v>rejected_guest_documents/e028578a-633a-4d59-bc20-8192458d7558_aadhar.jpg</v>
-      </c>
-      <c r="X104" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y104" t="str">
-        <v>28/9/2026, 10:11:17 pm</v>
-      </c>
-      <c r="Z104" t="str">
-        <v>29/9/2026, 5:27:00 pm</v>
-      </c>
-      <c r="AA104" t="str">
-        <v>6aba98ad931c10fb5b465fbc</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" t="str">
-        <v>5aeddb6d-2508-4dbf-ad1b-72b652bbd989</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Paramjot singh</v>
-      </c>
-      <c r="D105" t="str">
-        <v>paramjotsingh2950@gmail.com</v>
-      </c>
-      <c r="E105" t="str">
-        <v>9253300048</v>
-      </c>
-      <c r="F105" t="str">
-        <v>9253300048</v>
-      </c>
-      <c r="G105" t="str">
-        <v>Arya bal bharti public school</v>
-      </c>
-      <c r="H105" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I105" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J105" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K105" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L105" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M105" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N105" t="str">
-        <v>documents not uploaded</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>0</v>
-      </c>
-      <c r="R105" t="str">
-        <v/>
-      </c>
-      <c r="S105" t="str">
-        <v>STUDENT_PASS_5AEDDB6D</v>
-      </c>
-      <c r="T105" t="str">
-        <v>Saved (7.4 KB)</v>
-      </c>
-      <c r="U105" t="str">
-        <v>rejected_guest_documents/5aeddb6d-2508-4dbf-ad1b-72b652bbd989_school_id.jpg</v>
-      </c>
-      <c r="V105" t="str">
-        <v>Saved (129.4 KB)</v>
-      </c>
-      <c r="W105" t="str">
-        <v>rejected_guest_documents/5aeddb6d-2508-4dbf-ad1b-72b652bbd989_aadhar.jpg</v>
-      </c>
-      <c r="X105" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y105" t="str">
-        <v>28/9/2026, 10:07:17 pm</v>
-      </c>
-      <c r="Z105" t="str">
-        <v>29/9/2026, 5:24:12 pm</v>
-      </c>
-      <c r="AA105" t="str">
-        <v>6aba97bd931c10fb5b465fb6</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106" t="str">
-        <v>35c390ca-da25-433f-a7b2-1b4f2f9cb265</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Mayank</v>
-      </c>
-      <c r="D106" t="str">
-        <v>mayankkaushik2709@gmail.com</v>
-      </c>
-      <c r="E106" t="str">
-        <v>8708018499</v>
-      </c>
-      <c r="F106" t="str">
-        <v>8708018499</v>
-      </c>
-      <c r="G106" t="str">
-        <v>Maharaj Agarsen public school</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I106" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J106" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K106" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L106" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M106" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N106" t="str">
-        <v>xii completed</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>0</v>
-      </c>
-      <c r="R106" t="str">
-        <v/>
-      </c>
-      <c r="S106" t="str">
-        <v>STUDENT_PASS_35C390CA</v>
-      </c>
-      <c r="T106" t="str">
-        <v>Saved (138.7 KB)</v>
-      </c>
-      <c r="U106" t="str">
-        <v>rejected_guest_documents/35c390ca-da25-433f-a7b2-1b4f2f9cb265_school_id.jpg</v>
-      </c>
-      <c r="V106" t="str">
-        <v>Saved (53.5 KB)</v>
-      </c>
-      <c r="W106" t="str">
-        <v>rejected_guest_documents/35c390ca-da25-433f-a7b2-1b4f2f9cb265_aadhar.jpg</v>
-      </c>
-      <c r="X106" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y106" t="str">
-        <v>28/9/2026, 10:01:32 pm</v>
-      </c>
-      <c r="Z106" t="str">
-        <v>29/9/2026, 5:23:03 pm</v>
-      </c>
-      <c r="AA106" t="str">
-        <v>6aba9664931c10fb5b465fb3</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107" t="str">
-        <v>f50e1b79-f2a3-4af9-8704-399ae675133e</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Shaleen Galhotra</v>
-      </c>
-      <c r="D107" t="str">
-        <v>galhotrashaleen8@gmail.com</v>
-      </c>
-      <c r="E107" t="str">
-        <v>8901114842</v>
-      </c>
-      <c r="F107" t="str">
-        <v>8901114842</v>
-      </c>
-      <c r="G107" t="str">
-        <v>DAV Huda Panipat</v>
-      </c>
-      <c r="H107" t="str">
-        <v>No</v>
-      </c>
-      <c r="I107" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J107" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K107" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M107" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N107" t="str">
-        <v>duplicate entry</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>0</v>
-      </c>
-      <c r="R107" t="str">
-        <v/>
-      </c>
-      <c r="S107" t="str">
-        <v>STUDENT_PASS_F50E1B79</v>
-      </c>
-      <c r="T107" t="str">
-        <v>Saved (111.3 KB)</v>
-      </c>
-      <c r="U107" t="str">
-        <v>rejected_guest_documents/f50e1b79-f2a3-4af9-8704-399ae675133e_school_id.jpg</v>
-      </c>
-      <c r="V107" t="str">
-        <v>Saved (94.3 KB)</v>
-      </c>
-      <c r="W107" t="str">
-        <v>rejected_guest_documents/f50e1b79-f2a3-4af9-8704-399ae675133e_aadhar.jpg</v>
-      </c>
-      <c r="X107" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y107" t="str">
-        <v>28/9/2026, 9:56:39 pm</v>
-      </c>
-      <c r="Z107" t="str">
-        <v>29/9/2026, 4:49:34 pm</v>
-      </c>
-      <c r="AA107" t="str">
-        <v>6aba953f931c10fb5b465fb0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" t="str">
-        <v>1aa04c29-30d7-4de6-8028-4c7f65dce37c</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Paramjot singh</v>
-      </c>
-      <c r="D108" t="str">
-        <v>paramjotsingh2950@gmail.com</v>
-      </c>
-      <c r="E108" t="str">
-        <v>9253300048</v>
-      </c>
-      <c r="F108" t="str">
-        <v>9253300048</v>
-      </c>
-      <c r="G108" t="str">
-        <v>Arya Sr Sec School Panipat</v>
-      </c>
-      <c r="H108" t="str">
-        <v>No</v>
-      </c>
-      <c r="I108" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J108" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K108" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L108" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M108" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N108" t="str">
-        <v>upload school id card</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108" t="str">
-        <v/>
-      </c>
-      <c r="S108" t="str">
-        <v>STUDENT_PASS_1AA04C29</v>
-      </c>
-      <c r="T108" t="str">
-        <v>Saved (78.0 KB)</v>
-      </c>
-      <c r="U108" t="str">
-        <v>rejected_guest_documents/1aa04c29-30d7-4de6-8028-4c7f65dce37c_school_id.jpg</v>
-      </c>
-      <c r="V108" t="str">
-        <v>Saved (129.4 KB)</v>
-      </c>
-      <c r="W108" t="str">
-        <v>rejected_guest_documents/1aa04c29-30d7-4de6-8028-4c7f65dce37c_aadhar.jpg</v>
-      </c>
-      <c r="X108" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y108" t="str">
-        <v>28/9/2026, 9:56:02 pm</v>
-      </c>
-      <c r="Z108" t="str">
-        <v>29/9/2026, 4:48:37 pm</v>
-      </c>
-      <c r="AA108" t="str">
-        <v>6aba951a931c10fb5b465fad</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109" t="str">
-        <v>4c559446-3fea-4030-9a5a-3055f8df41fd</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Shivam Rawal</v>
-      </c>
-      <c r="D109" t="str">
-        <v>rawalanu26@gmail.com</v>
-      </c>
-      <c r="E109" t="str">
-        <v>9467669287</v>
-      </c>
-      <c r="F109" t="str">
-        <v>9467669287</v>
-      </c>
-      <c r="G109" t="str">
-        <v>DAV Public school thermal colony panipat</v>
-      </c>
-      <c r="H109" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I109" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J109" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K109" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L109" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M109" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N109" t="str">
-        <v>upload complete picture of id card</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>0</v>
-      </c>
-      <c r="R109" t="str">
-        <v/>
-      </c>
-      <c r="S109" t="str">
-        <v>STUDENT_PASS_4C559446</v>
-      </c>
-      <c r="T109" t="str">
-        <v>Saved (240.5 KB)</v>
-      </c>
-      <c r="U109" t="str">
-        <v>rejected_guest_documents/4c559446-3fea-4030-9a5a-3055f8df41fd_school_id.jpg</v>
-      </c>
-      <c r="V109" t="str">
-        <v>Saved (312.7 KB)</v>
-      </c>
-      <c r="W109" t="str">
-        <v>rejected_guest_documents/4c559446-3fea-4030-9a5a-3055f8df41fd_aadhar.jpg</v>
-      </c>
-      <c r="X109" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y109" t="str">
-        <v>28/9/2026, 9:55:39 pm</v>
-      </c>
-      <c r="Z109" t="str">
-        <v>29/9/2026, 4:47:48 pm</v>
-      </c>
-      <c r="AA109" t="str">
-        <v>6aba9503931c10fb5b465fa7</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110" t="str">
-        <v>ccb9b238-641f-4f2d-9149-eb13513c265a</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Naman Singla</v>
-      </c>
-      <c r="D110" t="str">
-        <v>singlanaman920@gmail.com</v>
-      </c>
-      <c r="E110" t="str">
-        <v>9996644957</v>
-      </c>
-      <c r="F110" t="str">
-        <v>9996644957</v>
-      </c>
-      <c r="G110" t="str">
-        <v>S D Vidya Mandir</v>
-      </c>
-      <c r="H110" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I110" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J110" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K110" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L110" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M110" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N110" t="str">
-        <v>xii already completed</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>0</v>
-      </c>
-      <c r="R110" t="str">
-        <v/>
-      </c>
-      <c r="S110" t="str">
-        <v>STUDENT_PASS_CCB9B238</v>
-      </c>
-      <c r="T110" t="str">
-        <v>Saved (115.7 KB)</v>
-      </c>
-      <c r="U110" t="str">
-        <v>rejected_guest_documents/ccb9b238-641f-4f2d-9149-eb13513c265a_school_id.jpg</v>
-      </c>
-      <c r="V110" t="str">
-        <v>Saved (234.3 KB)</v>
-      </c>
-      <c r="W110" t="str">
-        <v>rejected_guest_documents/ccb9b238-641f-4f2d-9149-eb13513c265a_aadhar.jpg</v>
-      </c>
-      <c r="X110" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y110" t="str">
-        <v>28/9/2026, 9:52:18 pm</v>
-      </c>
-      <c r="Z110" t="str">
-        <v>29/9/2026, 4:46:46 pm</v>
-      </c>
-      <c r="AA110" t="str">
-        <v>6aba943a931c10fb5b465fa4</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111" t="str">
-        <v>337a425e-99a7-4765-9884-15db013bfe72</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Mayank</v>
-      </c>
-      <c r="D111" t="str">
-        <v>mayankkaushik2709@gmail.com</v>
-      </c>
-      <c r="E111" t="str">
-        <v>8708718499</v>
-      </c>
-      <c r="F111" t="str">
-        <v>8708718499</v>
-      </c>
-      <c r="G111" t="str">
-        <v>Maharaj agarsen public school</v>
-      </c>
-      <c r="H111" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I111" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J111" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K111" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L111" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M111" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N111" t="str">
-        <v>xii already completed</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>0</v>
-      </c>
-      <c r="R111" t="str">
-        <v/>
-      </c>
-      <c r="S111" t="str">
-        <v>STUDENT_PASS_337A425E</v>
-      </c>
-      <c r="T111" t="str">
-        <v>Saved (138.7 KB)</v>
-      </c>
-      <c r="U111" t="str">
-        <v>rejected_guest_documents/337a425e-99a7-4765-9884-15db013bfe72_school_id.jpg</v>
-      </c>
-      <c r="V111" t="str">
-        <v>Saved (53.5 KB)</v>
-      </c>
-      <c r="W111" t="str">
-        <v>rejected_guest_documents/337a425e-99a7-4765-9884-15db013bfe72_aadhar.jpg</v>
-      </c>
-      <c r="X111" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y111" t="str">
-        <v>28/9/2026, 9:51:26 pm</v>
-      </c>
-      <c r="Z111" t="str">
-        <v>29/9/2026, 4:45:26 pm</v>
-      </c>
-      <c r="AA111" t="str">
-        <v>6aba9406931c10fb5b465fa1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112" t="str">
-        <v>0857fdea-583a-4a56-bc92-3ccdad018432</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Yash Goyal</v>
-      </c>
-      <c r="D112" t="str">
-        <v>yash06hr@gmail.com</v>
-      </c>
-      <c r="E112" t="str">
-        <v>8168643928</v>
-      </c>
-      <c r="F112" t="str">
-        <v>8168643928</v>
-      </c>
-      <c r="G112" t="str">
-        <v>Arya bal bharti public school</v>
-      </c>
-      <c r="H112" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I112" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J112" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K112" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L112" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M112" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N112" t="str">
-        <v>xii already completed</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>0</v>
-      </c>
-      <c r="R112" t="str">
-        <v/>
-      </c>
-      <c r="S112" t="str">
-        <v>STUDENT_PASS_0857FDEA</v>
-      </c>
-      <c r="T112" t="str">
-        <v>Saved (194.1 KB)</v>
-      </c>
-      <c r="U112" t="str">
-        <v>rejected_guest_documents/0857fdea-583a-4a56-bc92-3ccdad018432_school_id.jpg</v>
-      </c>
-      <c r="V112" t="str">
-        <v>Saved (183.6 KB)</v>
-      </c>
-      <c r="W112" t="str">
-        <v>rejected_guest_documents/0857fdea-583a-4a56-bc92-3ccdad018432_aadhar.jpg</v>
-      </c>
-      <c r="X112" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y112" t="str">
-        <v>28/9/2026, 9:17:29 pm</v>
-      </c>
-      <c r="Z112" t="str">
-        <v>29/9/2026, 4:44:18 pm</v>
-      </c>
-      <c r="AA112" t="str">
-        <v>6aba8c11931c10fb5b465f9e</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113" t="str">
-        <v>6c14c2a9-e899-44a6-8ed2-537da9174d28</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Khushi Khanna</v>
-      </c>
-      <c r="D113" t="str">
-        <v>khushikhanna1270@gmail.com</v>
-      </c>
-      <c r="E113" t="str">
-        <v>9991332127</v>
-      </c>
-      <c r="F113" t="str">
-        <v>9991332127</v>
-      </c>
-      <c r="G113" t="str">
-        <v>Ravi High school</v>
-      </c>
-      <c r="H113" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I113" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J113" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K113" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L113" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M113" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N113" t="str">
-        <v>kindly upload enlarged documents</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113" t="str">
-        <v/>
-      </c>
-      <c r="S113" t="str">
-        <v>STUDENT_PASS_6C14C2A9</v>
-      </c>
-      <c r="T113" t="str">
-        <v>Saved (109.9 KB)</v>
-      </c>
-      <c r="U113" t="str">
-        <v>rejected_guest_documents/6c14c2a9-e899-44a6-8ed2-537da9174d28_school_id.jpg</v>
-      </c>
-      <c r="V113" t="str">
-        <v>Saved (57.9 KB)</v>
-      </c>
-      <c r="W113" t="str">
-        <v>rejected_guest_documents/6c14c2a9-e899-44a6-8ed2-537da9174d28_aadhar.jpg</v>
-      </c>
-      <c r="X113" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y113" t="str">
-        <v>28/9/2026, 8:36:43 pm</v>
-      </c>
-      <c r="Z113" t="str">
-        <v>29/9/2026, 4:38:41 pm</v>
-      </c>
-      <c r="AA113" t="str">
-        <v>6aba82832f8c3a147ff8da6c</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" t="str">
-        <v>06da4006-6c34-426f-8920-0bbb78584850</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Nikhil arora</v>
-      </c>
-      <c r="D114" t="str">
-        <v>na4570183@gmail.com</v>
-      </c>
-      <c r="E114" t="str">
-        <v>9053938601</v>
-      </c>
-      <c r="F114" t="str">
-        <v>9053938601</v>
-      </c>
-      <c r="G114" t="str">
-        <v>Ibl public school</v>
-      </c>
-      <c r="H114" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I114" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J114" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K114" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L114" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M114" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N114" t="str">
-        <v>done xii in 2025</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>0</v>
-      </c>
-      <c r="R114" t="str">
-        <v/>
-      </c>
-      <c r="S114" t="str">
-        <v>STUDENT_PASS_06DA4006</v>
-      </c>
-      <c r="T114" t="str">
-        <v>Saved (114.2 KB)</v>
-      </c>
-      <c r="U114" t="str">
-        <v>rejected_guest_documents/06da4006-6c34-426f-8920-0bbb78584850_school_id.jpg</v>
-      </c>
-      <c r="V114" t="str">
-        <v>Saved (31.3 KB)</v>
-      </c>
-      <c r="W114" t="str">
-        <v>rejected_guest_documents/06da4006-6c34-426f-8920-0bbb78584850_aadhar.jpg</v>
-      </c>
-      <c r="X114" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y114" t="str">
-        <v>28/9/2026, 8:25:30 pm</v>
-      </c>
-      <c r="Z114" t="str">
-        <v>29/9/2026, 4:37:54 pm</v>
-      </c>
-      <c r="AA114" t="str">
-        <v>6aba7fe22f8c3a147ff8da69</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" t="str">
-        <v>01ae3074-d3da-48fc-868f-77b7aafea4db</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Santoshi</v>
-      </c>
-      <c r="D115" t="str">
-        <v>sharmasoni5895@gmail.com</v>
-      </c>
-      <c r="E115" t="str">
-        <v>9896198960</v>
-      </c>
-      <c r="F115" t="str">
-        <v>9896198960</v>
-      </c>
-      <c r="G115" t="str">
-        <v>Dr.r.k sr sec school</v>
-      </c>
-      <c r="H115" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I115" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J115" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K115" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L115" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M115" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N115" t="str">
-        <v>kindly upload proper id card and adhar card with visible dob</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115" t="str">
-        <v/>
-      </c>
-      <c r="S115" t="str">
-        <v>STUDENT_PASS_01AE3074</v>
-      </c>
-      <c r="T115" t="str">
-        <v>Saved (118.8 KB)</v>
-      </c>
-      <c r="U115" t="str">
-        <v>rejected_guest_documents/01ae3074-d3da-48fc-868f-77b7aafea4db_school_id.jpg</v>
-      </c>
-      <c r="V115" t="str">
-        <v>Saved (76.3 KB)</v>
-      </c>
-      <c r="W115" t="str">
-        <v>rejected_guest_documents/01ae3074-d3da-48fc-868f-77b7aafea4db_aadhar.jpg</v>
-      </c>
-      <c r="X115" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y115" t="str">
-        <v>28/9/2026, 8:18:22 pm</v>
-      </c>
-      <c r="Z115" t="str">
-        <v>29/9/2026, 4:36:26 pm</v>
-      </c>
-      <c r="AA115" t="str">
-        <v>6aba7e362f8c3a147ff8da60</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" t="str">
-        <v>9a7d43e6-022f-4851-a4b4-67dd33a9153d</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Taniya</v>
-      </c>
-      <c r="D116" t="str">
-        <v>ms9275327@gmail.com</v>
-      </c>
-      <c r="E116" t="str">
-        <v>7988117700</v>
-      </c>
-      <c r="F116" t="str">
-        <v>7988117700</v>
-      </c>
-      <c r="G116" t="str">
-        <v>Dr.rk.sr.sec.school panipat</v>
-      </c>
-      <c r="H116" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I116" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J116" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K116" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L116" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M116" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N116" t="str">
-        <v>Student ID card not uploaded please upload school id card</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116" t="str">
-        <v/>
-      </c>
-      <c r="S116" t="str">
-        <v>STUDENT_PASS_9A7D43E6</v>
-      </c>
-      <c r="T116" t="str">
-        <v>Saved (37.1 KB)</v>
-      </c>
-      <c r="U116" t="str">
-        <v>rejected_guest_documents/9a7d43e6-022f-4851-a4b4-67dd33a9153d_school_id.jpg</v>
-      </c>
-      <c r="V116" t="str">
-        <v>Saved (76.1 KB)</v>
-      </c>
-      <c r="W116" t="str">
-        <v>rejected_guest_documents/9a7d43e6-022f-4851-a4b4-67dd33a9153d_aadhar.jpg</v>
-      </c>
-      <c r="X116" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y116" t="str">
-        <v>28/9/2026, 7:30:39 pm</v>
-      </c>
-      <c r="Z116" t="str">
-        <v>29/9/2026, 3:29:57 pm</v>
-      </c>
-      <c r="AA116" t="str">
-        <v>6aba73072f8c3a147ff8da4b</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" t="str">
-        <v>cc0ad637-ba68-4c16-8839-d2a80cb381bf</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Drishti Kaushik</v>
-      </c>
-      <c r="D117" t="str">
-        <v>drishtikaushik301@gmail.com</v>
-      </c>
-      <c r="E117" t="str">
-        <v>9050051108</v>
-      </c>
-      <c r="F117" t="str">
-        <v>9050051108</v>
-      </c>
-      <c r="G117" t="str">
-        <v>Maharaja Agrasen Public school</v>
-      </c>
-      <c r="H117" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I117" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J117" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K117" t="str">
-        <v>Samalkha</v>
-      </c>
-      <c r="L117" t="str">
-        <v>Samalkha, Haryana</v>
-      </c>
-      <c r="M117" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N117" t="str">
-        <v>you are passout</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>0</v>
-      </c>
-      <c r="R117" t="str">
-        <v/>
-      </c>
-      <c r="S117" t="str">
-        <v>STUDENT_PASS_CC0AD637</v>
-      </c>
-      <c r="T117" t="str">
-        <v>Saved (399.2 KB)</v>
-      </c>
-      <c r="U117" t="str">
-        <v>rejected_guest_documents/cc0ad637-ba68-4c16-8839-d2a80cb381bf_school_id.jpg</v>
-      </c>
-      <c r="V117" t="str">
-        <v>Saved (372.7 KB)</v>
-      </c>
-      <c r="W117" t="str">
-        <v>rejected_guest_documents/cc0ad637-ba68-4c16-8839-d2a80cb381bf_aadhar.jpg</v>
-      </c>
-      <c r="X117" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Y117" t="str">
-        <v>28/9/2026, 7:25:48 pm</v>
-      </c>
-      <c r="Z117" t="str">
-        <v>29/9/2026, 3:37:53 pm</v>
-      </c>
-      <c r="AA117" t="str">
-        <v>6aba71e42f8c3a147ff8da48</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118" t="str">
-        <v>553b75b2-f974-4f5f-b789-5c14e8373fed</v>
-      </c>
-      <c r="C118" t="str">
-        <v>Shivam</v>
-      </c>
-      <c r="D118" t="str">
-        <v>jaglanpushpa7@gmail.com</v>
-      </c>
-      <c r="E118" t="str">
-        <v>7015325454</v>
-      </c>
-      <c r="F118" t="str">
-        <v>7015325454</v>
-      </c>
-      <c r="G118" t="str">
-        <v>G.S.S.S BURSHAM PANIPAT</v>
-      </c>
-      <c r="H118" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I118" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J118" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K118" t="str">
-        <v>Panipat</v>
-      </c>
-      <c r="L118" t="str">
-        <v>Panipat, Haryana</v>
-      </c>
-      <c r="M118" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N118" t="str">
-        <v>PLease upload shivam Student ID card</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118" t="str">
-        <v/>
-      </c>
-      <c r="S118" t="str">
-        <v>STUDENT_PASS_553B75B2</v>
-      </c>
-      <c r="T118" t="str">
-        <v>Saved (84.0 KB)</v>
-      </c>
-      <c r="U118" t="str">
-        <v>rejected_guest_documents/553b75b2-f974-4f5f-b789-5c14e8373fed_school_id.jpg</v>
-      </c>
-      <c r="V118" t="str">
-        <v>Saved (71.1 KB)</v>
-      </c>
-      <c r="W118" t="str">
-        <v>rejected_guest_documents/553b75b2-f974-4f5f-b789-5c14e8373fed_aadhar.jpg</v>
-      </c>
-      <c r="X118" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y118" t="str">
-        <v>28/9/2026, 6:37:15 pm</v>
-      </c>
-      <c r="Z118" t="str">
-        <v>29/9/2026, 3:33:13 pm</v>
-      </c>
-      <c r="AA118" t="str">
-        <v>6aba66832f8c3a147ff8da2e</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119" t="str">
-        <v>1a26525a-b3ae-44be-8fc6-22dcc99502bf</v>
-      </c>
-      <c r="C119" t="str">
-        <v>Sahil Bhardwaj</v>
-      </c>
-      <c r="D119" t="str">
-        <v>sahilbhardwaj4488@gmail.com</v>
-      </c>
-      <c r="E119" t="str">
-        <v>9053709750</v>
-      </c>
-      <c r="F119" t="str">
-        <v>9053709750</v>
-      </c>
-      <c r="G119" t="str">
-        <v>Adarsh Sr. Sec. School</v>
-      </c>
-      <c r="H119" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="I119" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J119" t="str">
-        <v>Haryana</v>
-      </c>
-      <c r="K119" t="str">
-        <v>Faridabad</v>
-      </c>
-      <c r="L119" t="str">
-        <v>Faridabad, Haryana</v>
-      </c>
-      <c r="M119" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N119" t="str">
-        <v>Real document not uploaded</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119" t="str">
-        <v/>
-      </c>
-      <c r="S119" t="str">
-        <v>STUDENT_PASS_1A26525A</v>
-      </c>
-      <c r="T119" t="str">
-        <v>Saved (37.3 KB)</v>
-      </c>
-      <c r="U119" t="str">
-        <v>rejected_guest_documents/1a26525a-b3ae-44be-8fc6-22dcc99502bf_school_id.jpg</v>
-      </c>
-      <c r="V119" t="str">
-        <v>Saved (82.9 KB)</v>
-      </c>
-      <c r="W119" t="str">
-        <v>rejected_guest_documents/1a26525a-b3ae-44be-8fc6-22dcc99502bf_aadhar.jpg</v>
-      </c>
-      <c r="X119" t="str">
-        <v>No</v>
-      </c>
-      <c r="Y119" t="str">
-        <v>28/9/2026, 10:43:55 am</v>
-      </c>
-      <c r="Z119" t="str">
-        <v>28/9/2026, 10:48:13 am</v>
-      </c>
-      <c r="AA119" t="str">
-        <v>6ab9f793f526a1aea861afcc</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120" t="str">
-        <v>885d859d-fb55-478f-8fa9-b9cecfdca3d0</v>
-      </c>
-      <c r="C120" t="str">
-        <v>Sahil Bhardwaj</v>
-      </c>
-      <c r="D120" t="str">
-        <v>sahilbhardwaj4488@gmail.com</v>
-      </c>
-      <c r="E120" t="str">
-        <v>9053709750</v>
-      </c>
-      <c r="F120" t="str">
-        <v>9053709750</v>
-      </c>
-      <c r="G120" t="str">
-        <v>geeta</v>
-      </c>
-      <c r="H120" t="str">
-        <v>No</v>
-      </c>
-      <c r="I120" t="str">
-        <v>12th</v>
-      </c>
-      <c r="J120" t="str">
-        <v/>
-      </c>
-      <c r="K120" t="str">
-        <v>Rohtak</v>
-      </c>
-      <c r="L120" t="str">
-        <v>Rohtak</v>
-      </c>
-      <c r="M120" t="str">
-        <v>failed</v>
-      </c>
-      <c r="N120" t="str">
-        <v>Documents could not be verified</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120" t="str">
-        <v/>
-      </c>
-      <c r="S120" t="str">
-        <v>STUDENT_PASS_885D859D</v>
-      </c>
-      <c r="T120" t="str">
-        <v>Not Provided</v>
-      </c>
-      <c r="U120" t="str">
-        <v/>
-      </c>
-      <c r="V120" t="str">
-        <v>Not Provided</v>
-      </c>
-      <c r="W120" t="str">
-        <v/>
-      </c>
-      <c r="X120" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Y120" t="str">
-        <v>26/9/2026, 11:57:51 am</v>
-      </c>
-      <c r="Z120" t="str">
-        <v>29/9/2026, 1:55:46 pm</v>
-      </c>
-      <c r="AA120" t="str">
-        <v>6ab765e733e7578048f5b8a1</v>
+        <v>6abcc5cd083b87ff8a3f6370</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA120"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA88"/>
   </ignoredErrors>
 </worksheet>
 </file>